--- a/в бланки заводов/Останкино СЫР/OrderCheeseInForm/новый_бланк/Бланк заказов сыр  дистр.xlsx
+++ b/в бланки заводов/Останкино СЫР/OrderCheeseInForm/новый_бланк/Бланк заказов сыр  дистр.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино СЫР\OrderCheeseInForm\новый_бланк\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{017696ED-97B3-48DD-AEB8-97AA4881C7C7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B306DB2A-9113-4CF9-ACA8-DF9BAE49D8D5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Мелитополь" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="82">
   <si>
     <t>Артикул</t>
   </si>
@@ -249,9 +249,6 @@
     <t>Майонезный соус провансаль деликатесный с массовой долей жира 25%ТМ "Коровино" 824,5 г</t>
   </si>
   <si>
-    <t>Сыр полутвердый Российский, цилиндр, 1/4, пленка с логотипом ЮКМП, массовая доля жира в сухом веществе 50%</t>
-  </si>
-  <si>
     <t>Сыр Косичка сырная 45% 100г/8шт ТМ Папа Может</t>
   </si>
   <si>
@@ -271,6 +268,21 @@
   </si>
   <si>
     <t>Продукт белково-жировой Сметанковый 50% вес ТМ Коровино</t>
+  </si>
+  <si>
+    <t>не доступно к заказу</t>
+  </si>
+  <si>
+    <t>Сыр полутвердый Российский, цилиндр, 1/4, пленка, массовая доля жира в сухом веществе 50%</t>
+  </si>
+  <si>
+    <t>Сыр полутвердый "Голландский" с массовой долей жира в пересчете на сухое вещество 45%, брус из блока 1/5, пленка желтая, короб складной ТМ Папа может</t>
+  </si>
+  <si>
+    <t>Сыр полутвердый "Купеческий" с ароматом топленого молока, с массовой долей жира в пересчете на сухое вещество 50%, брус из блока 1/5, пленка желтая, короб складной ТМ "Папа может"</t>
+  </si>
+  <si>
+    <t>Средний вес короба 16,4( вес 1 брус 3,2кг)</t>
   </si>
 </sst>
 </file>
@@ -479,11 +491,6 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -530,6 +537,11 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -902,7 +914,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I59"/>
+  <dimension ref="A1:I61"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="10" style="4" customWidth="1"/>
@@ -948,31 +960,31 @@
       <c r="I2" s="7"/>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="15" t="s">
+      <c r="A3" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="D3" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="16" t="s">
+      <c r="E3" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="15" t="s">
+      <c r="F3" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="17" t="s">
+      <c r="G3" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="11" t="s">
         <v>7</v>
       </c>
     </row>
@@ -980,14 +992,14 @@
       <c r="A4" s="1">
         <v>5038435</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="19" t="s">
         <v>35</v>
       </c>
       <c r="C4" s="10">
         <v>10</v>
       </c>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
       <c r="F4" s="11">
         <f>D4/C4</f>
         <v>0</v>
@@ -1011,8 +1023,10 @@
       <c r="C5" s="10">
         <v>5</v>
       </c>
-      <c r="D5" s="20"/>
-      <c r="E5" s="20"/>
+      <c r="D5" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="E5" s="17"/>
       <c r="F5" s="11">
         <f>E5/16.5</f>
         <v>0</v>
@@ -1026,43 +1040,43 @@
       </c>
       <c r="I5" s="11"/>
     </row>
-    <row r="6" spans="1:9" s="29" customFormat="1" ht="25.5">
-      <c r="A6" s="23">
+    <row r="6" spans="1:9" s="26" customFormat="1" ht="25.5">
+      <c r="A6" s="20">
         <v>8783323</v>
       </c>
-      <c r="B6" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="C6" s="25">
-        <v>8</v>
-      </c>
-      <c r="D6" s="26"/>
-      <c r="E6" s="20"/>
-      <c r="F6" s="27">
-        <f>E5/15</f>
-        <v>0</v>
-      </c>
-      <c r="G6" s="28">
+      <c r="B6" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="C6" s="22">
+        <v>4</v>
+      </c>
+      <c r="D6" s="23"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="11">
+        <f>E6/5</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="25">
         <v>1.8</v>
       </c>
-      <c r="H6" s="27">
+      <c r="H6" s="24">
         <f>E6</f>
         <v>0</v>
       </c>
-      <c r="I6" s="27"/>
+      <c r="I6" s="24"/>
     </row>
     <row r="7" spans="1:9" s="13" customFormat="1" ht="25.5">
       <c r="A7" s="1">
         <v>5038459</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="19" t="s">
         <v>33</v>
       </c>
       <c r="C7" s="10">
         <v>10</v>
       </c>
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
       <c r="F7" s="11">
         <f>D7/C7</f>
         <v>0</v>
@@ -1077,100 +1091,102 @@
       <c r="I7" s="11"/>
     </row>
     <row r="8" spans="1:9" s="13" customFormat="1" ht="25.5">
-      <c r="A8" s="1">
+      <c r="A8" s="20">
+        <v>8785235</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="C8" s="10">
+        <v>5</v>
+      </c>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="11">
+        <f>E8/16.5</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="11">
+        <v>3.5</v>
+      </c>
+      <c r="H8" s="11">
+        <f>E8</f>
+        <v>0</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" s="13" customFormat="1" ht="25.5">
+      <c r="A9" s="1">
         <v>5038411</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B9" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C9" s="10">
         <v>10</v>
       </c>
-      <c r="D8" s="20"/>
-      <c r="E8" s="20"/>
-      <c r="F8" s="11">
-        <f>D8/C8</f>
-        <v>0</v>
-      </c>
-      <c r="G8" s="12">
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="11">
+        <f>D9/C9</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="12">
         <v>0.18</v>
       </c>
-      <c r="H8" s="11">
-        <f>G8*D8</f>
-        <v>0</v>
-      </c>
-      <c r="I8" s="11"/>
-    </row>
-    <row r="9" spans="1:9" s="13" customFormat="1" ht="25.5">
-      <c r="A9" s="2">
+      <c r="H9" s="11">
+        <f>G9*D9</f>
+        <v>0</v>
+      </c>
+      <c r="I9" s="11"/>
+    </row>
+    <row r="10" spans="1:9" s="13" customFormat="1" ht="25.5">
+      <c r="A10" s="2">
         <v>8785242</v>
       </c>
-      <c r="B9" s="22" t="s">
+      <c r="B10" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C10" s="10">
         <v>5</v>
       </c>
-      <c r="D9" s="20"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="11">
-        <f>E9/16.5</f>
-        <v>0</v>
-      </c>
-      <c r="G9" s="11">
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="11">
+        <f>E10/16.5</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="11">
         <v>3.5</v>
       </c>
-      <c r="H9" s="11">
-        <f>E9</f>
-        <v>0</v>
-      </c>
-      <c r="I9" s="11" t="s">
+      <c r="H10" s="11">
+        <f>E10</f>
+        <v>0</v>
+      </c>
+      <c r="I10" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:9" s="13" customFormat="1" ht="25.5">
-      <c r="A10" s="1">
+    <row r="11" spans="1:9" s="13" customFormat="1" ht="25.5">
+      <c r="A11" s="1">
         <v>5038398</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B11" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="10">
+      <c r="C11" s="10">
         <v>10</v>
       </c>
-      <c r="D10" s="20"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="11">
-        <f>D10/C10</f>
-        <v>0</v>
-      </c>
-      <c r="G10" s="12">
-        <v>0.18</v>
-      </c>
-      <c r="H10" s="11">
-        <f>G10*D10</f>
-        <v>0</v>
-      </c>
-      <c r="I10" s="11"/>
-    </row>
-    <row r="11" spans="1:9" s="13" customFormat="1">
-      <c r="A11" s="1">
-        <v>5039609</v>
-      </c>
-      <c r="B11" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="C11" s="10">
-        <v>8</v>
-      </c>
-      <c r="D11" s="20"/>
-      <c r="E11" s="20"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
       <c r="F11" s="11">
         <f>D11/C11</f>
         <v>0</v>
       </c>
       <c r="G11" s="12">
-        <v>0.4</v>
+        <v>0.18</v>
       </c>
       <c r="H11" s="11">
         <f>G11*D11</f>
@@ -1178,74 +1194,76 @@
       </c>
       <c r="I11" s="11"/>
     </row>
-    <row r="12" spans="1:9" s="13" customFormat="1" ht="25.5">
-      <c r="A12" s="2">
-        <v>8785259</v>
-      </c>
-      <c r="B12" s="22" t="s">
-        <v>52</v>
+    <row r="12" spans="1:9" s="13" customFormat="1">
+      <c r="A12" s="1">
+        <v>5039609</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>43</v>
       </c>
       <c r="C12" s="10">
-        <v>5</v>
-      </c>
-      <c r="D12" s="20"/>
-      <c r="E12" s="20"/>
+        <v>8</v>
+      </c>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17" t="s">
+        <v>77</v>
+      </c>
       <c r="F12" s="11">
-        <f>E12/16.5</f>
-        <v>0</v>
-      </c>
-      <c r="G12" s="11">
-        <v>3.5</v>
+        <f>D12/C12</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="12">
+        <v>0.4</v>
       </c>
       <c r="H12" s="11">
-        <f>E12</f>
+        <f>G12*D12</f>
         <v>0</v>
       </c>
       <c r="I12" s="11"/>
     </row>
     <row r="13" spans="1:9" s="13" customFormat="1" ht="25.5">
       <c r="A13" s="2">
+        <v>8785259</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" s="10">
+        <v>5</v>
+      </c>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="11">
+        <f>E13/16.5</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="11">
+        <v>3.5</v>
+      </c>
+      <c r="H13" s="11">
+        <f>E13</f>
+        <v>0</v>
+      </c>
+      <c r="I13" s="11"/>
+    </row>
+    <row r="14" spans="1:9" s="13" customFormat="1" ht="25.5">
+      <c r="A14" s="2">
         <v>5038855</v>
       </c>
-      <c r="B13" s="30" t="s">
+      <c r="B14" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="C13" s="10">
+      <c r="C14" s="10">
         <v>10</v>
       </c>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="11">
-        <f t="shared" ref="F13:F25" si="0">D13/C13</f>
-        <v>0</v>
-      </c>
-      <c r="G13" s="12">
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="11">
+        <f t="shared" ref="F14:F27" si="0">D14/C14</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="12">
         <v>0.2</v>
-      </c>
-      <c r="H13" s="11">
-        <f>G13*D13</f>
-        <v>0</v>
-      </c>
-      <c r="I13" s="11"/>
-    </row>
-    <row r="14" spans="1:9" s="13" customFormat="1">
-      <c r="A14" s="2">
-        <v>5039647</v>
-      </c>
-      <c r="B14" s="31" t="s">
-        <v>44</v>
-      </c>
-      <c r="C14" s="10">
-        <v>8</v>
-      </c>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G14" s="12">
-        <v>0.4</v>
       </c>
       <c r="H14" s="11">
         <f>G14*D14</f>
@@ -1253,24 +1271,24 @@
       </c>
       <c r="I14" s="11"/>
     </row>
-    <row r="15" spans="1:9" s="13" customFormat="1" ht="25.5">
+    <row r="15" spans="1:9" s="13" customFormat="1">
       <c r="A15" s="2">
-        <v>5038831</v>
-      </c>
-      <c r="B15" s="22" t="s">
-        <v>39</v>
-      </c>
-      <c r="C15" s="32">
-        <v>10</v>
-      </c>
-      <c r="D15" s="20"/>
-      <c r="E15" s="20"/>
+        <v>5039647</v>
+      </c>
+      <c r="B15" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="10">
+        <v>8</v>
+      </c>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
       <c r="F15" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G15" s="12">
-        <v>0.18</v>
+        <v>0.4</v>
       </c>
       <c r="H15" s="11">
         <f>G15*D15</f>
@@ -1278,24 +1296,24 @@
       </c>
       <c r="I15" s="11"/>
     </row>
-    <row r="16" spans="1:9" s="13" customFormat="1">
+    <row r="16" spans="1:9" s="13" customFormat="1" ht="25.5">
       <c r="A16" s="2">
-        <v>5039623</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="C16" s="32">
-        <v>8</v>
-      </c>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
+        <v>5038831</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16" s="29">
+        <v>10</v>
+      </c>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
       <c r="F16" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G16" s="12">
-        <v>0.4</v>
+        <v>0.18</v>
       </c>
       <c r="H16" s="11">
         <f>G16*D16</f>
@@ -1305,97 +1323,101 @@
     </row>
     <row r="17" spans="1:9" s="13" customFormat="1">
       <c r="A17" s="2">
-        <v>1018950</v>
+        <v>5039623</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="C17" s="10">
-        <v>10</v>
-      </c>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
+        <v>45</v>
+      </c>
+      <c r="C17" s="29">
+        <v>8</v>
+      </c>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17" t="s">
+        <v>77</v>
+      </c>
       <c r="F17" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G17" s="12">
-        <v>0.18</v>
+        <v>0.4</v>
       </c>
       <c r="H17" s="11">
-        <f t="shared" ref="H17:H25" si="1">G17*D17</f>
+        <f>G17*D17</f>
         <v>0</v>
       </c>
       <c r="I17" s="11"/>
     </row>
-    <row r="18" spans="1:9" s="13" customFormat="1">
-      <c r="A18" s="2">
-        <v>1018967</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="C18" s="10">
-        <v>10</v>
-      </c>
-      <c r="D18" s="20"/>
-      <c r="E18" s="20"/>
+    <row r="18" spans="1:9" s="13" customFormat="1" ht="38.25">
+      <c r="A18" s="15">
+        <v>8784931</v>
+      </c>
+      <c r="B18" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="C18" s="29">
+        <v>5</v>
+      </c>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
       <c r="F18" s="11">
-        <f t="shared" si="0"/>
+        <f>E18/16.4</f>
         <v>0</v>
       </c>
       <c r="G18" s="12">
-        <v>0.18</v>
+        <v>3.5</v>
       </c>
       <c r="H18" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I18" s="11"/>
+        <f>E18</f>
+        <v>0</v>
+      </c>
+      <c r="I18" s="11" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="19" spans="1:9" s="13" customFormat="1">
       <c r="A19" s="2">
-        <v>8444194</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>20</v>
+        <v>1018950</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>40</v>
       </c>
       <c r="C19" s="10">
-        <v>6</v>
-      </c>
-      <c r="D19" s="20"/>
-      <c r="E19" s="20"/>
+        <v>10</v>
+      </c>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
       <c r="F19" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G19" s="12">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="H19" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="H19:H27" si="1">G19*D19</f>
         <v>0</v>
       </c>
       <c r="I19" s="11"/>
     </row>
     <row r="20" spans="1:9" s="13" customFormat="1">
       <c r="A20" s="2">
-        <v>8444187</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>21</v>
+        <v>1018967</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>42</v>
       </c>
       <c r="C20" s="10">
-        <v>6</v>
-      </c>
-      <c r="D20" s="20"/>
-      <c r="E20" s="20"/>
+        <v>10</v>
+      </c>
+      <c r="D20" s="17"/>
+      <c r="E20" s="17"/>
       <c r="F20" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G20" s="12">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="H20" s="11">
         <f t="shared" si="1"/>
@@ -1405,16 +1427,16 @@
     </row>
     <row r="21" spans="1:9" s="13" customFormat="1">
       <c r="A21" s="2">
-        <v>8444163</v>
+        <v>8444194</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C21" s="10">
-        <v>8</v>
-      </c>
-      <c r="D21" s="20"/>
-      <c r="E21" s="20"/>
+        <v>6</v>
+      </c>
+      <c r="D21" s="17"/>
+      <c r="E21" s="17"/>
       <c r="F21" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1430,18 +1452,18 @@
     </row>
     <row r="22" spans="1:9" s="13" customFormat="1">
       <c r="A22" s="2">
-        <v>8444170</v>
+        <v>8444187</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="C22" s="10">
-        <v>8</v>
-      </c>
-      <c r="D22" s="20"/>
-      <c r="E22" s="20"/>
+        <v>6</v>
+      </c>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
       <c r="F22" s="11">
-        <f>D22/C22</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G22" s="12">
@@ -1455,22 +1477,22 @@
     </row>
     <row r="23" spans="1:9" s="13" customFormat="1">
       <c r="A23" s="2">
-        <v>9988377</v>
+        <v>8444163</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C23" s="10">
-        <v>16</v>
-      </c>
-      <c r="D23" s="20"/>
-      <c r="E23" s="20"/>
+        <v>8</v>
+      </c>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
       <c r="F23" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G23" s="12">
-        <v>0.14000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="H23" s="11">
         <f t="shared" si="1"/>
@@ -1480,22 +1502,22 @@
     </row>
     <row r="24" spans="1:9" s="13" customFormat="1">
       <c r="A24" s="2">
-        <v>9988391</v>
+        <v>8444170</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="C24" s="10">
-        <v>16</v>
-      </c>
-      <c r="D24" s="20"/>
-      <c r="E24" s="20"/>
+        <v>8</v>
+      </c>
+      <c r="D24" s="17"/>
+      <c r="E24" s="17"/>
       <c r="F24" s="11">
-        <f t="shared" si="0"/>
+        <f>D24/C24</f>
         <v>0</v>
       </c>
       <c r="G24" s="12">
-        <v>0.14000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="H24" s="11">
         <f t="shared" si="1"/>
@@ -1505,22 +1527,22 @@
     </row>
     <row r="25" spans="1:9" s="13" customFormat="1">
       <c r="A25" s="2">
-        <v>5034819</v>
+        <v>9988377</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C25" s="10">
-        <v>6</v>
-      </c>
-      <c r="D25" s="20"/>
-      <c r="E25" s="20"/>
+        <v>16</v>
+      </c>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17"/>
       <c r="F25" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G25" s="12">
-        <v>0.18</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="H25" s="11">
         <f t="shared" si="1"/>
@@ -1530,151 +1552,151 @@
     </row>
     <row r="26" spans="1:9" s="13" customFormat="1">
       <c r="A26" s="2">
-        <v>2981244</v>
+        <v>9988391</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C26" s="10">
-        <v>6</v>
-      </c>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
+        <v>16</v>
+      </c>
+      <c r="D26" s="17"/>
+      <c r="E26" s="17"/>
       <c r="F26" s="11">
-        <f>E26/7.8</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G26" s="12">
-        <v>1.3</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="H26" s="11">
-        <f>E26</f>
-        <v>0</v>
-      </c>
-      <c r="I26" s="11" t="s">
-        <v>19</v>
-      </c>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I26" s="11"/>
     </row>
     <row r="27" spans="1:9" s="13" customFormat="1">
       <c r="A27" s="2">
-        <v>8785198</v>
+        <v>5034819</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C27" s="10">
-        <v>5</v>
-      </c>
-      <c r="D27" s="20"/>
-      <c r="E27" s="20"/>
+        <v>6</v>
+      </c>
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
       <c r="F27" s="11">
-        <f>E27/16.5</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G27" s="12">
-        <v>3.2</v>
+        <v>0.18</v>
       </c>
       <c r="H27" s="11">
-        <f>E27</f>
-        <v>0</v>
-      </c>
-      <c r="I27" s="11" t="s">
-        <v>15</v>
-      </c>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I27" s="11"/>
     </row>
     <row r="28" spans="1:9" s="13" customFormat="1">
       <c r="A28" s="2">
-        <v>9988452</v>
+        <v>2981244</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C28" s="10">
-        <v>8</v>
-      </c>
-      <c r="D28" s="20"/>
-      <c r="E28" s="20"/>
+        <v>6</v>
+      </c>
+      <c r="D28" s="17"/>
+      <c r="E28" s="17"/>
       <c r="F28" s="11">
-        <f t="shared" ref="F28:F41" si="2">D28/C28</f>
+        <f>E28/7.8</f>
         <v>0</v>
       </c>
       <c r="G28" s="12">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="H28" s="11">
-        <f t="shared" ref="H28:H33" si="3">G28*D28</f>
-        <v>0</v>
-      </c>
-      <c r="I28" s="11"/>
+        <f>E28</f>
+        <v>0</v>
+      </c>
+      <c r="I28" s="11" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="29" spans="1:9" s="13" customFormat="1">
       <c r="A29" s="2">
-        <v>9988476</v>
+        <v>8785198</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C29" s="10">
-        <v>28</v>
-      </c>
-      <c r="D29" s="20"/>
-      <c r="E29" s="20"/>
+        <v>5</v>
+      </c>
+      <c r="D29" s="17"/>
+      <c r="E29" s="17"/>
       <c r="F29" s="11">
-        <f t="shared" si="2"/>
+        <f>E29/16.5</f>
         <v>0</v>
       </c>
       <c r="G29" s="12">
-        <v>0.4</v>
+        <v>3.2</v>
       </c>
       <c r="H29" s="11">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I29" s="11"/>
+        <f>E29</f>
+        <v>0</v>
+      </c>
+      <c r="I29" s="11" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="30" spans="1:9" s="13" customFormat="1">
       <c r="A30" s="2">
-        <v>9988681</v>
+        <v>9988452</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="C30" s="10">
-        <v>16</v>
-      </c>
-      <c r="D30" s="20"/>
-      <c r="E30" s="20"/>
+        <v>8</v>
+      </c>
+      <c r="D30" s="17"/>
+      <c r="E30" s="17"/>
       <c r="F30" s="11">
-        <f>D30/C30</f>
+        <f t="shared" ref="F30:F43" si="2">D30/C30</f>
         <v>0</v>
       </c>
       <c r="G30" s="12">
-        <v>0.18</v>
+        <v>0.4</v>
       </c>
       <c r="H30" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="H30:H35" si="3">G30*D30</f>
         <v>0</v>
       </c>
       <c r="I30" s="11"/>
     </row>
     <row r="31" spans="1:9" s="13" customFormat="1">
       <c r="A31" s="2">
-        <v>9988438</v>
+        <v>9988476</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C31" s="10">
-        <v>16</v>
-      </c>
-      <c r="D31" s="20"/>
-      <c r="E31" s="20"/>
+        <v>28</v>
+      </c>
+      <c r="D31" s="17"/>
+      <c r="E31" s="17"/>
       <c r="F31" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G31" s="12">
-        <v>0.18</v>
+        <v>0.4</v>
       </c>
       <c r="H31" s="11">
         <f t="shared" si="3"/>
@@ -1684,18 +1706,18 @@
     </row>
     <row r="32" spans="1:9" s="13" customFormat="1">
       <c r="A32" s="2">
-        <v>9988445</v>
+        <v>9988681</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C32" s="10">
         <v>16</v>
       </c>
-      <c r="D32" s="20"/>
-      <c r="E32" s="20"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17"/>
       <c r="F32" s="11">
-        <f t="shared" si="2"/>
+        <f>D32/C32</f>
         <v>0</v>
       </c>
       <c r="G32" s="12">
@@ -1709,22 +1731,22 @@
     </row>
     <row r="33" spans="1:9" s="13" customFormat="1">
       <c r="A33" s="2">
-        <v>9988421</v>
+        <v>9988438</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C33" s="10">
         <v>16</v>
       </c>
-      <c r="D33" s="20"/>
-      <c r="E33" s="20"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="17"/>
       <c r="F33" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G33" s="12">
-        <v>0.14000000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="H33" s="11">
         <f t="shared" si="3"/>
@@ -1734,16 +1756,16 @@
     </row>
     <row r="34" spans="1:9" s="13" customFormat="1">
       <c r="A34" s="2">
-        <v>9988674</v>
+        <v>9988445</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="C34" s="10">
         <v>16</v>
       </c>
-      <c r="D34" s="20"/>
-      <c r="E34" s="20"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="17"/>
       <c r="F34" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -1752,73 +1774,73 @@
         <v>0.18</v>
       </c>
       <c r="H34" s="11">
-        <f t="shared" ref="H34:H41" si="4">D34*G34</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I34" s="11"/>
     </row>
     <row r="35" spans="1:9" s="13" customFormat="1">
-      <c r="A35" s="33">
-        <v>8444903</v>
-      </c>
-      <c r="B35" s="34" t="s">
-        <v>49</v>
+      <c r="A35" s="2">
+        <v>9988421</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>32</v>
       </c>
       <c r="C35" s="10">
-        <v>8</v>
-      </c>
-      <c r="D35" s="20"/>
-      <c r="E35" s="20"/>
+        <v>16</v>
+      </c>
+      <c r="D35" s="17"/>
+      <c r="E35" s="17"/>
       <c r="F35" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G35" s="12">
-        <v>0.1</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="H35" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I35" s="11"/>
     </row>
     <row r="36" spans="1:9" s="13" customFormat="1">
-      <c r="A36" s="33">
-        <v>8444910</v>
-      </c>
-      <c r="B36" s="34" t="s">
-        <v>50</v>
+      <c r="A36" s="2">
+        <v>9988674</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="C36" s="10">
-        <v>8</v>
-      </c>
-      <c r="D36" s="20"/>
-      <c r="E36" s="20"/>
+        <v>16</v>
+      </c>
+      <c r="D36" s="17"/>
+      <c r="E36" s="17"/>
       <c r="F36" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G36" s="12">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="H36" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="H36:H43" si="4">D36*G36</f>
         <v>0</v>
       </c>
       <c r="I36" s="11"/>
     </row>
     <row r="37" spans="1:9" s="13" customFormat="1">
-      <c r="A37" s="33">
-        <v>8444927</v>
-      </c>
-      <c r="B37" s="34" t="s">
-        <v>51</v>
+      <c r="A37" s="30">
+        <v>8444903</v>
+      </c>
+      <c r="B37" s="31" t="s">
+        <v>49</v>
       </c>
       <c r="C37" s="10">
         <v>8</v>
       </c>
-      <c r="D37" s="20"/>
-      <c r="E37" s="20"/>
+      <c r="D37" s="17"/>
+      <c r="E37" s="17"/>
       <c r="F37" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -1833,17 +1855,17 @@
       <c r="I37" s="11"/>
     </row>
     <row r="38" spans="1:9" s="13" customFormat="1">
-      <c r="A38" s="18">
-        <v>8445160</v>
-      </c>
-      <c r="B38" s="19" t="s">
-        <v>71</v>
+      <c r="A38" s="30">
+        <v>8444910</v>
+      </c>
+      <c r="B38" s="31" t="s">
+        <v>50</v>
       </c>
       <c r="C38" s="10">
         <v>8</v>
       </c>
-      <c r="D38" s="20"/>
-      <c r="E38" s="20"/>
+      <c r="D38" s="17"/>
+      <c r="E38" s="17"/>
       <c r="F38" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -1852,23 +1874,23 @@
         <v>0.1</v>
       </c>
       <c r="H38" s="11">
-        <f>G38*D38</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I38" s="11"/>
     </row>
     <row r="39" spans="1:9" s="13" customFormat="1">
-      <c r="A39" s="18">
-        <v>8445177</v>
-      </c>
-      <c r="B39" s="19" t="s">
-        <v>72</v>
+      <c r="A39" s="30">
+        <v>8444927</v>
+      </c>
+      <c r="B39" s="31" t="s">
+        <v>51</v>
       </c>
       <c r="C39" s="10">
         <v>8</v>
       </c>
-      <c r="D39" s="20"/>
-      <c r="E39" s="20"/>
+      <c r="D39" s="17"/>
+      <c r="E39" s="17"/>
       <c r="F39" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -1877,125 +1899,127 @@
         <v>0.1</v>
       </c>
       <c r="H39" s="11">
-        <f>G39*D39</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I39" s="11"/>
     </row>
-    <row r="40" spans="1:9" s="39" customFormat="1">
-      <c r="A40" s="33">
+    <row r="40" spans="1:9" s="36" customFormat="1">
+      <c r="A40" s="15">
+        <v>8445160</v>
+      </c>
+      <c r="B40" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="C40" s="10">
+        <v>8</v>
+      </c>
+      <c r="D40" s="17"/>
+      <c r="E40" s="17"/>
+      <c r="F40" s="11">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G40" s="12">
+        <v>0.1</v>
+      </c>
+      <c r="H40" s="11">
+        <f>G40*D40</f>
+        <v>0</v>
+      </c>
+      <c r="I40" s="11"/>
+    </row>
+    <row r="41" spans="1:9" s="36" customFormat="1" ht="11.25" customHeight="1">
+      <c r="A41" s="15">
+        <v>8445177</v>
+      </c>
+      <c r="B41" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="C41" s="10">
+        <v>8</v>
+      </c>
+      <c r="D41" s="17"/>
+      <c r="E41" s="17"/>
+      <c r="F41" s="11">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G41" s="12">
+        <v>0.1</v>
+      </c>
+      <c r="H41" s="11">
+        <f>G41*D41</f>
+        <v>0</v>
+      </c>
+      <c r="I41" s="11"/>
+    </row>
+    <row r="42" spans="1:9" s="13" customFormat="1">
+      <c r="A42" s="30">
         <v>6600454</v>
       </c>
-      <c r="B40" s="34" t="s">
+      <c r="B42" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="C40" s="35">
+      <c r="C42" s="32">
         <v>12</v>
       </c>
-      <c r="D40" s="36"/>
-      <c r="E40" s="20"/>
-      <c r="F40" s="37">
+      <c r="D42" s="33"/>
+      <c r="E42" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="F42" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G40" s="38">
+      <c r="G42" s="35">
         <v>0.125</v>
       </c>
-      <c r="H40" s="37">
+      <c r="H42" s="34">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I40" s="37"/>
-    </row>
-    <row r="41" spans="1:9" s="39" customFormat="1" ht="11.25" customHeight="1">
-      <c r="A41" s="33">
+      <c r="I42" s="34"/>
+    </row>
+    <row r="43" spans="1:9" s="13" customFormat="1">
+      <c r="A43" s="30">
         <v>6600447</v>
       </c>
-      <c r="B41" s="34" t="s">
+      <c r="B43" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="C41" s="35">
+      <c r="C43" s="32">
         <v>12</v>
       </c>
-      <c r="D41" s="36"/>
-      <c r="E41" s="20"/>
-      <c r="F41" s="37">
+      <c r="D43" s="33"/>
+      <c r="E43" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="F43" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G41" s="38">
+      <c r="G43" s="35">
         <v>0.125</v>
       </c>
-      <c r="H41" s="37">
+      <c r="H43" s="34">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I41" s="37"/>
-    </row>
-    <row r="42" spans="1:9" s="13" customFormat="1">
-      <c r="A42" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B42" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="C42" s="10">
-        <v>10</v>
-      </c>
-      <c r="D42" s="20"/>
-      <c r="E42" s="20"/>
-      <c r="F42" s="11">
-        <f>D42/C42</f>
-        <v>0</v>
-      </c>
-      <c r="G42" s="12">
-        <v>0.2</v>
-      </c>
-      <c r="H42" s="11">
-        <f>G42*D42</f>
-        <v>0</v>
-      </c>
-      <c r="I42" s="11"/>
-    </row>
-    <row r="43" spans="1:9" s="13" customFormat="1">
-      <c r="A43" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B43" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C43" s="10">
-        <v>4</v>
-      </c>
-      <c r="D43" s="20"/>
-      <c r="E43" s="20"/>
-      <c r="F43" s="11">
-        <f>E43/15</f>
-        <v>0</v>
-      </c>
-      <c r="G43" s="12">
-        <v>3.5</v>
-      </c>
-      <c r="H43" s="11">
-        <f>E43</f>
-        <v>0</v>
-      </c>
-      <c r="I43" s="11" t="s">
-        <v>18</v>
-      </c>
+      <c r="I43" s="34"/>
     </row>
     <row r="44" spans="1:9" s="13" customFormat="1">
       <c r="A44" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C44" s="10">
         <v>10</v>
       </c>
-      <c r="D44" s="20"/>
-      <c r="E44" s="20"/>
+      <c r="D44" s="17"/>
+      <c r="E44" s="17"/>
       <c r="F44" s="11">
         <f>D44/C44</f>
         <v>0</v>
@@ -2011,16 +2035,16 @@
     </row>
     <row r="45" spans="1:9" s="13" customFormat="1">
       <c r="A45" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C45" s="10">
         <v>4</v>
       </c>
-      <c r="D45" s="20"/>
-      <c r="E45" s="20"/>
+      <c r="D45" s="17"/>
+      <c r="E45" s="17"/>
       <c r="F45" s="11">
         <f>E45/15</f>
         <v>0</v>
@@ -2037,17 +2061,17 @@
       </c>
     </row>
     <row r="46" spans="1:9" s="13" customFormat="1">
-      <c r="A46" s="2">
-        <v>7100108</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>73</v>
+      <c r="A46" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B46" s="12" t="s">
+        <v>14</v>
       </c>
       <c r="C46" s="10">
-        <v>12</v>
-      </c>
-      <c r="D46" s="20"/>
-      <c r="E46" s="20"/>
+        <v>10</v>
+      </c>
+      <c r="D46" s="17"/>
+      <c r="E46" s="17"/>
       <c r="F46" s="11">
         <f>D46/C46</f>
         <v>0</v>
@@ -2056,50 +2080,50 @@
         <v>0.2</v>
       </c>
       <c r="H46" s="11">
-        <f>D46*G46</f>
+        <f>G46*D46</f>
         <v>0</v>
       </c>
       <c r="I46" s="11"/>
     </row>
     <row r="47" spans="1:9" s="13" customFormat="1">
-      <c r="A47" s="2">
-        <v>7100139</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>74</v>
+      <c r="A47" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B47" s="12" t="s">
+        <v>17</v>
       </c>
       <c r="C47" s="10">
-        <v>8</v>
-      </c>
-      <c r="D47" s="20"/>
-      <c r="E47" s="20"/>
+        <v>4</v>
+      </c>
+      <c r="D47" s="17"/>
+      <c r="E47" s="17"/>
       <c r="F47" s="11">
-        <f>E47/20</f>
+        <f>E47/15</f>
         <v>0</v>
       </c>
       <c r="G47" s="12">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="H47" s="11">
         <f>E47</f>
         <v>0</v>
       </c>
       <c r="I47" s="11" t="s">
-        <v>75</v>
+        <v>18</v>
       </c>
     </row>
     <row r="48" spans="1:9" s="13" customFormat="1">
       <c r="A48" s="2">
-        <v>7100740</v>
+        <v>7100108</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C48" s="10">
         <v>12</v>
       </c>
-      <c r="D48" s="20"/>
-      <c r="E48" s="20"/>
+      <c r="D48" s="17"/>
+      <c r="E48" s="17"/>
       <c r="F48" s="11">
         <f>D48/C48</f>
         <v>0</v>
@@ -2115,16 +2139,16 @@
     </row>
     <row r="49" spans="1:9" s="13" customFormat="1">
       <c r="A49" s="2">
-        <v>7100726</v>
+        <v>7100139</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C49" s="10">
         <v>8</v>
       </c>
-      <c r="D49" s="20"/>
-      <c r="E49" s="20"/>
+      <c r="D49" s="17"/>
+      <c r="E49" s="17"/>
       <c r="F49" s="11">
         <f>E49/20</f>
         <v>0</v>
@@ -2137,77 +2161,79 @@
         <v>0</v>
       </c>
       <c r="I49" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="50" spans="1:9" s="13" customFormat="1">
       <c r="A50" s="2">
-        <v>4421584</v>
+        <v>7100740</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="C50" s="10">
         <v>12</v>
       </c>
-      <c r="D50" s="20"/>
-      <c r="E50" s="20"/>
+      <c r="D50" s="17"/>
+      <c r="E50" s="17"/>
       <c r="F50" s="11">
         <f>D50/C50</f>
         <v>0</v>
       </c>
       <c r="G50" s="12">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="H50" s="11">
-        <f>G50*D50</f>
+        <f>D50*G50</f>
         <v>0</v>
       </c>
       <c r="I50" s="11"/>
     </row>
     <row r="51" spans="1:9" s="13" customFormat="1">
       <c r="A51" s="2">
-        <v>4421577</v>
+        <v>7100726</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="C51" s="10">
-        <v>12</v>
-      </c>
-      <c r="D51" s="20"/>
-      <c r="E51" s="20"/>
+        <v>8</v>
+      </c>
+      <c r="D51" s="17"/>
+      <c r="E51" s="17"/>
       <c r="F51" s="11">
-        <f>D51/C51</f>
+        <f>E51/20</f>
         <v>0</v>
       </c>
       <c r="G51" s="12">
-        <v>0.18</v>
+        <v>2.5</v>
       </c>
       <c r="H51" s="11">
-        <f>G51*D51</f>
-        <v>0</v>
-      </c>
-      <c r="I51" s="11"/>
+        <f>E51</f>
+        <v>0</v>
+      </c>
+      <c r="I51" s="11" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="52" spans="1:9" s="13" customFormat="1">
       <c r="A52" s="2">
-        <v>9985949</v>
+        <v>4421584</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C52" s="10">
-        <v>10</v>
-      </c>
-      <c r="D52" s="20"/>
-      <c r="E52" s="20"/>
+        <v>12</v>
+      </c>
+      <c r="D52" s="17"/>
+      <c r="E52" s="17"/>
       <c r="F52" s="11">
         <f>D52/C52</f>
         <v>0</v>
       </c>
-      <c r="G52" s="21">
-        <v>1</v>
+      <c r="G52" s="12">
+        <v>0.18</v>
       </c>
       <c r="H52" s="11">
         <f>G52*D52</f>
@@ -2217,49 +2243,47 @@
     </row>
     <row r="53" spans="1:9" s="13" customFormat="1">
       <c r="A53" s="2">
-        <v>8786928</v>
+        <v>4421577</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C53" s="10">
-        <v>4</v>
-      </c>
-      <c r="D53" s="20"/>
-      <c r="E53" s="20"/>
+        <v>12</v>
+      </c>
+      <c r="D53" s="17"/>
+      <c r="E53" s="17"/>
       <c r="F53" s="11">
-        <f>E53/6</f>
+        <f>D53/C53</f>
         <v>0</v>
       </c>
       <c r="G53" s="12">
-        <v>1.5</v>
+        <v>0.18</v>
       </c>
       <c r="H53" s="11">
-        <f>E53</f>
-        <v>0</v>
-      </c>
-      <c r="I53" s="11" t="s">
-        <v>64</v>
-      </c>
+        <f>G53*D53</f>
+        <v>0</v>
+      </c>
+      <c r="I53" s="11"/>
     </row>
     <row r="54" spans="1:9" s="13" customFormat="1">
       <c r="A54" s="2">
-        <v>6948270</v>
+        <v>9985949</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C54" s="10">
-        <v>12</v>
-      </c>
-      <c r="D54" s="20"/>
-      <c r="E54" s="20"/>
+        <v>10</v>
+      </c>
+      <c r="D54" s="17"/>
+      <c r="E54" s="17"/>
       <c r="F54" s="11">
         <f>D54/C54</f>
         <v>0</v>
       </c>
-      <c r="G54" s="12">
-        <v>0.372</v>
+      <c r="G54" s="18">
+        <v>1</v>
       </c>
       <c r="H54" s="11">
         <f>G54*D54</f>
@@ -2269,41 +2293,43 @@
     </row>
     <row r="55" spans="1:9" s="13" customFormat="1">
       <c r="A55" s="2">
-        <v>6948287</v>
+        <v>8786928</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C55" s="10">
-        <v>12</v>
-      </c>
-      <c r="D55" s="20"/>
-      <c r="E55" s="20"/>
+        <v>4</v>
+      </c>
+      <c r="D55" s="17"/>
+      <c r="E55" s="17"/>
       <c r="F55" s="11">
-        <f>D55/C55</f>
+        <f>E55/6</f>
         <v>0</v>
       </c>
       <c r="G55" s="12">
-        <v>0.74399999999999999</v>
+        <v>1.5</v>
       </c>
       <c r="H55" s="11">
-        <f>G55*D55</f>
-        <v>0</v>
-      </c>
-      <c r="I55" s="11"/>
+        <f>E55</f>
+        <v>0</v>
+      </c>
+      <c r="I55" s="11" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="56" spans="1:9" s="13" customFormat="1">
       <c r="A56" s="2">
-        <v>6948256</v>
+        <v>6948270</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C56" s="10">
         <v>12</v>
       </c>
-      <c r="D56" s="20"/>
-      <c r="E56" s="20"/>
+      <c r="D56" s="17"/>
+      <c r="E56" s="17"/>
       <c r="F56" s="11">
         <f>D56/C56</f>
         <v>0</v>
@@ -2319,16 +2345,16 @@
     </row>
     <row r="57" spans="1:9" s="13" customFormat="1">
       <c r="A57" s="2">
-        <v>6948263</v>
+        <v>6948287</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C57" s="10">
         <v>12</v>
       </c>
-      <c r="D57" s="20"/>
-      <c r="E57" s="20"/>
+      <c r="D57" s="17"/>
+      <c r="E57" s="17"/>
       <c r="F57" s="11">
         <f>D57/C57</f>
         <v>0</v>
@@ -2344,22 +2370,22 @@
     </row>
     <row r="58" spans="1:9" s="13" customFormat="1">
       <c r="A58" s="2">
-        <v>6948249</v>
+        <v>6948256</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C58" s="10">
         <v>12</v>
       </c>
-      <c r="D58" s="20"/>
-      <c r="E58" s="20"/>
+      <c r="D58" s="17"/>
+      <c r="E58" s="17"/>
       <c r="F58" s="11">
         <f>D58/C58</f>
         <v>0</v>
       </c>
       <c r="G58" s="12">
-        <v>0.82499999999999996</v>
+        <v>0.372</v>
       </c>
       <c r="H58" s="11">
         <f>G58*D58</f>
@@ -2368,20 +2394,70 @@
       <c r="I58" s="11"/>
     </row>
     <row r="59" spans="1:9" s="13" customFormat="1">
-      <c r="A59" s="11"/>
-      <c r="B59" s="12" t="s">
+      <c r="A59" s="2">
+        <v>6948263</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C59" s="10">
+        <v>12</v>
+      </c>
+      <c r="D59" s="17"/>
+      <c r="E59" s="17"/>
+      <c r="F59" s="11">
+        <f>D59/C59</f>
+        <v>0</v>
+      </c>
+      <c r="G59" s="12">
+        <v>0.74399999999999999</v>
+      </c>
+      <c r="H59" s="11">
+        <f>G59*D59</f>
+        <v>0</v>
+      </c>
+      <c r="I59" s="11"/>
+    </row>
+    <row r="60" spans="1:9">
+      <c r="A60" s="2">
+        <v>6948249</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C60" s="10">
+        <v>12</v>
+      </c>
+      <c r="D60" s="17"/>
+      <c r="E60" s="17"/>
+      <c r="F60" s="11">
+        <f>D60/C60</f>
+        <v>0</v>
+      </c>
+      <c r="G60" s="12">
+        <v>0.82499999999999996</v>
+      </c>
+      <c r="H60" s="11">
+        <f>G60*D60</f>
+        <v>0</v>
+      </c>
+      <c r="I60" s="11"/>
+    </row>
+    <row r="61" spans="1:9">
+      <c r="A61" s="11"/>
+      <c r="B61" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C59" s="11"/>
-      <c r="D59" s="20"/>
-      <c r="E59" s="20"/>
-      <c r="F59" s="11"/>
-      <c r="G59" s="11"/>
-      <c r="H59" s="3">
-        <f>SUM(H4:H58)</f>
-        <v>0</v>
-      </c>
-      <c r="I59" s="11"/>
+      <c r="C61" s="11"/>
+      <c r="D61" s="17"/>
+      <c r="E61" s="17"/>
+      <c r="F61" s="11"/>
+      <c r="G61" s="11"/>
+      <c r="H61" s="3">
+        <f>SUM(H4:H60)</f>
+        <v>0</v>
+      </c>
+      <c r="I61" s="11"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
@@ -2397,7 +2473,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I59"/>
+  <dimension ref="A1:I61"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="10" style="4" customWidth="1"/>
@@ -2443,31 +2519,31 @@
       <c r="I2" s="7"/>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="15" t="s">
+      <c r="A3" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="D3" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="16" t="s">
+      <c r="E3" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="15" t="s">
+      <c r="F3" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="17" t="s">
+      <c r="G3" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="11" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2475,14 +2551,14 @@
       <c r="A4" s="1">
         <v>5038435</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="19" t="s">
         <v>35</v>
       </c>
       <c r="C4" s="10">
         <v>10</v>
       </c>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
       <c r="F4" s="11">
         <f>D4/C4</f>
         <v>0</v>
@@ -2506,8 +2582,10 @@
       <c r="C5" s="10">
         <v>5</v>
       </c>
-      <c r="D5" s="20"/>
-      <c r="E5" s="20"/>
+      <c r="D5" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="E5" s="17"/>
       <c r="F5" s="11">
         <f>E5/16.5</f>
         <v>0</v>
@@ -2521,43 +2599,43 @@
       </c>
       <c r="I5" s="11"/>
     </row>
-    <row r="6" spans="1:9" s="29" customFormat="1" ht="25.5">
-      <c r="A6" s="23">
+    <row r="6" spans="1:9" s="26" customFormat="1" ht="25.5">
+      <c r="A6" s="20">
         <v>8783323</v>
       </c>
-      <c r="B6" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="C6" s="25">
-        <v>8</v>
-      </c>
-      <c r="D6" s="26"/>
-      <c r="E6" s="20"/>
-      <c r="F6" s="27">
-        <f>E5/15</f>
-        <v>0</v>
-      </c>
-      <c r="G6" s="28">
+      <c r="B6" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="C6" s="22">
+        <v>4</v>
+      </c>
+      <c r="D6" s="23"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="11">
+        <f>E6/5</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="25">
         <v>1.8</v>
       </c>
-      <c r="H6" s="27">
+      <c r="H6" s="24">
         <f>E6</f>
         <v>0</v>
       </c>
-      <c r="I6" s="27"/>
+      <c r="I6" s="24"/>
     </row>
     <row r="7" spans="1:9" s="13" customFormat="1" ht="25.5">
       <c r="A7" s="1">
         <v>5038459</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="19" t="s">
         <v>33</v>
       </c>
       <c r="C7" s="10">
         <v>10</v>
       </c>
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
       <c r="F7" s="11">
         <f>D7/C7</f>
         <v>0</v>
@@ -2572,100 +2650,102 @@
       <c r="I7" s="11"/>
     </row>
     <row r="8" spans="1:9" s="13" customFormat="1" ht="25.5">
-      <c r="A8" s="1">
+      <c r="A8" s="20">
+        <v>8785235</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="C8" s="10">
+        <v>5</v>
+      </c>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="11">
+        <f>E8/16.5</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="11">
+        <v>3.5</v>
+      </c>
+      <c r="H8" s="11">
+        <f>E8</f>
+        <v>0</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" s="13" customFormat="1" ht="25.5">
+      <c r="A9" s="1">
         <v>5038411</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B9" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C9" s="10">
         <v>10</v>
       </c>
-      <c r="D8" s="20"/>
-      <c r="E8" s="20"/>
-      <c r="F8" s="11">
-        <f>D8/C8</f>
-        <v>0</v>
-      </c>
-      <c r="G8" s="12">
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="11">
+        <f>D9/C9</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="12">
         <v>0.18</v>
       </c>
-      <c r="H8" s="11">
-        <f>G8*D8</f>
-        <v>0</v>
-      </c>
-      <c r="I8" s="11"/>
-    </row>
-    <row r="9" spans="1:9" s="13" customFormat="1" ht="25.5">
-      <c r="A9" s="2">
+      <c r="H9" s="11">
+        <f>G9*D9</f>
+        <v>0</v>
+      </c>
+      <c r="I9" s="11"/>
+    </row>
+    <row r="10" spans="1:9" s="13" customFormat="1" ht="25.5">
+      <c r="A10" s="2">
         <v>8785242</v>
       </c>
-      <c r="B9" s="22" t="s">
+      <c r="B10" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C10" s="10">
         <v>5</v>
       </c>
-      <c r="D9" s="20"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="11">
-        <f>E9/16.5</f>
-        <v>0</v>
-      </c>
-      <c r="G9" s="11">
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="11">
+        <f>E10/16.5</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="11">
         <v>3.5</v>
       </c>
-      <c r="H9" s="11">
-        <f>E9</f>
-        <v>0</v>
-      </c>
-      <c r="I9" s="11" t="s">
+      <c r="H10" s="11">
+        <f>E10</f>
+        <v>0</v>
+      </c>
+      <c r="I10" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:9" s="13" customFormat="1" ht="25.5">
-      <c r="A10" s="1">
+    <row r="11" spans="1:9" s="13" customFormat="1" ht="25.5">
+      <c r="A11" s="1">
         <v>5038398</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B11" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="10">
+      <c r="C11" s="10">
         <v>10</v>
       </c>
-      <c r="D10" s="20"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="11">
-        <f>D10/C10</f>
-        <v>0</v>
-      </c>
-      <c r="G10" s="12">
-        <v>0.18</v>
-      </c>
-      <c r="H10" s="11">
-        <f>G10*D10</f>
-        <v>0</v>
-      </c>
-      <c r="I10" s="11"/>
-    </row>
-    <row r="11" spans="1:9" s="13" customFormat="1">
-      <c r="A11" s="1">
-        <v>5039609</v>
-      </c>
-      <c r="B11" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="C11" s="10">
-        <v>8</v>
-      </c>
-      <c r="D11" s="20"/>
-      <c r="E11" s="20"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
       <c r="F11" s="11">
         <f>D11/C11</f>
         <v>0</v>
       </c>
       <c r="G11" s="12">
-        <v>0.4</v>
+        <v>0.18</v>
       </c>
       <c r="H11" s="11">
         <f>G11*D11</f>
@@ -2673,74 +2753,76 @@
       </c>
       <c r="I11" s="11"/>
     </row>
-    <row r="12" spans="1:9" s="13" customFormat="1" ht="25.5">
-      <c r="A12" s="2">
-        <v>8785259</v>
-      </c>
-      <c r="B12" s="22" t="s">
-        <v>52</v>
+    <row r="12" spans="1:9" s="13" customFormat="1">
+      <c r="A12" s="1">
+        <v>5039609</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>43</v>
       </c>
       <c r="C12" s="10">
-        <v>5</v>
-      </c>
-      <c r="D12" s="20"/>
-      <c r="E12" s="20"/>
+        <v>8</v>
+      </c>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17" t="s">
+        <v>77</v>
+      </c>
       <c r="F12" s="11">
-        <f>E12/16.5</f>
-        <v>0</v>
-      </c>
-      <c r="G12" s="11">
-        <v>3.5</v>
+        <f>D12/C12</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="12">
+        <v>0.4</v>
       </c>
       <c r="H12" s="11">
-        <f>E12</f>
+        <f>G12*D12</f>
         <v>0</v>
       </c>
       <c r="I12" s="11"/>
     </row>
     <row r="13" spans="1:9" s="13" customFormat="1" ht="25.5">
       <c r="A13" s="2">
+        <v>8785259</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" s="10">
+        <v>5</v>
+      </c>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="11">
+        <f>E13/16.5</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="11">
+        <v>3.5</v>
+      </c>
+      <c r="H13" s="11">
+        <f>E13</f>
+        <v>0</v>
+      </c>
+      <c r="I13" s="11"/>
+    </row>
+    <row r="14" spans="1:9" s="13" customFormat="1" ht="25.5">
+      <c r="A14" s="2">
         <v>5038855</v>
       </c>
-      <c r="B13" s="30" t="s">
+      <c r="B14" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="C13" s="10">
+      <c r="C14" s="10">
         <v>10</v>
       </c>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="11">
-        <f t="shared" ref="F13:F25" si="0">D13/C13</f>
-        <v>0</v>
-      </c>
-      <c r="G13" s="12">
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="11">
+        <f t="shared" ref="F14:F27" si="0">D14/C14</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="12">
         <v>0.2</v>
-      </c>
-      <c r="H13" s="11">
-        <f>G13*D13</f>
-        <v>0</v>
-      </c>
-      <c r="I13" s="11"/>
-    </row>
-    <row r="14" spans="1:9" s="13" customFormat="1">
-      <c r="A14" s="2">
-        <v>5039647</v>
-      </c>
-      <c r="B14" s="31" t="s">
-        <v>44</v>
-      </c>
-      <c r="C14" s="10">
-        <v>8</v>
-      </c>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G14" s="12">
-        <v>0.4</v>
       </c>
       <c r="H14" s="11">
         <f>G14*D14</f>
@@ -2748,24 +2830,24 @@
       </c>
       <c r="I14" s="11"/>
     </row>
-    <row r="15" spans="1:9" s="13" customFormat="1" ht="25.5">
+    <row r="15" spans="1:9" s="13" customFormat="1">
       <c r="A15" s="2">
-        <v>5038831</v>
-      </c>
-      <c r="B15" s="22" t="s">
-        <v>39</v>
-      </c>
-      <c r="C15" s="32">
-        <v>10</v>
-      </c>
-      <c r="D15" s="20"/>
-      <c r="E15" s="20"/>
+        <v>5039647</v>
+      </c>
+      <c r="B15" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="10">
+        <v>8</v>
+      </c>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
       <c r="F15" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G15" s="12">
-        <v>0.18</v>
+        <v>0.4</v>
       </c>
       <c r="H15" s="11">
         <f>G15*D15</f>
@@ -2773,24 +2855,24 @@
       </c>
       <c r="I15" s="11"/>
     </row>
-    <row r="16" spans="1:9" s="13" customFormat="1">
+    <row r="16" spans="1:9" s="13" customFormat="1" ht="25.5">
       <c r="A16" s="2">
-        <v>5039623</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="C16" s="32">
-        <v>8</v>
-      </c>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
+        <v>5038831</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16" s="29">
+        <v>10</v>
+      </c>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
       <c r="F16" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G16" s="12">
-        <v>0.4</v>
+        <v>0.18</v>
       </c>
       <c r="H16" s="11">
         <f>G16*D16</f>
@@ -2800,97 +2882,101 @@
     </row>
     <row r="17" spans="1:9" s="13" customFormat="1">
       <c r="A17" s="2">
-        <v>1018950</v>
+        <v>5039623</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="C17" s="10">
-        <v>10</v>
-      </c>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
+        <v>45</v>
+      </c>
+      <c r="C17" s="29">
+        <v>8</v>
+      </c>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17" t="s">
+        <v>77</v>
+      </c>
       <c r="F17" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G17" s="12">
-        <v>0.18</v>
+        <v>0.4</v>
       </c>
       <c r="H17" s="11">
-        <f t="shared" ref="H17:H25" si="1">G17*D17</f>
+        <f>G17*D17</f>
         <v>0</v>
       </c>
       <c r="I17" s="11"/>
     </row>
-    <row r="18" spans="1:9" s="13" customFormat="1">
-      <c r="A18" s="2">
-        <v>1018967</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="C18" s="10">
-        <v>10</v>
-      </c>
-      <c r="D18" s="20"/>
-      <c r="E18" s="20"/>
+    <row r="18" spans="1:9" s="13" customFormat="1" ht="38.25">
+      <c r="A18" s="15">
+        <v>8784931</v>
+      </c>
+      <c r="B18" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="C18" s="29">
+        <v>5</v>
+      </c>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
       <c r="F18" s="11">
-        <f t="shared" si="0"/>
+        <f>E18/16.4</f>
         <v>0</v>
       </c>
       <c r="G18" s="12">
-        <v>0.18</v>
+        <v>3.5</v>
       </c>
       <c r="H18" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I18" s="11"/>
+        <f>E18</f>
+        <v>0</v>
+      </c>
+      <c r="I18" s="11" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="19" spans="1:9" s="13" customFormat="1">
       <c r="A19" s="2">
-        <v>8444194</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>20</v>
+        <v>1018950</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>40</v>
       </c>
       <c r="C19" s="10">
-        <v>6</v>
-      </c>
-      <c r="D19" s="20"/>
-      <c r="E19" s="20"/>
+        <v>10</v>
+      </c>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
       <c r="F19" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G19" s="12">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="H19" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="H19:H27" si="1">G19*D19</f>
         <v>0</v>
       </c>
       <c r="I19" s="11"/>
     </row>
     <row r="20" spans="1:9" s="13" customFormat="1">
       <c r="A20" s="2">
-        <v>8444187</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>21</v>
+        <v>1018967</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>42</v>
       </c>
       <c r="C20" s="10">
-        <v>6</v>
-      </c>
-      <c r="D20" s="20"/>
-      <c r="E20" s="20"/>
+        <v>10</v>
+      </c>
+      <c r="D20" s="17"/>
+      <c r="E20" s="17"/>
       <c r="F20" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G20" s="12">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="H20" s="11">
         <f t="shared" si="1"/>
@@ -2900,16 +2986,16 @@
     </row>
     <row r="21" spans="1:9" s="13" customFormat="1">
       <c r="A21" s="2">
-        <v>8444163</v>
+        <v>8444194</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C21" s="10">
-        <v>8</v>
-      </c>
-      <c r="D21" s="20"/>
-      <c r="E21" s="20"/>
+        <v>6</v>
+      </c>
+      <c r="D21" s="17"/>
+      <c r="E21" s="17"/>
       <c r="F21" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2925,18 +3011,18 @@
     </row>
     <row r="22" spans="1:9" s="13" customFormat="1">
       <c r="A22" s="2">
-        <v>8444170</v>
+        <v>8444187</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="C22" s="10">
-        <v>8</v>
-      </c>
-      <c r="D22" s="20"/>
-      <c r="E22" s="20"/>
+        <v>6</v>
+      </c>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
       <c r="F22" s="11">
-        <f>D22/C22</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G22" s="12">
@@ -2950,22 +3036,22 @@
     </row>
     <row r="23" spans="1:9" s="13" customFormat="1">
       <c r="A23" s="2">
-        <v>9988377</v>
+        <v>8444163</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C23" s="10">
-        <v>16</v>
-      </c>
-      <c r="D23" s="20"/>
-      <c r="E23" s="20"/>
+        <v>8</v>
+      </c>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
       <c r="F23" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G23" s="12">
-        <v>0.14000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="H23" s="11">
         <f t="shared" si="1"/>
@@ -2975,22 +3061,22 @@
     </row>
     <row r="24" spans="1:9" s="13" customFormat="1">
       <c r="A24" s="2">
-        <v>9988391</v>
+        <v>8444170</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="C24" s="10">
-        <v>16</v>
-      </c>
-      <c r="D24" s="20"/>
-      <c r="E24" s="20"/>
+        <v>8</v>
+      </c>
+      <c r="D24" s="17"/>
+      <c r="E24" s="17"/>
       <c r="F24" s="11">
-        <f t="shared" si="0"/>
+        <f>D24/C24</f>
         <v>0</v>
       </c>
       <c r="G24" s="12">
-        <v>0.14000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="H24" s="11">
         <f t="shared" si="1"/>
@@ -3000,22 +3086,22 @@
     </row>
     <row r="25" spans="1:9" s="13" customFormat="1">
       <c r="A25" s="2">
-        <v>5034819</v>
+        <v>9988377</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C25" s="10">
-        <v>6</v>
-      </c>
-      <c r="D25" s="20"/>
-      <c r="E25" s="20"/>
+        <v>16</v>
+      </c>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17"/>
       <c r="F25" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G25" s="12">
-        <v>0.18</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="H25" s="11">
         <f t="shared" si="1"/>
@@ -3025,151 +3111,151 @@
     </row>
     <row r="26" spans="1:9" s="13" customFormat="1">
       <c r="A26" s="2">
-        <v>2981244</v>
+        <v>9988391</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C26" s="10">
-        <v>6</v>
-      </c>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
+        <v>16</v>
+      </c>
+      <c r="D26" s="17"/>
+      <c r="E26" s="17"/>
       <c r="F26" s="11">
-        <f>E26/7.8</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G26" s="12">
-        <v>1.3</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="H26" s="11">
-        <f>E26</f>
-        <v>0</v>
-      </c>
-      <c r="I26" s="11" t="s">
-        <v>19</v>
-      </c>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I26" s="11"/>
     </row>
     <row r="27" spans="1:9" s="13" customFormat="1">
       <c r="A27" s="2">
-        <v>8785198</v>
+        <v>5034819</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C27" s="10">
-        <v>5</v>
-      </c>
-      <c r="D27" s="20"/>
-      <c r="E27" s="20"/>
+        <v>6</v>
+      </c>
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
       <c r="F27" s="11">
-        <f>E27/16.5</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G27" s="12">
-        <v>3.2</v>
+        <v>0.18</v>
       </c>
       <c r="H27" s="11">
-        <f>E27</f>
-        <v>0</v>
-      </c>
-      <c r="I27" s="11" t="s">
-        <v>15</v>
-      </c>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I27" s="11"/>
     </row>
     <row r="28" spans="1:9" s="13" customFormat="1">
       <c r="A28" s="2">
-        <v>9988452</v>
+        <v>2981244</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C28" s="10">
-        <v>8</v>
-      </c>
-      <c r="D28" s="20"/>
-      <c r="E28" s="20"/>
+        <v>6</v>
+      </c>
+      <c r="D28" s="17"/>
+      <c r="E28" s="17"/>
       <c r="F28" s="11">
-        <f t="shared" ref="F28:F41" si="2">D28/C28</f>
+        <f>E28/7.8</f>
         <v>0</v>
       </c>
       <c r="G28" s="12">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="H28" s="11">
-        <f t="shared" ref="H28:H33" si="3">G28*D28</f>
-        <v>0</v>
-      </c>
-      <c r="I28" s="11"/>
+        <f>E28</f>
+        <v>0</v>
+      </c>
+      <c r="I28" s="11" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="29" spans="1:9" s="13" customFormat="1">
       <c r="A29" s="2">
-        <v>9988476</v>
+        <v>8785198</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C29" s="10">
-        <v>28</v>
-      </c>
-      <c r="D29" s="20"/>
-      <c r="E29" s="20"/>
+        <v>5</v>
+      </c>
+      <c r="D29" s="17"/>
+      <c r="E29" s="17"/>
       <c r="F29" s="11">
-        <f t="shared" si="2"/>
+        <f>E29/16.5</f>
         <v>0</v>
       </c>
       <c r="G29" s="12">
-        <v>0.4</v>
+        <v>3.2</v>
       </c>
       <c r="H29" s="11">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I29" s="11"/>
+        <f>E29</f>
+        <v>0</v>
+      </c>
+      <c r="I29" s="11" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="30" spans="1:9" s="13" customFormat="1">
       <c r="A30" s="2">
-        <v>9988681</v>
+        <v>9988452</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="C30" s="10">
-        <v>16</v>
-      </c>
-      <c r="D30" s="20"/>
-      <c r="E30" s="20"/>
+        <v>8</v>
+      </c>
+      <c r="D30" s="17"/>
+      <c r="E30" s="17"/>
       <c r="F30" s="11">
-        <f>D30/C30</f>
+        <f t="shared" ref="F30:F43" si="2">D30/C30</f>
         <v>0</v>
       </c>
       <c r="G30" s="12">
-        <v>0.18</v>
+        <v>0.4</v>
       </c>
       <c r="H30" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="H30:H35" si="3">G30*D30</f>
         <v>0</v>
       </c>
       <c r="I30" s="11"/>
     </row>
     <row r="31" spans="1:9" s="13" customFormat="1">
       <c r="A31" s="2">
-        <v>9988438</v>
+        <v>9988476</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C31" s="10">
-        <v>16</v>
-      </c>
-      <c r="D31" s="20"/>
-      <c r="E31" s="20"/>
+        <v>28</v>
+      </c>
+      <c r="D31" s="17"/>
+      <c r="E31" s="17"/>
       <c r="F31" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G31" s="12">
-        <v>0.18</v>
+        <v>0.4</v>
       </c>
       <c r="H31" s="11">
         <f t="shared" si="3"/>
@@ -3179,18 +3265,18 @@
     </row>
     <row r="32" spans="1:9" s="13" customFormat="1">
       <c r="A32" s="2">
-        <v>9988445</v>
+        <v>9988681</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C32" s="10">
         <v>16</v>
       </c>
-      <c r="D32" s="20"/>
-      <c r="E32" s="20"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17"/>
       <c r="F32" s="11">
-        <f t="shared" si="2"/>
+        <f>D32/C32</f>
         <v>0</v>
       </c>
       <c r="G32" s="12">
@@ -3204,22 +3290,22 @@
     </row>
     <row r="33" spans="1:9" s="13" customFormat="1">
       <c r="A33" s="2">
-        <v>9988421</v>
+        <v>9988438</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C33" s="10">
         <v>16</v>
       </c>
-      <c r="D33" s="20"/>
-      <c r="E33" s="20"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="17"/>
       <c r="F33" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G33" s="12">
-        <v>0.14000000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="H33" s="11">
         <f t="shared" si="3"/>
@@ -3229,16 +3315,16 @@
     </row>
     <row r="34" spans="1:9" s="13" customFormat="1">
       <c r="A34" s="2">
-        <v>9988674</v>
+        <v>9988445</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="C34" s="10">
         <v>16</v>
       </c>
-      <c r="D34" s="20"/>
-      <c r="E34" s="20"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="17"/>
       <c r="F34" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -3247,73 +3333,73 @@
         <v>0.18</v>
       </c>
       <c r="H34" s="11">
-        <f t="shared" ref="H34:H41" si="4">D34*G34</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I34" s="11"/>
     </row>
     <row r="35" spans="1:9" s="13" customFormat="1">
-      <c r="A35" s="33">
-        <v>8444903</v>
-      </c>
-      <c r="B35" s="34" t="s">
-        <v>49</v>
+      <c r="A35" s="2">
+        <v>9988421</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>32</v>
       </c>
       <c r="C35" s="10">
-        <v>8</v>
-      </c>
-      <c r="D35" s="20"/>
-      <c r="E35" s="20"/>
+        <v>16</v>
+      </c>
+      <c r="D35" s="17"/>
+      <c r="E35" s="17"/>
       <c r="F35" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G35" s="12">
-        <v>0.1</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="H35" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I35" s="11"/>
     </row>
     <row r="36" spans="1:9" s="13" customFormat="1">
-      <c r="A36" s="33">
-        <v>8444910</v>
-      </c>
-      <c r="B36" s="34" t="s">
-        <v>50</v>
+      <c r="A36" s="2">
+        <v>9988674</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="C36" s="10">
-        <v>8</v>
-      </c>
-      <c r="D36" s="20"/>
-      <c r="E36" s="20"/>
+        <v>16</v>
+      </c>
+      <c r="D36" s="17"/>
+      <c r="E36" s="17"/>
       <c r="F36" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G36" s="12">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="H36" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="H36:H43" si="4">D36*G36</f>
         <v>0</v>
       </c>
       <c r="I36" s="11"/>
     </row>
     <row r="37" spans="1:9" s="13" customFormat="1">
-      <c r="A37" s="33">
-        <v>8444927</v>
-      </c>
-      <c r="B37" s="34" t="s">
-        <v>51</v>
+      <c r="A37" s="30">
+        <v>8444903</v>
+      </c>
+      <c r="B37" s="31" t="s">
+        <v>49</v>
       </c>
       <c r="C37" s="10">
         <v>8</v>
       </c>
-      <c r="D37" s="20"/>
-      <c r="E37" s="20"/>
+      <c r="D37" s="17"/>
+      <c r="E37" s="17"/>
       <c r="F37" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -3328,17 +3414,17 @@
       <c r="I37" s="11"/>
     </row>
     <row r="38" spans="1:9" s="13" customFormat="1">
-      <c r="A38" s="18">
-        <v>8445160</v>
-      </c>
-      <c r="B38" s="19" t="s">
-        <v>71</v>
+      <c r="A38" s="30">
+        <v>8444910</v>
+      </c>
+      <c r="B38" s="31" t="s">
+        <v>50</v>
       </c>
       <c r="C38" s="10">
         <v>8</v>
       </c>
-      <c r="D38" s="20"/>
-      <c r="E38" s="20"/>
+      <c r="D38" s="17"/>
+      <c r="E38" s="17"/>
       <c r="F38" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -3347,23 +3433,23 @@
         <v>0.1</v>
       </c>
       <c r="H38" s="11">
-        <f>G38*D38</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I38" s="11"/>
     </row>
     <row r="39" spans="1:9" s="13" customFormat="1">
-      <c r="A39" s="18">
-        <v>8445177</v>
-      </c>
-      <c r="B39" s="19" t="s">
-        <v>72</v>
+      <c r="A39" s="30">
+        <v>8444927</v>
+      </c>
+      <c r="B39" s="31" t="s">
+        <v>51</v>
       </c>
       <c r="C39" s="10">
         <v>8</v>
       </c>
-      <c r="D39" s="20"/>
-      <c r="E39" s="20"/>
+      <c r="D39" s="17"/>
+      <c r="E39" s="17"/>
       <c r="F39" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -3372,125 +3458,127 @@
         <v>0.1</v>
       </c>
       <c r="H39" s="11">
-        <f>G39*D39</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I39" s="11"/>
     </row>
-    <row r="40" spans="1:9" s="39" customFormat="1">
-      <c r="A40" s="33">
+    <row r="40" spans="1:9" s="36" customFormat="1">
+      <c r="A40" s="15">
+        <v>8445160</v>
+      </c>
+      <c r="B40" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="C40" s="10">
+        <v>8</v>
+      </c>
+      <c r="D40" s="17"/>
+      <c r="E40" s="17"/>
+      <c r="F40" s="11">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G40" s="12">
+        <v>0.1</v>
+      </c>
+      <c r="H40" s="11">
+        <f>G40*D40</f>
+        <v>0</v>
+      </c>
+      <c r="I40" s="11"/>
+    </row>
+    <row r="41" spans="1:9" s="36" customFormat="1" ht="11.25" customHeight="1">
+      <c r="A41" s="15">
+        <v>8445177</v>
+      </c>
+      <c r="B41" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="C41" s="10">
+        <v>8</v>
+      </c>
+      <c r="D41" s="17"/>
+      <c r="E41" s="17"/>
+      <c r="F41" s="11">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G41" s="12">
+        <v>0.1</v>
+      </c>
+      <c r="H41" s="11">
+        <f>G41*D41</f>
+        <v>0</v>
+      </c>
+      <c r="I41" s="11"/>
+    </row>
+    <row r="42" spans="1:9" s="13" customFormat="1">
+      <c r="A42" s="30">
         <v>6600454</v>
       </c>
-      <c r="B40" s="34" t="s">
+      <c r="B42" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="C40" s="35">
+      <c r="C42" s="32">
         <v>12</v>
       </c>
-      <c r="D40" s="36"/>
-      <c r="E40" s="20"/>
-      <c r="F40" s="37">
+      <c r="D42" s="33"/>
+      <c r="E42" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="F42" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G40" s="38">
+      <c r="G42" s="35">
         <v>0.125</v>
       </c>
-      <c r="H40" s="37">
+      <c r="H42" s="34">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I40" s="37"/>
-    </row>
-    <row r="41" spans="1:9" s="39" customFormat="1" ht="11.25" customHeight="1">
-      <c r="A41" s="33">
+      <c r="I42" s="34"/>
+    </row>
+    <row r="43" spans="1:9" s="13" customFormat="1">
+      <c r="A43" s="30">
         <v>6600447</v>
       </c>
-      <c r="B41" s="34" t="s">
+      <c r="B43" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="C41" s="35">
+      <c r="C43" s="32">
         <v>12</v>
       </c>
-      <c r="D41" s="36"/>
-      <c r="E41" s="20"/>
-      <c r="F41" s="37">
+      <c r="D43" s="33"/>
+      <c r="E43" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="F43" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G41" s="38">
+      <c r="G43" s="35">
         <v>0.125</v>
       </c>
-      <c r="H41" s="37">
+      <c r="H43" s="34">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I41" s="37"/>
-    </row>
-    <row r="42" spans="1:9" s="13" customFormat="1">
-      <c r="A42" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B42" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="C42" s="10">
-        <v>10</v>
-      </c>
-      <c r="D42" s="20"/>
-      <c r="E42" s="20"/>
-      <c r="F42" s="11">
-        <f>D42/C42</f>
-        <v>0</v>
-      </c>
-      <c r="G42" s="12">
-        <v>0.2</v>
-      </c>
-      <c r="H42" s="11">
-        <f>G42*D42</f>
-        <v>0</v>
-      </c>
-      <c r="I42" s="11"/>
-    </row>
-    <row r="43" spans="1:9" s="13" customFormat="1">
-      <c r="A43" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B43" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C43" s="10">
-        <v>4</v>
-      </c>
-      <c r="D43" s="20"/>
-      <c r="E43" s="20"/>
-      <c r="F43" s="11">
-        <f>E43/15</f>
-        <v>0</v>
-      </c>
-      <c r="G43" s="12">
-        <v>3.5</v>
-      </c>
-      <c r="H43" s="11">
-        <f>E43</f>
-        <v>0</v>
-      </c>
-      <c r="I43" s="11" t="s">
-        <v>18</v>
-      </c>
+      <c r="I43" s="34"/>
     </row>
     <row r="44" spans="1:9" s="13" customFormat="1">
       <c r="A44" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C44" s="10">
         <v>10</v>
       </c>
-      <c r="D44" s="20"/>
-      <c r="E44" s="20"/>
+      <c r="D44" s="17"/>
+      <c r="E44" s="17"/>
       <c r="F44" s="11">
         <f>D44/C44</f>
         <v>0</v>
@@ -3506,16 +3594,16 @@
     </row>
     <row r="45" spans="1:9" s="13" customFormat="1">
       <c r="A45" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C45" s="10">
         <v>4</v>
       </c>
-      <c r="D45" s="20"/>
-      <c r="E45" s="20"/>
+      <c r="D45" s="17"/>
+      <c r="E45" s="17"/>
       <c r="F45" s="11">
         <f>E45/15</f>
         <v>0</v>
@@ -3532,17 +3620,17 @@
       </c>
     </row>
     <row r="46" spans="1:9" s="13" customFormat="1">
-      <c r="A46" s="2">
-        <v>7100108</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>73</v>
+      <c r="A46" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B46" s="12" t="s">
+        <v>14</v>
       </c>
       <c r="C46" s="10">
-        <v>12</v>
-      </c>
-      <c r="D46" s="20"/>
-      <c r="E46" s="20"/>
+        <v>10</v>
+      </c>
+      <c r="D46" s="17"/>
+      <c r="E46" s="17"/>
       <c r="F46" s="11">
         <f>D46/C46</f>
         <v>0</v>
@@ -3551,50 +3639,50 @@
         <v>0.2</v>
       </c>
       <c r="H46" s="11">
-        <f>D46*G46</f>
+        <f>G46*D46</f>
         <v>0</v>
       </c>
       <c r="I46" s="11"/>
     </row>
     <row r="47" spans="1:9" s="13" customFormat="1">
-      <c r="A47" s="2">
-        <v>7100139</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>74</v>
+      <c r="A47" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B47" s="12" t="s">
+        <v>17</v>
       </c>
       <c r="C47" s="10">
-        <v>8</v>
-      </c>
-      <c r="D47" s="20"/>
-      <c r="E47" s="20"/>
+        <v>4</v>
+      </c>
+      <c r="D47" s="17"/>
+      <c r="E47" s="17"/>
       <c r="F47" s="11">
-        <f>E47/20</f>
+        <f>E47/15</f>
         <v>0</v>
       </c>
       <c r="G47" s="12">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="H47" s="11">
         <f>E47</f>
         <v>0</v>
       </c>
       <c r="I47" s="11" t="s">
-        <v>75</v>
+        <v>18</v>
       </c>
     </row>
     <row r="48" spans="1:9" s="13" customFormat="1">
       <c r="A48" s="2">
-        <v>7100740</v>
+        <v>7100108</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C48" s="10">
         <v>12</v>
       </c>
-      <c r="D48" s="20"/>
-      <c r="E48" s="20"/>
+      <c r="D48" s="17"/>
+      <c r="E48" s="17"/>
       <c r="F48" s="11">
         <f>D48/C48</f>
         <v>0</v>
@@ -3610,16 +3698,16 @@
     </row>
     <row r="49" spans="1:9" s="13" customFormat="1">
       <c r="A49" s="2">
-        <v>7100726</v>
+        <v>7100139</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C49" s="10">
         <v>8</v>
       </c>
-      <c r="D49" s="20"/>
-      <c r="E49" s="20"/>
+      <c r="D49" s="17"/>
+      <c r="E49" s="17"/>
       <c r="F49" s="11">
         <f>E49/20</f>
         <v>0</v>
@@ -3632,77 +3720,79 @@
         <v>0</v>
       </c>
       <c r="I49" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="50" spans="1:9" s="13" customFormat="1">
       <c r="A50" s="2">
-        <v>4421584</v>
+        <v>7100740</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="C50" s="10">
         <v>12</v>
       </c>
-      <c r="D50" s="20"/>
-      <c r="E50" s="20"/>
+      <c r="D50" s="17"/>
+      <c r="E50" s="17"/>
       <c r="F50" s="11">
         <f>D50/C50</f>
         <v>0</v>
       </c>
       <c r="G50" s="12">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="H50" s="11">
-        <f>G50*D50</f>
+        <f>D50*G50</f>
         <v>0</v>
       </c>
       <c r="I50" s="11"/>
     </row>
     <row r="51" spans="1:9" s="13" customFormat="1">
       <c r="A51" s="2">
-        <v>4421577</v>
+        <v>7100726</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="C51" s="10">
-        <v>12</v>
-      </c>
-      <c r="D51" s="20"/>
-      <c r="E51" s="20"/>
+        <v>8</v>
+      </c>
+      <c r="D51" s="17"/>
+      <c r="E51" s="17"/>
       <c r="F51" s="11">
-        <f>D51/C51</f>
+        <f>E51/20</f>
         <v>0</v>
       </c>
       <c r="G51" s="12">
-        <v>0.18</v>
+        <v>2.5</v>
       </c>
       <c r="H51" s="11">
-        <f>G51*D51</f>
-        <v>0</v>
-      </c>
-      <c r="I51" s="11"/>
+        <f>E51</f>
+        <v>0</v>
+      </c>
+      <c r="I51" s="11" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="52" spans="1:9" s="13" customFormat="1">
       <c r="A52" s="2">
-        <v>9985949</v>
+        <v>4421584</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C52" s="10">
-        <v>10</v>
-      </c>
-      <c r="D52" s="20"/>
-      <c r="E52" s="20"/>
+        <v>12</v>
+      </c>
+      <c r="D52" s="17"/>
+      <c r="E52" s="17"/>
       <c r="F52" s="11">
         <f>D52/C52</f>
         <v>0</v>
       </c>
-      <c r="G52" s="21">
-        <v>1</v>
+      <c r="G52" s="12">
+        <v>0.18</v>
       </c>
       <c r="H52" s="11">
         <f>G52*D52</f>
@@ -3712,49 +3802,47 @@
     </row>
     <row r="53" spans="1:9" s="13" customFormat="1">
       <c r="A53" s="2">
-        <v>8786928</v>
+        <v>4421577</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C53" s="10">
-        <v>4</v>
-      </c>
-      <c r="D53" s="20"/>
-      <c r="E53" s="20"/>
+        <v>12</v>
+      </c>
+      <c r="D53" s="17"/>
+      <c r="E53" s="17"/>
       <c r="F53" s="11">
-        <f>E53/6</f>
+        <f>D53/C53</f>
         <v>0</v>
       </c>
       <c r="G53" s="12">
-        <v>1.5</v>
+        <v>0.18</v>
       </c>
       <c r="H53" s="11">
-        <f>E53</f>
-        <v>0</v>
-      </c>
-      <c r="I53" s="11" t="s">
-        <v>64</v>
-      </c>
+        <f>G53*D53</f>
+        <v>0</v>
+      </c>
+      <c r="I53" s="11"/>
     </row>
     <row r="54" spans="1:9" s="13" customFormat="1">
       <c r="A54" s="2">
-        <v>6948270</v>
+        <v>9985949</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C54" s="10">
-        <v>12</v>
-      </c>
-      <c r="D54" s="20"/>
-      <c r="E54" s="20"/>
+        <v>10</v>
+      </c>
+      <c r="D54" s="17"/>
+      <c r="E54" s="17"/>
       <c r="F54" s="11">
         <f>D54/C54</f>
         <v>0</v>
       </c>
-      <c r="G54" s="12">
-        <v>0.372</v>
+      <c r="G54" s="18">
+        <v>1</v>
       </c>
       <c r="H54" s="11">
         <f>G54*D54</f>
@@ -3764,41 +3852,43 @@
     </row>
     <row r="55" spans="1:9" s="13" customFormat="1">
       <c r="A55" s="2">
-        <v>6948287</v>
+        <v>8786928</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C55" s="10">
-        <v>12</v>
-      </c>
-      <c r="D55" s="20"/>
-      <c r="E55" s="20"/>
+        <v>4</v>
+      </c>
+      <c r="D55" s="17"/>
+      <c r="E55" s="17"/>
       <c r="F55" s="11">
-        <f>D55/C55</f>
+        <f>E55/6</f>
         <v>0</v>
       </c>
       <c r="G55" s="12">
-        <v>0.74399999999999999</v>
+        <v>1.5</v>
       </c>
       <c r="H55" s="11">
-        <f>G55*D55</f>
-        <v>0</v>
-      </c>
-      <c r="I55" s="11"/>
+        <f>E55</f>
+        <v>0</v>
+      </c>
+      <c r="I55" s="11" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="56" spans="1:9" s="13" customFormat="1">
       <c r="A56" s="2">
-        <v>6948256</v>
+        <v>6948270</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C56" s="10">
         <v>12</v>
       </c>
-      <c r="D56" s="20"/>
-      <c r="E56" s="20"/>
+      <c r="D56" s="17"/>
+      <c r="E56" s="17"/>
       <c r="F56" s="11">
         <f>D56/C56</f>
         <v>0</v>
@@ -3814,16 +3904,16 @@
     </row>
     <row r="57" spans="1:9" s="13" customFormat="1">
       <c r="A57" s="2">
-        <v>6948263</v>
+        <v>6948287</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C57" s="10">
         <v>12</v>
       </c>
-      <c r="D57" s="20"/>
-      <c r="E57" s="20"/>
+      <c r="D57" s="17"/>
+      <c r="E57" s="17"/>
       <c r="F57" s="11">
         <f>D57/C57</f>
         <v>0</v>
@@ -3839,22 +3929,22 @@
     </row>
     <row r="58" spans="1:9" s="13" customFormat="1">
       <c r="A58" s="2">
-        <v>6948249</v>
+        <v>6948256</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C58" s="10">
         <v>12</v>
       </c>
-      <c r="D58" s="20"/>
-      <c r="E58" s="20"/>
+      <c r="D58" s="17"/>
+      <c r="E58" s="17"/>
       <c r="F58" s="11">
         <f>D58/C58</f>
         <v>0</v>
       </c>
       <c r="G58" s="12">
-        <v>0.82499999999999996</v>
+        <v>0.372</v>
       </c>
       <c r="H58" s="11">
         <f>G58*D58</f>
@@ -3863,20 +3953,70 @@
       <c r="I58" s="11"/>
     </row>
     <row r="59" spans="1:9" s="13" customFormat="1">
-      <c r="A59" s="11"/>
-      <c r="B59" s="12" t="s">
+      <c r="A59" s="2">
+        <v>6948263</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C59" s="10">
+        <v>12</v>
+      </c>
+      <c r="D59" s="17"/>
+      <c r="E59" s="17"/>
+      <c r="F59" s="11">
+        <f>D59/C59</f>
+        <v>0</v>
+      </c>
+      <c r="G59" s="12">
+        <v>0.74399999999999999</v>
+      </c>
+      <c r="H59" s="11">
+        <f>G59*D59</f>
+        <v>0</v>
+      </c>
+      <c r="I59" s="11"/>
+    </row>
+    <row r="60" spans="1:9">
+      <c r="A60" s="2">
+        <v>6948249</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C60" s="10">
+        <v>12</v>
+      </c>
+      <c r="D60" s="17"/>
+      <c r="E60" s="17"/>
+      <c r="F60" s="11">
+        <f>D60/C60</f>
+        <v>0</v>
+      </c>
+      <c r="G60" s="12">
+        <v>0.82499999999999996</v>
+      </c>
+      <c r="H60" s="11">
+        <f>G60*D60</f>
+        <v>0</v>
+      </c>
+      <c r="I60" s="11"/>
+    </row>
+    <row r="61" spans="1:9">
+      <c r="A61" s="11"/>
+      <c r="B61" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C59" s="11"/>
-      <c r="D59" s="20"/>
-      <c r="E59" s="20"/>
-      <c r="F59" s="11"/>
-      <c r="G59" s="11"/>
-      <c r="H59" s="3">
-        <f>SUM(H4:H58)</f>
-        <v>0</v>
-      </c>
-      <c r="I59" s="11"/>
+      <c r="C61" s="11"/>
+      <c r="D61" s="17"/>
+      <c r="E61" s="17"/>
+      <c r="F61" s="11"/>
+      <c r="G61" s="11"/>
+      <c r="H61" s="3">
+        <f>SUM(H4:H60)</f>
+        <v>0</v>
+      </c>
+      <c r="I61" s="11"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:I52" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
@@ -3886,7 +4026,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:I59"/>
+  <dimension ref="A1:I61"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="10" style="4" customWidth="1"/>
@@ -3932,31 +4072,31 @@
       <c r="I2" s="7"/>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="15" t="s">
+      <c r="A3" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="D3" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="16" t="s">
+      <c r="E3" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="15" t="s">
+      <c r="F3" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="17" t="s">
+      <c r="G3" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="11" t="s">
         <v>7</v>
       </c>
     </row>
@@ -3964,14 +4104,14 @@
       <c r="A4" s="1">
         <v>5038435</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="19" t="s">
         <v>35</v>
       </c>
       <c r="C4" s="10">
         <v>10</v>
       </c>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
       <c r="F4" s="11">
         <f>D4/C4</f>
         <v>0</v>
@@ -3995,8 +4135,10 @@
       <c r="C5" s="10">
         <v>5</v>
       </c>
-      <c r="D5" s="20"/>
-      <c r="E5" s="20"/>
+      <c r="D5" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="E5" s="17"/>
       <c r="F5" s="11">
         <f>E5/16.5</f>
         <v>0</v>
@@ -4010,43 +4152,43 @@
       </c>
       <c r="I5" s="11"/>
     </row>
-    <row r="6" spans="1:9" s="29" customFormat="1" ht="25.5">
-      <c r="A6" s="23">
+    <row r="6" spans="1:9" s="26" customFormat="1" ht="25.5">
+      <c r="A6" s="20">
         <v>8783323</v>
       </c>
-      <c r="B6" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="C6" s="25">
-        <v>8</v>
-      </c>
-      <c r="D6" s="26"/>
-      <c r="E6" s="20"/>
-      <c r="F6" s="27">
-        <f>E5/15</f>
-        <v>0</v>
-      </c>
-      <c r="G6" s="28">
+      <c r="B6" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="C6" s="22">
+        <v>4</v>
+      </c>
+      <c r="D6" s="23"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="11">
+        <f>E6/5</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="25">
         <v>1.8</v>
       </c>
-      <c r="H6" s="27">
+      <c r="H6" s="24">
         <f>E6</f>
         <v>0</v>
       </c>
-      <c r="I6" s="27"/>
+      <c r="I6" s="24"/>
     </row>
     <row r="7" spans="1:9" s="13" customFormat="1" ht="25.5">
       <c r="A7" s="1">
         <v>5038459</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="19" t="s">
         <v>33</v>
       </c>
       <c r="C7" s="10">
         <v>10</v>
       </c>
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
       <c r="F7" s="11">
         <f>D7/C7</f>
         <v>0</v>
@@ -4061,100 +4203,102 @@
       <c r="I7" s="11"/>
     </row>
     <row r="8" spans="1:9" s="13" customFormat="1" ht="25.5">
-      <c r="A8" s="1">
+      <c r="A8" s="20">
+        <v>8785235</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="C8" s="10">
+        <v>5</v>
+      </c>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="11">
+        <f>E8/16.5</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="11">
+        <v>3.5</v>
+      </c>
+      <c r="H8" s="11">
+        <f>E8</f>
+        <v>0</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" s="13" customFormat="1" ht="25.5">
+      <c r="A9" s="1">
         <v>5038411</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B9" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C9" s="10">
         <v>10</v>
       </c>
-      <c r="D8" s="20"/>
-      <c r="E8" s="20"/>
-      <c r="F8" s="11">
-        <f>D8/C8</f>
-        <v>0</v>
-      </c>
-      <c r="G8" s="12">
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="11">
+        <f>D9/C9</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="12">
         <v>0.18</v>
       </c>
-      <c r="H8" s="11">
-        <f>G8*D8</f>
-        <v>0</v>
-      </c>
-      <c r="I8" s="11"/>
-    </row>
-    <row r="9" spans="1:9" s="13" customFormat="1" ht="25.5">
-      <c r="A9" s="2">
+      <c r="H9" s="11">
+        <f>G9*D9</f>
+        <v>0</v>
+      </c>
+      <c r="I9" s="11"/>
+    </row>
+    <row r="10" spans="1:9" s="13" customFormat="1" ht="25.5">
+      <c r="A10" s="2">
         <v>8785242</v>
       </c>
-      <c r="B9" s="22" t="s">
+      <c r="B10" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C10" s="10">
         <v>5</v>
       </c>
-      <c r="D9" s="20"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="11">
-        <f>E9/16.5</f>
-        <v>0</v>
-      </c>
-      <c r="G9" s="11">
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="11">
+        <f>E10/16.5</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="11">
         <v>3.5</v>
       </c>
-      <c r="H9" s="11">
-        <f>E9</f>
-        <v>0</v>
-      </c>
-      <c r="I9" s="11" t="s">
+      <c r="H10" s="11">
+        <f>E10</f>
+        <v>0</v>
+      </c>
+      <c r="I10" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:9" s="13" customFormat="1" ht="25.5">
-      <c r="A10" s="1">
+    <row r="11" spans="1:9" s="13" customFormat="1" ht="25.5">
+      <c r="A11" s="1">
         <v>5038398</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B11" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="10">
+      <c r="C11" s="10">
         <v>10</v>
       </c>
-      <c r="D10" s="20"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="11">
-        <f>D10/C10</f>
-        <v>0</v>
-      </c>
-      <c r="G10" s="12">
-        <v>0.18</v>
-      </c>
-      <c r="H10" s="11">
-        <f>G10*D10</f>
-        <v>0</v>
-      </c>
-      <c r="I10" s="11"/>
-    </row>
-    <row r="11" spans="1:9" s="13" customFormat="1">
-      <c r="A11" s="1">
-        <v>5039609</v>
-      </c>
-      <c r="B11" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="C11" s="10">
-        <v>8</v>
-      </c>
-      <c r="D11" s="20"/>
-      <c r="E11" s="20"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
       <c r="F11" s="11">
         <f>D11/C11</f>
         <v>0</v>
       </c>
       <c r="G11" s="12">
-        <v>0.4</v>
+        <v>0.18</v>
       </c>
       <c r="H11" s="11">
         <f>G11*D11</f>
@@ -4162,74 +4306,76 @@
       </c>
       <c r="I11" s="11"/>
     </row>
-    <row r="12" spans="1:9" s="13" customFormat="1" ht="25.5">
-      <c r="A12" s="2">
-        <v>8785259</v>
-      </c>
-      <c r="B12" s="22" t="s">
-        <v>52</v>
+    <row r="12" spans="1:9" s="13" customFormat="1">
+      <c r="A12" s="1">
+        <v>5039609</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>43</v>
       </c>
       <c r="C12" s="10">
-        <v>5</v>
-      </c>
-      <c r="D12" s="20"/>
-      <c r="E12" s="20"/>
+        <v>8</v>
+      </c>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17" t="s">
+        <v>77</v>
+      </c>
       <c r="F12" s="11">
-        <f>E12/16.5</f>
-        <v>0</v>
-      </c>
-      <c r="G12" s="11">
-        <v>3.5</v>
+        <f>D12/C12</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="12">
+        <v>0.4</v>
       </c>
       <c r="H12" s="11">
-        <f>E12</f>
+        <f>G12*D12</f>
         <v>0</v>
       </c>
       <c r="I12" s="11"/>
     </row>
     <row r="13" spans="1:9" s="13" customFormat="1" ht="25.5">
       <c r="A13" s="2">
+        <v>8785259</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" s="10">
+        <v>5</v>
+      </c>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="11">
+        <f>E13/16.5</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="11">
+        <v>3.5</v>
+      </c>
+      <c r="H13" s="11">
+        <f>E13</f>
+        <v>0</v>
+      </c>
+      <c r="I13" s="11"/>
+    </row>
+    <row r="14" spans="1:9" s="13" customFormat="1" ht="25.5">
+      <c r="A14" s="2">
         <v>5038855</v>
       </c>
-      <c r="B13" s="30" t="s">
+      <c r="B14" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="C13" s="10">
+      <c r="C14" s="10">
         <v>10</v>
       </c>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="11">
-        <f t="shared" ref="F13:F25" si="0">D13/C13</f>
-        <v>0</v>
-      </c>
-      <c r="G13" s="12">
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="11">
+        <f t="shared" ref="F14:F27" si="0">D14/C14</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="12">
         <v>0.2</v>
-      </c>
-      <c r="H13" s="11">
-        <f>G13*D13</f>
-        <v>0</v>
-      </c>
-      <c r="I13" s="11"/>
-    </row>
-    <row r="14" spans="1:9" s="13" customFormat="1">
-      <c r="A14" s="2">
-        <v>5039647</v>
-      </c>
-      <c r="B14" s="31" t="s">
-        <v>44</v>
-      </c>
-      <c r="C14" s="10">
-        <v>8</v>
-      </c>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G14" s="12">
-        <v>0.4</v>
       </c>
       <c r="H14" s="11">
         <f>G14*D14</f>
@@ -4237,24 +4383,24 @@
       </c>
       <c r="I14" s="11"/>
     </row>
-    <row r="15" spans="1:9" s="13" customFormat="1" ht="25.5">
+    <row r="15" spans="1:9" s="13" customFormat="1">
       <c r="A15" s="2">
-        <v>5038831</v>
-      </c>
-      <c r="B15" s="22" t="s">
-        <v>39</v>
-      </c>
-      <c r="C15" s="32">
-        <v>10</v>
-      </c>
-      <c r="D15" s="20"/>
-      <c r="E15" s="20"/>
+        <v>5039647</v>
+      </c>
+      <c r="B15" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="10">
+        <v>8</v>
+      </c>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
       <c r="F15" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G15" s="12">
-        <v>0.18</v>
+        <v>0.4</v>
       </c>
       <c r="H15" s="11">
         <f>G15*D15</f>
@@ -4262,24 +4408,24 @@
       </c>
       <c r="I15" s="11"/>
     </row>
-    <row r="16" spans="1:9" s="13" customFormat="1">
+    <row r="16" spans="1:9" s="13" customFormat="1" ht="25.5">
       <c r="A16" s="2">
-        <v>5039623</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="C16" s="32">
-        <v>8</v>
-      </c>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
+        <v>5038831</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16" s="29">
+        <v>10</v>
+      </c>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
       <c r="F16" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G16" s="12">
-        <v>0.4</v>
+        <v>0.18</v>
       </c>
       <c r="H16" s="11">
         <f>G16*D16</f>
@@ -4289,97 +4435,101 @@
     </row>
     <row r="17" spans="1:9" s="13" customFormat="1">
       <c r="A17" s="2">
-        <v>1018950</v>
+        <v>5039623</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="C17" s="10">
-        <v>10</v>
-      </c>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
+        <v>45</v>
+      </c>
+      <c r="C17" s="29">
+        <v>8</v>
+      </c>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17" t="s">
+        <v>77</v>
+      </c>
       <c r="F17" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G17" s="12">
-        <v>0.18</v>
+        <v>0.4</v>
       </c>
       <c r="H17" s="11">
-        <f t="shared" ref="H17:H25" si="1">G17*D17</f>
+        <f>G17*D17</f>
         <v>0</v>
       </c>
       <c r="I17" s="11"/>
     </row>
-    <row r="18" spans="1:9" s="13" customFormat="1">
-      <c r="A18" s="2">
-        <v>1018967</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="C18" s="10">
-        <v>10</v>
-      </c>
-      <c r="D18" s="20"/>
-      <c r="E18" s="20"/>
+    <row r="18" spans="1:9" s="13" customFormat="1" ht="38.25">
+      <c r="A18" s="15">
+        <v>8784931</v>
+      </c>
+      <c r="B18" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="C18" s="29">
+        <v>5</v>
+      </c>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
       <c r="F18" s="11">
-        <f t="shared" si="0"/>
+        <f>E18/16.4</f>
         <v>0</v>
       </c>
       <c r="G18" s="12">
-        <v>0.18</v>
+        <v>3.5</v>
       </c>
       <c r="H18" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I18" s="11"/>
+        <f>E18</f>
+        <v>0</v>
+      </c>
+      <c r="I18" s="11" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="19" spans="1:9" s="13" customFormat="1">
       <c r="A19" s="2">
-        <v>8444194</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>20</v>
+        <v>1018950</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>40</v>
       </c>
       <c r="C19" s="10">
-        <v>6</v>
-      </c>
-      <c r="D19" s="20"/>
-      <c r="E19" s="20"/>
+        <v>10</v>
+      </c>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
       <c r="F19" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G19" s="12">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="H19" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="H19:H27" si="1">G19*D19</f>
         <v>0</v>
       </c>
       <c r="I19" s="11"/>
     </row>
     <row r="20" spans="1:9" s="13" customFormat="1">
       <c r="A20" s="2">
-        <v>8444187</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>21</v>
+        <v>1018967</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>42</v>
       </c>
       <c r="C20" s="10">
-        <v>6</v>
-      </c>
-      <c r="D20" s="20"/>
-      <c r="E20" s="20"/>
+        <v>10</v>
+      </c>
+      <c r="D20" s="17"/>
+      <c r="E20" s="17"/>
       <c r="F20" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G20" s="12">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="H20" s="11">
         <f t="shared" si="1"/>
@@ -4389,16 +4539,16 @@
     </row>
     <row r="21" spans="1:9" s="13" customFormat="1">
       <c r="A21" s="2">
-        <v>8444163</v>
+        <v>8444194</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C21" s="10">
-        <v>8</v>
-      </c>
-      <c r="D21" s="20"/>
-      <c r="E21" s="20"/>
+        <v>6</v>
+      </c>
+      <c r="D21" s="17"/>
+      <c r="E21" s="17"/>
       <c r="F21" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -4414,18 +4564,18 @@
     </row>
     <row r="22" spans="1:9" s="13" customFormat="1">
       <c r="A22" s="2">
-        <v>8444170</v>
+        <v>8444187</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="C22" s="10">
-        <v>8</v>
-      </c>
-      <c r="D22" s="20"/>
-      <c r="E22" s="20"/>
+        <v>6</v>
+      </c>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
       <c r="F22" s="11">
-        <f>D22/C22</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G22" s="12">
@@ -4439,22 +4589,22 @@
     </row>
     <row r="23" spans="1:9" s="13" customFormat="1">
       <c r="A23" s="2">
-        <v>9988377</v>
+        <v>8444163</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C23" s="10">
-        <v>16</v>
-      </c>
-      <c r="D23" s="20"/>
-      <c r="E23" s="20"/>
+        <v>8</v>
+      </c>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
       <c r="F23" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G23" s="12">
-        <v>0.14000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="H23" s="11">
         <f t="shared" si="1"/>
@@ -4464,22 +4614,22 @@
     </row>
     <row r="24" spans="1:9" s="13" customFormat="1">
       <c r="A24" s="2">
-        <v>9988391</v>
+        <v>8444170</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="C24" s="10">
-        <v>16</v>
-      </c>
-      <c r="D24" s="20"/>
-      <c r="E24" s="20"/>
+        <v>8</v>
+      </c>
+      <c r="D24" s="17"/>
+      <c r="E24" s="17"/>
       <c r="F24" s="11">
-        <f t="shared" si="0"/>
+        <f>D24/C24</f>
         <v>0</v>
       </c>
       <c r="G24" s="12">
-        <v>0.14000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="H24" s="11">
         <f t="shared" si="1"/>
@@ -4489,22 +4639,22 @@
     </row>
     <row r="25" spans="1:9" s="13" customFormat="1">
       <c r="A25" s="2">
-        <v>5034819</v>
+        <v>9988377</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C25" s="10">
-        <v>6</v>
-      </c>
-      <c r="D25" s="20"/>
-      <c r="E25" s="20"/>
+        <v>16</v>
+      </c>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17"/>
       <c r="F25" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G25" s="12">
-        <v>0.18</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="H25" s="11">
         <f t="shared" si="1"/>
@@ -4514,151 +4664,151 @@
     </row>
     <row r="26" spans="1:9" s="13" customFormat="1">
       <c r="A26" s="2">
-        <v>2981244</v>
+        <v>9988391</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C26" s="10">
-        <v>6</v>
-      </c>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
+        <v>16</v>
+      </c>
+      <c r="D26" s="17"/>
+      <c r="E26" s="17"/>
       <c r="F26" s="11">
-        <f>E26/7.8</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G26" s="12">
-        <v>1.3</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="H26" s="11">
-        <f>E26</f>
-        <v>0</v>
-      </c>
-      <c r="I26" s="11" t="s">
-        <v>19</v>
-      </c>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I26" s="11"/>
     </row>
     <row r="27" spans="1:9" s="13" customFormat="1">
       <c r="A27" s="2">
-        <v>8785198</v>
+        <v>5034819</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C27" s="10">
-        <v>5</v>
-      </c>
-      <c r="D27" s="20"/>
-      <c r="E27" s="20"/>
+        <v>6</v>
+      </c>
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
       <c r="F27" s="11">
-        <f>E27/16.5</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G27" s="12">
-        <v>3.2</v>
+        <v>0.18</v>
       </c>
       <c r="H27" s="11">
-        <f>E27</f>
-        <v>0</v>
-      </c>
-      <c r="I27" s="11" t="s">
-        <v>15</v>
-      </c>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I27" s="11"/>
     </row>
     <row r="28" spans="1:9" s="13" customFormat="1">
       <c r="A28" s="2">
-        <v>9988452</v>
+        <v>2981244</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C28" s="10">
-        <v>8</v>
-      </c>
-      <c r="D28" s="20"/>
-      <c r="E28" s="20"/>
+        <v>6</v>
+      </c>
+      <c r="D28" s="17"/>
+      <c r="E28" s="17"/>
       <c r="F28" s="11">
-        <f t="shared" ref="F28:F41" si="2">D28/C28</f>
+        <f>E28/7.8</f>
         <v>0</v>
       </c>
       <c r="G28" s="12">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="H28" s="11">
-        <f t="shared" ref="H28:H33" si="3">G28*D28</f>
-        <v>0</v>
-      </c>
-      <c r="I28" s="11"/>
+        <f>E28</f>
+        <v>0</v>
+      </c>
+      <c r="I28" s="11" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="29" spans="1:9" s="13" customFormat="1">
       <c r="A29" s="2">
-        <v>9988476</v>
+        <v>8785198</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C29" s="10">
-        <v>28</v>
-      </c>
-      <c r="D29" s="20"/>
-      <c r="E29" s="20"/>
+        <v>5</v>
+      </c>
+      <c r="D29" s="17"/>
+      <c r="E29" s="17"/>
       <c r="F29" s="11">
-        <f t="shared" si="2"/>
+        <f>E29/16.5</f>
         <v>0</v>
       </c>
       <c r="G29" s="12">
-        <v>0.4</v>
+        <v>3.2</v>
       </c>
       <c r="H29" s="11">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I29" s="11"/>
+        <f>E29</f>
+        <v>0</v>
+      </c>
+      <c r="I29" s="11" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="30" spans="1:9" s="13" customFormat="1">
       <c r="A30" s="2">
-        <v>9988681</v>
+        <v>9988452</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="C30" s="10">
-        <v>16</v>
-      </c>
-      <c r="D30" s="20"/>
-      <c r="E30" s="20"/>
+        <v>8</v>
+      </c>
+      <c r="D30" s="17"/>
+      <c r="E30" s="17"/>
       <c r="F30" s="11">
-        <f>D30/C30</f>
+        <f t="shared" ref="F30:F43" si="2">D30/C30</f>
         <v>0</v>
       </c>
       <c r="G30" s="12">
-        <v>0.18</v>
+        <v>0.4</v>
       </c>
       <c r="H30" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="H30:H35" si="3">G30*D30</f>
         <v>0</v>
       </c>
       <c r="I30" s="11"/>
     </row>
     <row r="31" spans="1:9" s="13" customFormat="1">
       <c r="A31" s="2">
-        <v>9988438</v>
+        <v>9988476</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C31" s="10">
-        <v>16</v>
-      </c>
-      <c r="D31" s="20"/>
-      <c r="E31" s="20"/>
+        <v>28</v>
+      </c>
+      <c r="D31" s="17"/>
+      <c r="E31" s="17"/>
       <c r="F31" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G31" s="12">
-        <v>0.18</v>
+        <v>0.4</v>
       </c>
       <c r="H31" s="11">
         <f t="shared" si="3"/>
@@ -4668,18 +4818,18 @@
     </row>
     <row r="32" spans="1:9" s="13" customFormat="1">
       <c r="A32" s="2">
-        <v>9988445</v>
+        <v>9988681</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C32" s="10">
         <v>16</v>
       </c>
-      <c r="D32" s="20"/>
-      <c r="E32" s="20"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17"/>
       <c r="F32" s="11">
-        <f t="shared" si="2"/>
+        <f>D32/C32</f>
         <v>0</v>
       </c>
       <c r="G32" s="12">
@@ -4693,22 +4843,22 @@
     </row>
     <row r="33" spans="1:9" s="13" customFormat="1">
       <c r="A33" s="2">
-        <v>9988421</v>
+        <v>9988438</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C33" s="10">
         <v>16</v>
       </c>
-      <c r="D33" s="20"/>
-      <c r="E33" s="20"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="17"/>
       <c r="F33" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G33" s="12">
-        <v>0.14000000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="H33" s="11">
         <f t="shared" si="3"/>
@@ -4718,16 +4868,16 @@
     </row>
     <row r="34" spans="1:9" s="13" customFormat="1">
       <c r="A34" s="2">
-        <v>9988674</v>
+        <v>9988445</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="C34" s="10">
         <v>16</v>
       </c>
-      <c r="D34" s="20"/>
-      <c r="E34" s="20"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="17"/>
       <c r="F34" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -4736,73 +4886,73 @@
         <v>0.18</v>
       </c>
       <c r="H34" s="11">
-        <f t="shared" ref="H34:H41" si="4">D34*G34</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I34" s="11"/>
     </row>
     <row r="35" spans="1:9" s="13" customFormat="1">
-      <c r="A35" s="33">
-        <v>8444903</v>
-      </c>
-      <c r="B35" s="34" t="s">
-        <v>49</v>
+      <c r="A35" s="2">
+        <v>9988421</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>32</v>
       </c>
       <c r="C35" s="10">
-        <v>8</v>
-      </c>
-      <c r="D35" s="20"/>
-      <c r="E35" s="20"/>
+        <v>16</v>
+      </c>
+      <c r="D35" s="17"/>
+      <c r="E35" s="17"/>
       <c r="F35" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G35" s="12">
-        <v>0.1</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="H35" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I35" s="11"/>
     </row>
     <row r="36" spans="1:9" s="13" customFormat="1">
-      <c r="A36" s="33">
-        <v>8444910</v>
-      </c>
-      <c r="B36" s="34" t="s">
-        <v>50</v>
+      <c r="A36" s="2">
+        <v>9988674</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="C36" s="10">
-        <v>8</v>
-      </c>
-      <c r="D36" s="20"/>
-      <c r="E36" s="20"/>
+        <v>16</v>
+      </c>
+      <c r="D36" s="17"/>
+      <c r="E36" s="17"/>
       <c r="F36" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G36" s="12">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="H36" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="H36:H43" si="4">D36*G36</f>
         <v>0</v>
       </c>
       <c r="I36" s="11"/>
     </row>
     <row r="37" spans="1:9" s="13" customFormat="1">
-      <c r="A37" s="33">
-        <v>8444927</v>
-      </c>
-      <c r="B37" s="34" t="s">
-        <v>51</v>
+      <c r="A37" s="30">
+        <v>8444903</v>
+      </c>
+      <c r="B37" s="31" t="s">
+        <v>49</v>
       </c>
       <c r="C37" s="10">
         <v>8</v>
       </c>
-      <c r="D37" s="20"/>
-      <c r="E37" s="20"/>
+      <c r="D37" s="17"/>
+      <c r="E37" s="17"/>
       <c r="F37" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -4817,17 +4967,17 @@
       <c r="I37" s="11"/>
     </row>
     <row r="38" spans="1:9" s="13" customFormat="1">
-      <c r="A38" s="18">
-        <v>8445160</v>
-      </c>
-      <c r="B38" s="19" t="s">
-        <v>71</v>
+      <c r="A38" s="30">
+        <v>8444910</v>
+      </c>
+      <c r="B38" s="31" t="s">
+        <v>50</v>
       </c>
       <c r="C38" s="10">
         <v>8</v>
       </c>
-      <c r="D38" s="20"/>
-      <c r="E38" s="20"/>
+      <c r="D38" s="17"/>
+      <c r="E38" s="17"/>
       <c r="F38" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -4836,23 +4986,23 @@
         <v>0.1</v>
       </c>
       <c r="H38" s="11">
-        <f>G38*D38</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I38" s="11"/>
     </row>
     <row r="39" spans="1:9" s="13" customFormat="1">
-      <c r="A39" s="18">
-        <v>8445177</v>
-      </c>
-      <c r="B39" s="19" t="s">
-        <v>72</v>
+      <c r="A39" s="30">
+        <v>8444927</v>
+      </c>
+      <c r="B39" s="31" t="s">
+        <v>51</v>
       </c>
       <c r="C39" s="10">
         <v>8</v>
       </c>
-      <c r="D39" s="20"/>
-      <c r="E39" s="20"/>
+      <c r="D39" s="17"/>
+      <c r="E39" s="17"/>
       <c r="F39" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -4861,125 +5011,127 @@
         <v>0.1</v>
       </c>
       <c r="H39" s="11">
-        <f>G39*D39</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I39" s="11"/>
     </row>
-    <row r="40" spans="1:9" s="39" customFormat="1">
-      <c r="A40" s="33">
+    <row r="40" spans="1:9" s="36" customFormat="1">
+      <c r="A40" s="15">
+        <v>8445160</v>
+      </c>
+      <c r="B40" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="C40" s="10">
+        <v>8</v>
+      </c>
+      <c r="D40" s="17"/>
+      <c r="E40" s="17"/>
+      <c r="F40" s="11">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G40" s="12">
+        <v>0.1</v>
+      </c>
+      <c r="H40" s="11">
+        <f>G40*D40</f>
+        <v>0</v>
+      </c>
+      <c r="I40" s="11"/>
+    </row>
+    <row r="41" spans="1:9" s="36" customFormat="1" ht="11.25" customHeight="1">
+      <c r="A41" s="15">
+        <v>8445177</v>
+      </c>
+      <c r="B41" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="C41" s="10">
+        <v>8</v>
+      </c>
+      <c r="D41" s="17"/>
+      <c r="E41" s="17"/>
+      <c r="F41" s="11">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G41" s="12">
+        <v>0.1</v>
+      </c>
+      <c r="H41" s="11">
+        <f>G41*D41</f>
+        <v>0</v>
+      </c>
+      <c r="I41" s="11"/>
+    </row>
+    <row r="42" spans="1:9" s="13" customFormat="1">
+      <c r="A42" s="30">
         <v>6600454</v>
       </c>
-      <c r="B40" s="34" t="s">
+      <c r="B42" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="C40" s="35">
+      <c r="C42" s="32">
         <v>12</v>
       </c>
-      <c r="D40" s="36"/>
-      <c r="E40" s="20"/>
-      <c r="F40" s="37">
+      <c r="D42" s="33"/>
+      <c r="E42" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="F42" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G40" s="38">
+      <c r="G42" s="35">
         <v>0.125</v>
       </c>
-      <c r="H40" s="37">
+      <c r="H42" s="34">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I40" s="37"/>
-    </row>
-    <row r="41" spans="1:9" s="39" customFormat="1" ht="11.25" customHeight="1">
-      <c r="A41" s="33">
+      <c r="I42" s="34"/>
+    </row>
+    <row r="43" spans="1:9" s="13" customFormat="1">
+      <c r="A43" s="30">
         <v>6600447</v>
       </c>
-      <c r="B41" s="34" t="s">
+      <c r="B43" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="C41" s="35">
+      <c r="C43" s="32">
         <v>12</v>
       </c>
-      <c r="D41" s="36"/>
-      <c r="E41" s="20"/>
-      <c r="F41" s="37">
+      <c r="D43" s="33"/>
+      <c r="E43" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="F43" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G41" s="38">
+      <c r="G43" s="35">
         <v>0.125</v>
       </c>
-      <c r="H41" s="37">
+      <c r="H43" s="34">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I41" s="37"/>
-    </row>
-    <row r="42" spans="1:9" s="13" customFormat="1">
-      <c r="A42" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B42" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="C42" s="10">
-        <v>10</v>
-      </c>
-      <c r="D42" s="20"/>
-      <c r="E42" s="20"/>
-      <c r="F42" s="11">
-        <f>D42/C42</f>
-        <v>0</v>
-      </c>
-      <c r="G42" s="12">
-        <v>0.2</v>
-      </c>
-      <c r="H42" s="11">
-        <f>G42*D42</f>
-        <v>0</v>
-      </c>
-      <c r="I42" s="11"/>
-    </row>
-    <row r="43" spans="1:9" s="13" customFormat="1">
-      <c r="A43" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B43" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C43" s="10">
-        <v>4</v>
-      </c>
-      <c r="D43" s="20"/>
-      <c r="E43" s="20"/>
-      <c r="F43" s="11">
-        <f>E43/15</f>
-        <v>0</v>
-      </c>
-      <c r="G43" s="12">
-        <v>3.5</v>
-      </c>
-      <c r="H43" s="11">
-        <f>E43</f>
-        <v>0</v>
-      </c>
-      <c r="I43" s="11" t="s">
-        <v>18</v>
-      </c>
+      <c r="I43" s="34"/>
     </row>
     <row r="44" spans="1:9" s="13" customFormat="1">
       <c r="A44" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C44" s="10">
         <v>10</v>
       </c>
-      <c r="D44" s="20"/>
-      <c r="E44" s="20"/>
+      <c r="D44" s="17"/>
+      <c r="E44" s="17"/>
       <c r="F44" s="11">
         <f>D44/C44</f>
         <v>0</v>
@@ -4995,16 +5147,16 @@
     </row>
     <row r="45" spans="1:9" s="13" customFormat="1">
       <c r="A45" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C45" s="10">
         <v>4</v>
       </c>
-      <c r="D45" s="20"/>
-      <c r="E45" s="20"/>
+      <c r="D45" s="17"/>
+      <c r="E45" s="17"/>
       <c r="F45" s="11">
         <f>E45/15</f>
         <v>0</v>
@@ -5021,17 +5173,17 @@
       </c>
     </row>
     <row r="46" spans="1:9" s="13" customFormat="1">
-      <c r="A46" s="2">
-        <v>7100108</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>73</v>
+      <c r="A46" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B46" s="12" t="s">
+        <v>14</v>
       </c>
       <c r="C46" s="10">
-        <v>12</v>
-      </c>
-      <c r="D46" s="20"/>
-      <c r="E46" s="20"/>
+        <v>10</v>
+      </c>
+      <c r="D46" s="17"/>
+      <c r="E46" s="17"/>
       <c r="F46" s="11">
         <f>D46/C46</f>
         <v>0</v>
@@ -5040,50 +5192,50 @@
         <v>0.2</v>
       </c>
       <c r="H46" s="11">
-        <f>D46*G46</f>
+        <f>G46*D46</f>
         <v>0</v>
       </c>
       <c r="I46" s="11"/>
     </row>
     <row r="47" spans="1:9" s="13" customFormat="1">
-      <c r="A47" s="2">
-        <v>7100139</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>74</v>
+      <c r="A47" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B47" s="12" t="s">
+        <v>17</v>
       </c>
       <c r="C47" s="10">
-        <v>8</v>
-      </c>
-      <c r="D47" s="20"/>
-      <c r="E47" s="20"/>
+        <v>4</v>
+      </c>
+      <c r="D47" s="17"/>
+      <c r="E47" s="17"/>
       <c r="F47" s="11">
-        <f>E47/20</f>
+        <f>E47/15</f>
         <v>0</v>
       </c>
       <c r="G47" s="12">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="H47" s="11">
         <f>E47</f>
         <v>0</v>
       </c>
       <c r="I47" s="11" t="s">
-        <v>75</v>
+        <v>18</v>
       </c>
     </row>
     <row r="48" spans="1:9" s="13" customFormat="1">
       <c r="A48" s="2">
-        <v>7100740</v>
+        <v>7100108</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C48" s="10">
         <v>12</v>
       </c>
-      <c r="D48" s="20"/>
-      <c r="E48" s="20"/>
+      <c r="D48" s="17"/>
+      <c r="E48" s="17"/>
       <c r="F48" s="11">
         <f>D48/C48</f>
         <v>0</v>
@@ -5099,16 +5251,16 @@
     </row>
     <row r="49" spans="1:9" s="13" customFormat="1">
       <c r="A49" s="2">
-        <v>7100726</v>
+        <v>7100139</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C49" s="10">
         <v>8</v>
       </c>
-      <c r="D49" s="20"/>
-      <c r="E49" s="20"/>
+      <c r="D49" s="17"/>
+      <c r="E49" s="17"/>
       <c r="F49" s="11">
         <f>E49/20</f>
         <v>0</v>
@@ -5121,77 +5273,79 @@
         <v>0</v>
       </c>
       <c r="I49" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="50" spans="1:9" s="13" customFormat="1">
       <c r="A50" s="2">
-        <v>4421584</v>
+        <v>7100740</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="C50" s="10">
         <v>12</v>
       </c>
-      <c r="D50" s="20"/>
-      <c r="E50" s="20"/>
+      <c r="D50" s="17"/>
+      <c r="E50" s="17"/>
       <c r="F50" s="11">
         <f>D50/C50</f>
         <v>0</v>
       </c>
       <c r="G50" s="12">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="H50" s="11">
-        <f>G50*D50</f>
+        <f>D50*G50</f>
         <v>0</v>
       </c>
       <c r="I50" s="11"/>
     </row>
     <row r="51" spans="1:9" s="13" customFormat="1">
       <c r="A51" s="2">
-        <v>4421577</v>
+        <v>7100726</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="C51" s="10">
-        <v>12</v>
-      </c>
-      <c r="D51" s="20"/>
-      <c r="E51" s="20"/>
+        <v>8</v>
+      </c>
+      <c r="D51" s="17"/>
+      <c r="E51" s="17"/>
       <c r="F51" s="11">
-        <f>D51/C51</f>
+        <f>E51/20</f>
         <v>0</v>
       </c>
       <c r="G51" s="12">
-        <v>0.18</v>
+        <v>2.5</v>
       </c>
       <c r="H51" s="11">
-        <f>G51*D51</f>
-        <v>0</v>
-      </c>
-      <c r="I51" s="11"/>
+        <f>E51</f>
+        <v>0</v>
+      </c>
+      <c r="I51" s="11" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="52" spans="1:9" s="13" customFormat="1">
       <c r="A52" s="2">
-        <v>9985949</v>
+        <v>4421584</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C52" s="10">
-        <v>10</v>
-      </c>
-      <c r="D52" s="20"/>
-      <c r="E52" s="20"/>
+        <v>12</v>
+      </c>
+      <c r="D52" s="17"/>
+      <c r="E52" s="17"/>
       <c r="F52" s="11">
         <f>D52/C52</f>
         <v>0</v>
       </c>
-      <c r="G52" s="21">
-        <v>1</v>
+      <c r="G52" s="12">
+        <v>0.18</v>
       </c>
       <c r="H52" s="11">
         <f>G52*D52</f>
@@ -5201,49 +5355,47 @@
     </row>
     <row r="53" spans="1:9" s="13" customFormat="1">
       <c r="A53" s="2">
-        <v>8786928</v>
+        <v>4421577</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C53" s="10">
-        <v>4</v>
-      </c>
-      <c r="D53" s="20"/>
-      <c r="E53" s="20"/>
+        <v>12</v>
+      </c>
+      <c r="D53" s="17"/>
+      <c r="E53" s="17"/>
       <c r="F53" s="11">
-        <f>E53/6</f>
+        <f>D53/C53</f>
         <v>0</v>
       </c>
       <c r="G53" s="12">
-        <v>1.5</v>
+        <v>0.18</v>
       </c>
       <c r="H53" s="11">
-        <f>E53</f>
-        <v>0</v>
-      </c>
-      <c r="I53" s="11" t="s">
-        <v>64</v>
-      </c>
+        <f>G53*D53</f>
+        <v>0</v>
+      </c>
+      <c r="I53" s="11"/>
     </row>
     <row r="54" spans="1:9" s="13" customFormat="1">
       <c r="A54" s="2">
-        <v>6948270</v>
+        <v>9985949</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C54" s="10">
-        <v>12</v>
-      </c>
-      <c r="D54" s="20"/>
-      <c r="E54" s="20"/>
+        <v>10</v>
+      </c>
+      <c r="D54" s="17"/>
+      <c r="E54" s="17"/>
       <c r="F54" s="11">
         <f>D54/C54</f>
         <v>0</v>
       </c>
-      <c r="G54" s="12">
-        <v>0.372</v>
+      <c r="G54" s="18">
+        <v>1</v>
       </c>
       <c r="H54" s="11">
         <f>G54*D54</f>
@@ -5253,41 +5405,43 @@
     </row>
     <row r="55" spans="1:9" s="13" customFormat="1">
       <c r="A55" s="2">
-        <v>6948287</v>
+        <v>8786928</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C55" s="10">
-        <v>12</v>
-      </c>
-      <c r="D55" s="20"/>
-      <c r="E55" s="20"/>
+        <v>4</v>
+      </c>
+      <c r="D55" s="17"/>
+      <c r="E55" s="17"/>
       <c r="F55" s="11">
-        <f>D55/C55</f>
+        <f>E55/6</f>
         <v>0</v>
       </c>
       <c r="G55" s="12">
-        <v>0.74399999999999999</v>
+        <v>1.5</v>
       </c>
       <c r="H55" s="11">
-        <f>G55*D55</f>
-        <v>0</v>
-      </c>
-      <c r="I55" s="11"/>
+        <f>E55</f>
+        <v>0</v>
+      </c>
+      <c r="I55" s="11" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="56" spans="1:9" s="13" customFormat="1">
       <c r="A56" s="2">
-        <v>6948256</v>
+        <v>6948270</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C56" s="10">
         <v>12</v>
       </c>
-      <c r="D56" s="20"/>
-      <c r="E56" s="20"/>
+      <c r="D56" s="17"/>
+      <c r="E56" s="17"/>
       <c r="F56" s="11">
         <f>D56/C56</f>
         <v>0</v>
@@ -5303,16 +5457,16 @@
     </row>
     <row r="57" spans="1:9" s="13" customFormat="1">
       <c r="A57" s="2">
-        <v>6948263</v>
+        <v>6948287</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C57" s="10">
         <v>12</v>
       </c>
-      <c r="D57" s="20"/>
-      <c r="E57" s="20"/>
+      <c r="D57" s="17"/>
+      <c r="E57" s="17"/>
       <c r="F57" s="11">
         <f>D57/C57</f>
         <v>0</v>
@@ -5328,22 +5482,22 @@
     </row>
     <row r="58" spans="1:9" s="13" customFormat="1">
       <c r="A58" s="2">
-        <v>6948249</v>
+        <v>6948256</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C58" s="10">
         <v>12</v>
       </c>
-      <c r="D58" s="20"/>
-      <c r="E58" s="20"/>
+      <c r="D58" s="17"/>
+      <c r="E58" s="17"/>
       <c r="F58" s="11">
         <f>D58/C58</f>
         <v>0</v>
       </c>
       <c r="G58" s="12">
-        <v>0.82499999999999996</v>
+        <v>0.372</v>
       </c>
       <c r="H58" s="11">
         <f>G58*D58</f>
@@ -5352,20 +5506,70 @@
       <c r="I58" s="11"/>
     </row>
     <row r="59" spans="1:9" s="13" customFormat="1">
-      <c r="A59" s="11"/>
-      <c r="B59" s="12" t="s">
+      <c r="A59" s="2">
+        <v>6948263</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C59" s="10">
+        <v>12</v>
+      </c>
+      <c r="D59" s="17"/>
+      <c r="E59" s="17"/>
+      <c r="F59" s="11">
+        <f>D59/C59</f>
+        <v>0</v>
+      </c>
+      <c r="G59" s="12">
+        <v>0.74399999999999999</v>
+      </c>
+      <c r="H59" s="11">
+        <f>G59*D59</f>
+        <v>0</v>
+      </c>
+      <c r="I59" s="11"/>
+    </row>
+    <row r="60" spans="1:9">
+      <c r="A60" s="2">
+        <v>6948249</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C60" s="10">
+        <v>12</v>
+      </c>
+      <c r="D60" s="17"/>
+      <c r="E60" s="17"/>
+      <c r="F60" s="11">
+        <f>D60/C60</f>
+        <v>0</v>
+      </c>
+      <c r="G60" s="12">
+        <v>0.82499999999999996</v>
+      </c>
+      <c r="H60" s="11">
+        <f>G60*D60</f>
+        <v>0</v>
+      </c>
+      <c r="I60" s="11"/>
+    </row>
+    <row r="61" spans="1:9">
+      <c r="A61" s="11"/>
+      <c r="B61" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C59" s="11"/>
-      <c r="D59" s="20"/>
-      <c r="E59" s="20"/>
-      <c r="F59" s="11"/>
-      <c r="G59" s="11"/>
-      <c r="H59" s="3">
-        <f>SUM(H4:H58)</f>
-        <v>0</v>
-      </c>
-      <c r="I59" s="11"/>
+      <c r="C61" s="11"/>
+      <c r="D61" s="17"/>
+      <c r="E61" s="17"/>
+      <c r="F61" s="11"/>
+      <c r="G61" s="11"/>
+      <c r="H61" s="3">
+        <f>SUM(H4:H60)</f>
+        <v>0</v>
+      </c>
+      <c r="I61" s="11"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:I52" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
@@ -5375,7 +5579,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I59"/>
+  <dimension ref="A1:I61"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="10" style="4" customWidth="1"/>
@@ -5421,31 +5625,31 @@
       <c r="I2" s="7"/>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="15" t="s">
+      <c r="A3" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="D3" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="16" t="s">
+      <c r="E3" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="15" t="s">
+      <c r="F3" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="17" t="s">
+      <c r="G3" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="11" t="s">
         <v>7</v>
       </c>
     </row>
@@ -5453,14 +5657,14 @@
       <c r="A4" s="1">
         <v>5038435</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="19" t="s">
         <v>35</v>
       </c>
       <c r="C4" s="10">
         <v>10</v>
       </c>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
       <c r="F4" s="11">
         <f>D4/C4</f>
         <v>0</v>
@@ -5484,8 +5688,10 @@
       <c r="C5" s="10">
         <v>5</v>
       </c>
-      <c r="D5" s="20"/>
-      <c r="E5" s="20"/>
+      <c r="D5" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="E5" s="17"/>
       <c r="F5" s="11">
         <f>E5/16.5</f>
         <v>0</v>
@@ -5499,43 +5705,43 @@
       </c>
       <c r="I5" s="11"/>
     </row>
-    <row r="6" spans="1:9" s="29" customFormat="1" ht="25.5">
-      <c r="A6" s="23">
+    <row r="6" spans="1:9" s="26" customFormat="1" ht="25.5">
+      <c r="A6" s="20">
         <v>8783323</v>
       </c>
-      <c r="B6" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="C6" s="25">
-        <v>8</v>
-      </c>
-      <c r="D6" s="26"/>
-      <c r="E6" s="20"/>
-      <c r="F6" s="27">
-        <f>E5/15</f>
-        <v>0</v>
-      </c>
-      <c r="G6" s="28">
+      <c r="B6" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="C6" s="22">
+        <v>4</v>
+      </c>
+      <c r="D6" s="23"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="11">
+        <f>E6/5</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="25">
         <v>1.8</v>
       </c>
-      <c r="H6" s="27">
+      <c r="H6" s="24">
         <f>E6</f>
         <v>0</v>
       </c>
-      <c r="I6" s="27"/>
+      <c r="I6" s="24"/>
     </row>
     <row r="7" spans="1:9" s="13" customFormat="1" ht="25.5">
       <c r="A7" s="1">
         <v>5038459</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="19" t="s">
         <v>33</v>
       </c>
       <c r="C7" s="10">
         <v>10</v>
       </c>
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
       <c r="F7" s="11">
         <f>D7/C7</f>
         <v>0</v>
@@ -5550,100 +5756,102 @@
       <c r="I7" s="11"/>
     </row>
     <row r="8" spans="1:9" s="13" customFormat="1" ht="25.5">
-      <c r="A8" s="1">
+      <c r="A8" s="20">
+        <v>8785235</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="C8" s="10">
+        <v>5</v>
+      </c>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="11">
+        <f>E8/16.5</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="11">
+        <v>3.5</v>
+      </c>
+      <c r="H8" s="11">
+        <f>E8</f>
+        <v>0</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" s="13" customFormat="1" ht="25.5">
+      <c r="A9" s="1">
         <v>5038411</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B9" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C9" s="10">
         <v>10</v>
       </c>
-      <c r="D8" s="20"/>
-      <c r="E8" s="20"/>
-      <c r="F8" s="11">
-        <f>D8/C8</f>
-        <v>0</v>
-      </c>
-      <c r="G8" s="12">
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="11">
+        <f>D9/C9</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="12">
         <v>0.18</v>
       </c>
-      <c r="H8" s="11">
-        <f>G8*D8</f>
-        <v>0</v>
-      </c>
-      <c r="I8" s="11"/>
-    </row>
-    <row r="9" spans="1:9" s="13" customFormat="1" ht="25.5">
-      <c r="A9" s="2">
+      <c r="H9" s="11">
+        <f>G9*D9</f>
+        <v>0</v>
+      </c>
+      <c r="I9" s="11"/>
+    </row>
+    <row r="10" spans="1:9" s="13" customFormat="1" ht="25.5">
+      <c r="A10" s="2">
         <v>8785242</v>
       </c>
-      <c r="B9" s="22" t="s">
+      <c r="B10" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C10" s="10">
         <v>5</v>
       </c>
-      <c r="D9" s="20"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="11">
-        <f>E9/16.5</f>
-        <v>0</v>
-      </c>
-      <c r="G9" s="11">
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="11">
+        <f>E10/16.5</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="11">
         <v>3.5</v>
       </c>
-      <c r="H9" s="11">
-        <f>E9</f>
-        <v>0</v>
-      </c>
-      <c r="I9" s="11" t="s">
+      <c r="H10" s="11">
+        <f>E10</f>
+        <v>0</v>
+      </c>
+      <c r="I10" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:9" s="13" customFormat="1" ht="25.5">
-      <c r="A10" s="1">
+    <row r="11" spans="1:9" s="13" customFormat="1" ht="25.5">
+      <c r="A11" s="1">
         <v>5038398</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B11" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="10">
+      <c r="C11" s="10">
         <v>10</v>
       </c>
-      <c r="D10" s="20"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="11">
-        <f>D10/C10</f>
-        <v>0</v>
-      </c>
-      <c r="G10" s="12">
-        <v>0.18</v>
-      </c>
-      <c r="H10" s="11">
-        <f>G10*D10</f>
-        <v>0</v>
-      </c>
-      <c r="I10" s="11"/>
-    </row>
-    <row r="11" spans="1:9" s="13" customFormat="1">
-      <c r="A11" s="1">
-        <v>5039609</v>
-      </c>
-      <c r="B11" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="C11" s="10">
-        <v>8</v>
-      </c>
-      <c r="D11" s="20"/>
-      <c r="E11" s="20"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
       <c r="F11" s="11">
         <f>D11/C11</f>
         <v>0</v>
       </c>
       <c r="G11" s="12">
-        <v>0.4</v>
+        <v>0.18</v>
       </c>
       <c r="H11" s="11">
         <f>G11*D11</f>
@@ -5651,74 +5859,76 @@
       </c>
       <c r="I11" s="11"/>
     </row>
-    <row r="12" spans="1:9" s="13" customFormat="1" ht="25.5">
-      <c r="A12" s="2">
-        <v>8785259</v>
-      </c>
-      <c r="B12" s="22" t="s">
-        <v>52</v>
+    <row r="12" spans="1:9" s="13" customFormat="1">
+      <c r="A12" s="1">
+        <v>5039609</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>43</v>
       </c>
       <c r="C12" s="10">
-        <v>5</v>
-      </c>
-      <c r="D12" s="20"/>
-      <c r="E12" s="20"/>
+        <v>8</v>
+      </c>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17" t="s">
+        <v>77</v>
+      </c>
       <c r="F12" s="11">
-        <f>E12/16.5</f>
-        <v>0</v>
-      </c>
-      <c r="G12" s="11">
-        <v>3.5</v>
+        <f>D12/C12</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="12">
+        <v>0.4</v>
       </c>
       <c r="H12" s="11">
-        <f>E12</f>
+        <f>G12*D12</f>
         <v>0</v>
       </c>
       <c r="I12" s="11"/>
     </row>
     <row r="13" spans="1:9" s="13" customFormat="1" ht="25.5">
       <c r="A13" s="2">
+        <v>8785259</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" s="10">
+        <v>5</v>
+      </c>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="11">
+        <f>E13/16.5</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="11">
+        <v>3.5</v>
+      </c>
+      <c r="H13" s="11">
+        <f>E13</f>
+        <v>0</v>
+      </c>
+      <c r="I13" s="11"/>
+    </row>
+    <row r="14" spans="1:9" s="13" customFormat="1" ht="25.5">
+      <c r="A14" s="2">
         <v>5038855</v>
       </c>
-      <c r="B13" s="30" t="s">
+      <c r="B14" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="C13" s="10">
+      <c r="C14" s="10">
         <v>10</v>
       </c>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="11">
-        <f t="shared" ref="F13:F25" si="0">D13/C13</f>
-        <v>0</v>
-      </c>
-      <c r="G13" s="12">
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="11">
+        <f t="shared" ref="F14:F27" si="0">D14/C14</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="12">
         <v>0.2</v>
-      </c>
-      <c r="H13" s="11">
-        <f>G13*D13</f>
-        <v>0</v>
-      </c>
-      <c r="I13" s="11"/>
-    </row>
-    <row r="14" spans="1:9" s="13" customFormat="1">
-      <c r="A14" s="2">
-        <v>5039647</v>
-      </c>
-      <c r="B14" s="31" t="s">
-        <v>44</v>
-      </c>
-      <c r="C14" s="10">
-        <v>8</v>
-      </c>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G14" s="12">
-        <v>0.4</v>
       </c>
       <c r="H14" s="11">
         <f>G14*D14</f>
@@ -5726,24 +5936,24 @@
       </c>
       <c r="I14" s="11"/>
     </row>
-    <row r="15" spans="1:9" s="13" customFormat="1" ht="25.5">
+    <row r="15" spans="1:9" s="13" customFormat="1">
       <c r="A15" s="2">
-        <v>5038831</v>
-      </c>
-      <c r="B15" s="22" t="s">
-        <v>39</v>
-      </c>
-      <c r="C15" s="32">
-        <v>10</v>
-      </c>
-      <c r="D15" s="20"/>
-      <c r="E15" s="20"/>
+        <v>5039647</v>
+      </c>
+      <c r="B15" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="10">
+        <v>8</v>
+      </c>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
       <c r="F15" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G15" s="12">
-        <v>0.18</v>
+        <v>0.4</v>
       </c>
       <c r="H15" s="11">
         <f>G15*D15</f>
@@ -5751,24 +5961,24 @@
       </c>
       <c r="I15" s="11"/>
     </row>
-    <row r="16" spans="1:9" s="13" customFormat="1">
+    <row r="16" spans="1:9" s="13" customFormat="1" ht="25.5">
       <c r="A16" s="2">
-        <v>5039623</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="C16" s="32">
-        <v>8</v>
-      </c>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
+        <v>5038831</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16" s="29">
+        <v>10</v>
+      </c>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
       <c r="F16" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G16" s="12">
-        <v>0.4</v>
+        <v>0.18</v>
       </c>
       <c r="H16" s="11">
         <f>G16*D16</f>
@@ -5778,97 +5988,101 @@
     </row>
     <row r="17" spans="1:9" s="13" customFormat="1">
       <c r="A17" s="2">
-        <v>1018950</v>
+        <v>5039623</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="C17" s="10">
-        <v>10</v>
-      </c>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
+        <v>45</v>
+      </c>
+      <c r="C17" s="29">
+        <v>8</v>
+      </c>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17" t="s">
+        <v>77</v>
+      </c>
       <c r="F17" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G17" s="12">
-        <v>0.18</v>
+        <v>0.4</v>
       </c>
       <c r="H17" s="11">
-        <f t="shared" ref="H17:H25" si="1">G17*D17</f>
+        <f>G17*D17</f>
         <v>0</v>
       </c>
       <c r="I17" s="11"/>
     </row>
-    <row r="18" spans="1:9" s="13" customFormat="1">
-      <c r="A18" s="2">
-        <v>1018967</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="C18" s="10">
-        <v>10</v>
-      </c>
-      <c r="D18" s="20"/>
-      <c r="E18" s="20"/>
+    <row r="18" spans="1:9" s="13" customFormat="1" ht="38.25">
+      <c r="A18" s="15">
+        <v>8784931</v>
+      </c>
+      <c r="B18" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="C18" s="29">
+        <v>5</v>
+      </c>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
       <c r="F18" s="11">
-        <f t="shared" si="0"/>
+        <f>E18/16.4</f>
         <v>0</v>
       </c>
       <c r="G18" s="12">
-        <v>0.18</v>
+        <v>3.5</v>
       </c>
       <c r="H18" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I18" s="11"/>
+        <f>E18</f>
+        <v>0</v>
+      </c>
+      <c r="I18" s="11" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="19" spans="1:9" s="13" customFormat="1">
       <c r="A19" s="2">
-        <v>8444194</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>20</v>
+        <v>1018950</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>40</v>
       </c>
       <c r="C19" s="10">
-        <v>6</v>
-      </c>
-      <c r="D19" s="20"/>
-      <c r="E19" s="20"/>
+        <v>10</v>
+      </c>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
       <c r="F19" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G19" s="12">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="H19" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="H19:H27" si="1">G19*D19</f>
         <v>0</v>
       </c>
       <c r="I19" s="11"/>
     </row>
     <row r="20" spans="1:9" s="13" customFormat="1">
       <c r="A20" s="2">
-        <v>8444187</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>21</v>
+        <v>1018967</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>42</v>
       </c>
       <c r="C20" s="10">
-        <v>6</v>
-      </c>
-      <c r="D20" s="20"/>
-      <c r="E20" s="20"/>
+        <v>10</v>
+      </c>
+      <c r="D20" s="17"/>
+      <c r="E20" s="17"/>
       <c r="F20" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G20" s="12">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="H20" s="11">
         <f t="shared" si="1"/>
@@ -5878,16 +6092,16 @@
     </row>
     <row r="21" spans="1:9" s="13" customFormat="1">
       <c r="A21" s="2">
-        <v>8444163</v>
+        <v>8444194</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C21" s="10">
-        <v>8</v>
-      </c>
-      <c r="D21" s="20"/>
-      <c r="E21" s="20"/>
+        <v>6</v>
+      </c>
+      <c r="D21" s="17"/>
+      <c r="E21" s="17"/>
       <c r="F21" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5903,18 +6117,18 @@
     </row>
     <row r="22" spans="1:9" s="13" customFormat="1">
       <c r="A22" s="2">
-        <v>8444170</v>
+        <v>8444187</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="C22" s="10">
-        <v>8</v>
-      </c>
-      <c r="D22" s="20"/>
-      <c r="E22" s="20"/>
+        <v>6</v>
+      </c>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
       <c r="F22" s="11">
-        <f>D22/C22</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G22" s="12">
@@ -5928,22 +6142,22 @@
     </row>
     <row r="23" spans="1:9" s="13" customFormat="1">
       <c r="A23" s="2">
-        <v>9988377</v>
+        <v>8444163</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C23" s="10">
-        <v>16</v>
-      </c>
-      <c r="D23" s="20"/>
-      <c r="E23" s="20"/>
+        <v>8</v>
+      </c>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
       <c r="F23" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G23" s="12">
-        <v>0.14000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="H23" s="11">
         <f t="shared" si="1"/>
@@ -5953,22 +6167,22 @@
     </row>
     <row r="24" spans="1:9" s="13" customFormat="1">
       <c r="A24" s="2">
-        <v>9988391</v>
+        <v>8444170</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="C24" s="10">
-        <v>16</v>
-      </c>
-      <c r="D24" s="20"/>
-      <c r="E24" s="20"/>
+        <v>8</v>
+      </c>
+      <c r="D24" s="17"/>
+      <c r="E24" s="17"/>
       <c r="F24" s="11">
-        <f t="shared" si="0"/>
+        <f>D24/C24</f>
         <v>0</v>
       </c>
       <c r="G24" s="12">
-        <v>0.14000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="H24" s="11">
         <f t="shared" si="1"/>
@@ -5978,22 +6192,22 @@
     </row>
     <row r="25" spans="1:9" s="13" customFormat="1">
       <c r="A25" s="2">
-        <v>5034819</v>
+        <v>9988377</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C25" s="10">
-        <v>6</v>
-      </c>
-      <c r="D25" s="20"/>
-      <c r="E25" s="20"/>
+        <v>16</v>
+      </c>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17"/>
       <c r="F25" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G25" s="12">
-        <v>0.18</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="H25" s="11">
         <f t="shared" si="1"/>
@@ -6003,151 +6217,151 @@
     </row>
     <row r="26" spans="1:9" s="13" customFormat="1">
       <c r="A26" s="2">
-        <v>2981244</v>
+        <v>9988391</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C26" s="10">
-        <v>6</v>
-      </c>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
+        <v>16</v>
+      </c>
+      <c r="D26" s="17"/>
+      <c r="E26" s="17"/>
       <c r="F26" s="11">
-        <f>E26/7.8</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G26" s="12">
-        <v>1.3</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="H26" s="11">
-        <f>E26</f>
-        <v>0</v>
-      </c>
-      <c r="I26" s="11" t="s">
-        <v>19</v>
-      </c>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I26" s="11"/>
     </row>
     <row r="27" spans="1:9" s="13" customFormat="1">
       <c r="A27" s="2">
-        <v>8785198</v>
+        <v>5034819</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C27" s="10">
-        <v>5</v>
-      </c>
-      <c r="D27" s="20"/>
-      <c r="E27" s="20"/>
+        <v>6</v>
+      </c>
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
       <c r="F27" s="11">
-        <f>E27/16.5</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G27" s="12">
-        <v>3.2</v>
+        <v>0.18</v>
       </c>
       <c r="H27" s="11">
-        <f>E27</f>
-        <v>0</v>
-      </c>
-      <c r="I27" s="11" t="s">
-        <v>15</v>
-      </c>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I27" s="11"/>
     </row>
     <row r="28" spans="1:9" s="13" customFormat="1">
       <c r="A28" s="2">
-        <v>9988452</v>
+        <v>2981244</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C28" s="10">
-        <v>8</v>
-      </c>
-      <c r="D28" s="20"/>
-      <c r="E28" s="20"/>
+        <v>6</v>
+      </c>
+      <c r="D28" s="17"/>
+      <c r="E28" s="17"/>
       <c r="F28" s="11">
-        <f t="shared" ref="F28:F41" si="2">D28/C28</f>
+        <f>E28/7.8</f>
         <v>0</v>
       </c>
       <c r="G28" s="12">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="H28" s="11">
-        <f t="shared" ref="H28:H33" si="3">G28*D28</f>
-        <v>0</v>
-      </c>
-      <c r="I28" s="11"/>
+        <f>E28</f>
+        <v>0</v>
+      </c>
+      <c r="I28" s="11" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="29" spans="1:9" s="13" customFormat="1">
       <c r="A29" s="2">
-        <v>9988476</v>
+        <v>8785198</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C29" s="10">
-        <v>28</v>
-      </c>
-      <c r="D29" s="20"/>
-      <c r="E29" s="20"/>
+        <v>5</v>
+      </c>
+      <c r="D29" s="17"/>
+      <c r="E29" s="17"/>
       <c r="F29" s="11">
-        <f t="shared" si="2"/>
+        <f>E29/16.5</f>
         <v>0</v>
       </c>
       <c r="G29" s="12">
-        <v>0.4</v>
+        <v>3.2</v>
       </c>
       <c r="H29" s="11">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I29" s="11"/>
+        <f>E29</f>
+        <v>0</v>
+      </c>
+      <c r="I29" s="11" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="30" spans="1:9" s="13" customFormat="1">
       <c r="A30" s="2">
-        <v>9988681</v>
+        <v>9988452</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="C30" s="10">
-        <v>16</v>
-      </c>
-      <c r="D30" s="20"/>
-      <c r="E30" s="20"/>
+        <v>8</v>
+      </c>
+      <c r="D30" s="17"/>
+      <c r="E30" s="17"/>
       <c r="F30" s="11">
-        <f>D30/C30</f>
+        <f t="shared" ref="F30:F43" si="2">D30/C30</f>
         <v>0</v>
       </c>
       <c r="G30" s="12">
-        <v>0.18</v>
+        <v>0.4</v>
       </c>
       <c r="H30" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="H30:H35" si="3">G30*D30</f>
         <v>0</v>
       </c>
       <c r="I30" s="11"/>
     </row>
     <row r="31" spans="1:9" s="13" customFormat="1">
       <c r="A31" s="2">
-        <v>9988438</v>
+        <v>9988476</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C31" s="10">
-        <v>16</v>
-      </c>
-      <c r="D31" s="20"/>
-      <c r="E31" s="20"/>
+        <v>28</v>
+      </c>
+      <c r="D31" s="17"/>
+      <c r="E31" s="17"/>
       <c r="F31" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G31" s="12">
-        <v>0.18</v>
+        <v>0.4</v>
       </c>
       <c r="H31" s="11">
         <f t="shared" si="3"/>
@@ -6157,18 +6371,18 @@
     </row>
     <row r="32" spans="1:9" s="13" customFormat="1">
       <c r="A32" s="2">
-        <v>9988445</v>
+        <v>9988681</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C32" s="10">
         <v>16</v>
       </c>
-      <c r="D32" s="20"/>
-      <c r="E32" s="20"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17"/>
       <c r="F32" s="11">
-        <f t="shared" si="2"/>
+        <f>D32/C32</f>
         <v>0</v>
       </c>
       <c r="G32" s="12">
@@ -6182,22 +6396,22 @@
     </row>
     <row r="33" spans="1:9" s="13" customFormat="1">
       <c r="A33" s="2">
-        <v>9988421</v>
+        <v>9988438</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C33" s="10">
         <v>16</v>
       </c>
-      <c r="D33" s="20"/>
-      <c r="E33" s="20"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="17"/>
       <c r="F33" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G33" s="12">
-        <v>0.14000000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="H33" s="11">
         <f t="shared" si="3"/>
@@ -6207,16 +6421,16 @@
     </row>
     <row r="34" spans="1:9" s="13" customFormat="1">
       <c r="A34" s="2">
-        <v>9988674</v>
+        <v>9988445</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="C34" s="10">
         <v>16</v>
       </c>
-      <c r="D34" s="20"/>
-      <c r="E34" s="20"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="17"/>
       <c r="F34" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -6225,73 +6439,73 @@
         <v>0.18</v>
       </c>
       <c r="H34" s="11">
-        <f t="shared" ref="H34:H41" si="4">D34*G34</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I34" s="11"/>
     </row>
     <row r="35" spans="1:9" s="13" customFormat="1">
-      <c r="A35" s="33">
-        <v>8444903</v>
-      </c>
-      <c r="B35" s="34" t="s">
-        <v>49</v>
+      <c r="A35" s="2">
+        <v>9988421</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>32</v>
       </c>
       <c r="C35" s="10">
-        <v>8</v>
-      </c>
-      <c r="D35" s="20"/>
-      <c r="E35" s="20"/>
+        <v>16</v>
+      </c>
+      <c r="D35" s="17"/>
+      <c r="E35" s="17"/>
       <c r="F35" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G35" s="12">
-        <v>0.1</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="H35" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I35" s="11"/>
     </row>
     <row r="36" spans="1:9" s="13" customFormat="1">
-      <c r="A36" s="33">
-        <v>8444910</v>
-      </c>
-      <c r="B36" s="34" t="s">
-        <v>50</v>
+      <c r="A36" s="2">
+        <v>9988674</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="C36" s="10">
-        <v>8</v>
-      </c>
-      <c r="D36" s="20"/>
-      <c r="E36" s="20"/>
+        <v>16</v>
+      </c>
+      <c r="D36" s="17"/>
+      <c r="E36" s="17"/>
       <c r="F36" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G36" s="12">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="H36" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="H36:H43" si="4">D36*G36</f>
         <v>0</v>
       </c>
       <c r="I36" s="11"/>
     </row>
     <row r="37" spans="1:9" s="13" customFormat="1">
-      <c r="A37" s="33">
-        <v>8444927</v>
-      </c>
-      <c r="B37" s="34" t="s">
-        <v>51</v>
+      <c r="A37" s="30">
+        <v>8444903</v>
+      </c>
+      <c r="B37" s="31" t="s">
+        <v>49</v>
       </c>
       <c r="C37" s="10">
         <v>8</v>
       </c>
-      <c r="D37" s="20"/>
-      <c r="E37" s="20"/>
+      <c r="D37" s="17"/>
+      <c r="E37" s="17"/>
       <c r="F37" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -6306,17 +6520,17 @@
       <c r="I37" s="11"/>
     </row>
     <row r="38" spans="1:9" s="13" customFormat="1">
-      <c r="A38" s="18">
-        <v>8445160</v>
-      </c>
-      <c r="B38" s="19" t="s">
-        <v>71</v>
+      <c r="A38" s="30">
+        <v>8444910</v>
+      </c>
+      <c r="B38" s="31" t="s">
+        <v>50</v>
       </c>
       <c r="C38" s="10">
         <v>8</v>
       </c>
-      <c r="D38" s="20"/>
-      <c r="E38" s="20"/>
+      <c r="D38" s="17"/>
+      <c r="E38" s="17"/>
       <c r="F38" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -6325,23 +6539,23 @@
         <v>0.1</v>
       </c>
       <c r="H38" s="11">
-        <f>G38*D38</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I38" s="11"/>
     </row>
     <row r="39" spans="1:9" s="13" customFormat="1">
-      <c r="A39" s="18">
-        <v>8445177</v>
-      </c>
-      <c r="B39" s="19" t="s">
-        <v>72</v>
+      <c r="A39" s="30">
+        <v>8444927</v>
+      </c>
+      <c r="B39" s="31" t="s">
+        <v>51</v>
       </c>
       <c r="C39" s="10">
         <v>8</v>
       </c>
-      <c r="D39" s="20"/>
-      <c r="E39" s="20"/>
+      <c r="D39" s="17"/>
+      <c r="E39" s="17"/>
       <c r="F39" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -6350,125 +6564,127 @@
         <v>0.1</v>
       </c>
       <c r="H39" s="11">
-        <f>G39*D39</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I39" s="11"/>
     </row>
-    <row r="40" spans="1:9" s="39" customFormat="1">
-      <c r="A40" s="33">
+    <row r="40" spans="1:9" s="36" customFormat="1">
+      <c r="A40" s="15">
+        <v>8445160</v>
+      </c>
+      <c r="B40" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="C40" s="10">
+        <v>8</v>
+      </c>
+      <c r="D40" s="17"/>
+      <c r="E40" s="17"/>
+      <c r="F40" s="11">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G40" s="12">
+        <v>0.1</v>
+      </c>
+      <c r="H40" s="11">
+        <f>G40*D40</f>
+        <v>0</v>
+      </c>
+      <c r="I40" s="11"/>
+    </row>
+    <row r="41" spans="1:9" s="36" customFormat="1" ht="11.25" customHeight="1">
+      <c r="A41" s="15">
+        <v>8445177</v>
+      </c>
+      <c r="B41" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="C41" s="10">
+        <v>8</v>
+      </c>
+      <c r="D41" s="17"/>
+      <c r="E41" s="17"/>
+      <c r="F41" s="11">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G41" s="12">
+        <v>0.1</v>
+      </c>
+      <c r="H41" s="11">
+        <f>G41*D41</f>
+        <v>0</v>
+      </c>
+      <c r="I41" s="11"/>
+    </row>
+    <row r="42" spans="1:9" s="13" customFormat="1">
+      <c r="A42" s="30">
         <v>6600454</v>
       </c>
-      <c r="B40" s="34" t="s">
+      <c r="B42" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="C40" s="35">
+      <c r="C42" s="32">
         <v>12</v>
       </c>
-      <c r="D40" s="36"/>
-      <c r="E40" s="20"/>
-      <c r="F40" s="37">
+      <c r="D42" s="33"/>
+      <c r="E42" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="F42" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G40" s="38">
+      <c r="G42" s="35">
         <v>0.125</v>
       </c>
-      <c r="H40" s="37">
+      <c r="H42" s="34">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I40" s="37"/>
-    </row>
-    <row r="41" spans="1:9" s="39" customFormat="1" ht="11.25" customHeight="1">
-      <c r="A41" s="33">
+      <c r="I42" s="34"/>
+    </row>
+    <row r="43" spans="1:9" s="13" customFormat="1">
+      <c r="A43" s="30">
         <v>6600447</v>
       </c>
-      <c r="B41" s="34" t="s">
+      <c r="B43" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="C41" s="35">
+      <c r="C43" s="32">
         <v>12</v>
       </c>
-      <c r="D41" s="36"/>
-      <c r="E41" s="20"/>
-      <c r="F41" s="37">
+      <c r="D43" s="33"/>
+      <c r="E43" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="F43" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G41" s="38">
+      <c r="G43" s="35">
         <v>0.125</v>
       </c>
-      <c r="H41" s="37">
+      <c r="H43" s="34">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I41" s="37"/>
-    </row>
-    <row r="42" spans="1:9" s="13" customFormat="1">
-      <c r="A42" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B42" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="C42" s="10">
-        <v>10</v>
-      </c>
-      <c r="D42" s="20"/>
-      <c r="E42" s="20"/>
-      <c r="F42" s="11">
-        <f>D42/C42</f>
-        <v>0</v>
-      </c>
-      <c r="G42" s="12">
-        <v>0.2</v>
-      </c>
-      <c r="H42" s="11">
-        <f>G42*D42</f>
-        <v>0</v>
-      </c>
-      <c r="I42" s="11"/>
-    </row>
-    <row r="43" spans="1:9" s="13" customFormat="1">
-      <c r="A43" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B43" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C43" s="10">
-        <v>4</v>
-      </c>
-      <c r="D43" s="20"/>
-      <c r="E43" s="20"/>
-      <c r="F43" s="11">
-        <f>E43/15</f>
-        <v>0</v>
-      </c>
-      <c r="G43" s="12">
-        <v>3.5</v>
-      </c>
-      <c r="H43" s="11">
-        <f>E43</f>
-        <v>0</v>
-      </c>
-      <c r="I43" s="11" t="s">
-        <v>18</v>
-      </c>
+      <c r="I43" s="34"/>
     </row>
     <row r="44" spans="1:9" s="13" customFormat="1">
       <c r="A44" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C44" s="10">
         <v>10</v>
       </c>
-      <c r="D44" s="20"/>
-      <c r="E44" s="20"/>
+      <c r="D44" s="17"/>
+      <c r="E44" s="17"/>
       <c r="F44" s="11">
         <f>D44/C44</f>
         <v>0</v>
@@ -6484,16 +6700,16 @@
     </row>
     <row r="45" spans="1:9" s="13" customFormat="1">
       <c r="A45" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C45" s="10">
         <v>4</v>
       </c>
-      <c r="D45" s="20"/>
-      <c r="E45" s="20"/>
+      <c r="D45" s="17"/>
+      <c r="E45" s="17"/>
       <c r="F45" s="11">
         <f>E45/15</f>
         <v>0</v>
@@ -6510,17 +6726,17 @@
       </c>
     </row>
     <row r="46" spans="1:9" s="13" customFormat="1">
-      <c r="A46" s="2">
-        <v>7100108</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>73</v>
+      <c r="A46" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B46" s="12" t="s">
+        <v>14</v>
       </c>
       <c r="C46" s="10">
-        <v>12</v>
-      </c>
-      <c r="D46" s="20"/>
-      <c r="E46" s="20"/>
+        <v>10</v>
+      </c>
+      <c r="D46" s="17"/>
+      <c r="E46" s="17"/>
       <c r="F46" s="11">
         <f>D46/C46</f>
         <v>0</v>
@@ -6529,50 +6745,50 @@
         <v>0.2</v>
       </c>
       <c r="H46" s="11">
-        <f>D46*G46</f>
+        <f>G46*D46</f>
         <v>0</v>
       </c>
       <c r="I46" s="11"/>
     </row>
     <row r="47" spans="1:9" s="13" customFormat="1">
-      <c r="A47" s="2">
-        <v>7100139</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>74</v>
+      <c r="A47" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B47" s="12" t="s">
+        <v>17</v>
       </c>
       <c r="C47" s="10">
-        <v>8</v>
-      </c>
-      <c r="D47" s="20"/>
-      <c r="E47" s="20"/>
+        <v>4</v>
+      </c>
+      <c r="D47" s="17"/>
+      <c r="E47" s="17"/>
       <c r="F47" s="11">
-        <f>E47/20</f>
+        <f>E47/15</f>
         <v>0</v>
       </c>
       <c r="G47" s="12">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="H47" s="11">
         <f>E47</f>
         <v>0</v>
       </c>
       <c r="I47" s="11" t="s">
-        <v>75</v>
+        <v>18</v>
       </c>
     </row>
     <row r="48" spans="1:9" s="13" customFormat="1">
       <c r="A48" s="2">
-        <v>7100740</v>
+        <v>7100108</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C48" s="10">
         <v>12</v>
       </c>
-      <c r="D48" s="20"/>
-      <c r="E48" s="20"/>
+      <c r="D48" s="17"/>
+      <c r="E48" s="17"/>
       <c r="F48" s="11">
         <f>D48/C48</f>
         <v>0</v>
@@ -6588,16 +6804,16 @@
     </row>
     <row r="49" spans="1:9" s="13" customFormat="1">
       <c r="A49" s="2">
-        <v>7100726</v>
+        <v>7100139</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C49" s="10">
         <v>8</v>
       </c>
-      <c r="D49" s="20"/>
-      <c r="E49" s="20"/>
+      <c r="D49" s="17"/>
+      <c r="E49" s="17"/>
       <c r="F49" s="11">
         <f>E49/20</f>
         <v>0</v>
@@ -6610,77 +6826,79 @@
         <v>0</v>
       </c>
       <c r="I49" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="50" spans="1:9" s="13" customFormat="1">
       <c r="A50" s="2">
-        <v>4421584</v>
+        <v>7100740</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="C50" s="10">
         <v>12</v>
       </c>
-      <c r="D50" s="20"/>
-      <c r="E50" s="20"/>
+      <c r="D50" s="17"/>
+      <c r="E50" s="17"/>
       <c r="F50" s="11">
         <f>D50/C50</f>
         <v>0</v>
       </c>
       <c r="G50" s="12">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="H50" s="11">
-        <f>G50*D50</f>
+        <f>D50*G50</f>
         <v>0</v>
       </c>
       <c r="I50" s="11"/>
     </row>
     <row r="51" spans="1:9" s="13" customFormat="1">
       <c r="A51" s="2">
-        <v>4421577</v>
+        <v>7100726</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="C51" s="10">
-        <v>12</v>
-      </c>
-      <c r="D51" s="20"/>
-      <c r="E51" s="20"/>
+        <v>8</v>
+      </c>
+      <c r="D51" s="17"/>
+      <c r="E51" s="17"/>
       <c r="F51" s="11">
-        <f>D51/C51</f>
+        <f>E51/20</f>
         <v>0</v>
       </c>
       <c r="G51" s="12">
-        <v>0.18</v>
+        <v>2.5</v>
       </c>
       <c r="H51" s="11">
-        <f>G51*D51</f>
-        <v>0</v>
-      </c>
-      <c r="I51" s="11"/>
+        <f>E51</f>
+        <v>0</v>
+      </c>
+      <c r="I51" s="11" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="52" spans="1:9" s="13" customFormat="1">
       <c r="A52" s="2">
-        <v>9985949</v>
+        <v>4421584</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C52" s="10">
-        <v>10</v>
-      </c>
-      <c r="D52" s="20"/>
-      <c r="E52" s="20"/>
+        <v>12</v>
+      </c>
+      <c r="D52" s="17"/>
+      <c r="E52" s="17"/>
       <c r="F52" s="11">
         <f>D52/C52</f>
         <v>0</v>
       </c>
-      <c r="G52" s="21">
-        <v>1</v>
+      <c r="G52" s="12">
+        <v>0.18</v>
       </c>
       <c r="H52" s="11">
         <f>G52*D52</f>
@@ -6690,49 +6908,47 @@
     </row>
     <row r="53" spans="1:9" s="13" customFormat="1">
       <c r="A53" s="2">
-        <v>8786928</v>
+        <v>4421577</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C53" s="10">
-        <v>4</v>
-      </c>
-      <c r="D53" s="20"/>
-      <c r="E53" s="20"/>
+        <v>12</v>
+      </c>
+      <c r="D53" s="17"/>
+      <c r="E53" s="17"/>
       <c r="F53" s="11">
-        <f>E53/6</f>
+        <f>D53/C53</f>
         <v>0</v>
       </c>
       <c r="G53" s="12">
-        <v>1.5</v>
+        <v>0.18</v>
       </c>
       <c r="H53" s="11">
-        <f>E53</f>
-        <v>0</v>
-      </c>
-      <c r="I53" s="11" t="s">
-        <v>64</v>
-      </c>
+        <f>G53*D53</f>
+        <v>0</v>
+      </c>
+      <c r="I53" s="11"/>
     </row>
     <row r="54" spans="1:9" s="13" customFormat="1">
       <c r="A54" s="2">
-        <v>6948270</v>
+        <v>9985949</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C54" s="10">
-        <v>12</v>
-      </c>
-      <c r="D54" s="20"/>
-      <c r="E54" s="20"/>
+        <v>10</v>
+      </c>
+      <c r="D54" s="17"/>
+      <c r="E54" s="17"/>
       <c r="F54" s="11">
         <f>D54/C54</f>
         <v>0</v>
       </c>
-      <c r="G54" s="12">
-        <v>0.372</v>
+      <c r="G54" s="18">
+        <v>1</v>
       </c>
       <c r="H54" s="11">
         <f>G54*D54</f>
@@ -6742,41 +6958,43 @@
     </row>
     <row r="55" spans="1:9" s="13" customFormat="1">
       <c r="A55" s="2">
-        <v>6948287</v>
+        <v>8786928</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C55" s="10">
-        <v>12</v>
-      </c>
-      <c r="D55" s="20"/>
-      <c r="E55" s="20"/>
+        <v>4</v>
+      </c>
+      <c r="D55" s="17"/>
+      <c r="E55" s="17"/>
       <c r="F55" s="11">
-        <f>D55/C55</f>
+        <f>E55/6</f>
         <v>0</v>
       </c>
       <c r="G55" s="12">
-        <v>0.74399999999999999</v>
+        <v>1.5</v>
       </c>
       <c r="H55" s="11">
-        <f>G55*D55</f>
-        <v>0</v>
-      </c>
-      <c r="I55" s="11"/>
+        <f>E55</f>
+        <v>0</v>
+      </c>
+      <c r="I55" s="11" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="56" spans="1:9" s="13" customFormat="1">
       <c r="A56" s="2">
-        <v>6948256</v>
+        <v>6948270</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C56" s="10">
         <v>12</v>
       </c>
-      <c r="D56" s="20"/>
-      <c r="E56" s="20"/>
+      <c r="D56" s="17"/>
+      <c r="E56" s="17"/>
       <c r="F56" s="11">
         <f>D56/C56</f>
         <v>0</v>
@@ -6792,16 +7010,16 @@
     </row>
     <row r="57" spans="1:9" s="13" customFormat="1">
       <c r="A57" s="2">
-        <v>6948263</v>
+        <v>6948287</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C57" s="10">
         <v>12</v>
       </c>
-      <c r="D57" s="20"/>
-      <c r="E57" s="20"/>
+      <c r="D57" s="17"/>
+      <c r="E57" s="17"/>
       <c r="F57" s="11">
         <f>D57/C57</f>
         <v>0</v>
@@ -6817,22 +7035,22 @@
     </row>
     <row r="58" spans="1:9" s="13" customFormat="1">
       <c r="A58" s="2">
-        <v>6948249</v>
+        <v>6948256</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C58" s="10">
         <v>12</v>
       </c>
-      <c r="D58" s="20"/>
-      <c r="E58" s="20"/>
+      <c r="D58" s="17"/>
+      <c r="E58" s="17"/>
       <c r="F58" s="11">
         <f>D58/C58</f>
         <v>0</v>
       </c>
       <c r="G58" s="12">
-        <v>0.82499999999999996</v>
+        <v>0.372</v>
       </c>
       <c r="H58" s="11">
         <f>G58*D58</f>
@@ -6841,20 +7059,70 @@
       <c r="I58" s="11"/>
     </row>
     <row r="59" spans="1:9" s="13" customFormat="1">
-      <c r="A59" s="11"/>
-      <c r="B59" s="12" t="s">
+      <c r="A59" s="2">
+        <v>6948263</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C59" s="10">
+        <v>12</v>
+      </c>
+      <c r="D59" s="17"/>
+      <c r="E59" s="17"/>
+      <c r="F59" s="11">
+        <f>D59/C59</f>
+        <v>0</v>
+      </c>
+      <c r="G59" s="12">
+        <v>0.74399999999999999</v>
+      </c>
+      <c r="H59" s="11">
+        <f>G59*D59</f>
+        <v>0</v>
+      </c>
+      <c r="I59" s="11"/>
+    </row>
+    <row r="60" spans="1:9">
+      <c r="A60" s="2">
+        <v>6948249</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C60" s="10">
+        <v>12</v>
+      </c>
+      <c r="D60" s="17"/>
+      <c r="E60" s="17"/>
+      <c r="F60" s="11">
+        <f>D60/C60</f>
+        <v>0</v>
+      </c>
+      <c r="G60" s="12">
+        <v>0.82499999999999996</v>
+      </c>
+      <c r="H60" s="11">
+        <f>G60*D60</f>
+        <v>0</v>
+      </c>
+      <c r="I60" s="11"/>
+    </row>
+    <row r="61" spans="1:9">
+      <c r="A61" s="11"/>
+      <c r="B61" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C59" s="11"/>
-      <c r="D59" s="20"/>
-      <c r="E59" s="20"/>
-      <c r="F59" s="11"/>
-      <c r="G59" s="11"/>
-      <c r="H59" s="3">
-        <f>SUM(H4:H58)</f>
-        <v>0</v>
-      </c>
-      <c r="I59" s="11"/>
+      <c r="C61" s="11"/>
+      <c r="D61" s="17"/>
+      <c r="E61" s="17"/>
+      <c r="F61" s="11"/>
+      <c r="G61" s="11"/>
+      <c r="H61" s="3">
+        <f>SUM(H4:H60)</f>
+        <v>0</v>
+      </c>
+      <c r="I61" s="11"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:I52" xr:uid="{00000000-0009-0000-0000-000003000000}"/>

--- a/в бланки заводов/Останкино СЫР/OrderCheeseInForm/новый_бланк/Бланк заказов сыр  дистр.xlsx
+++ b/в бланки заводов/Останкино СЫР/OrderCheeseInForm/новый_бланк/Бланк заказов сыр  дистр.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино СЫР\OrderCheeseInForm\новый_бланк\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B306DB2A-9113-4CF9-ACA8-DF9BAE49D8D5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1822C4D7-091B-4FC2-A136-C10D4FA25580}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Мелитополь" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="77">
   <si>
     <t>Артикул</t>
   </si>
@@ -168,24 +168,12 @@
     <t>Масло сливочное ПАПА МОЖЕТ 82.5%, фас. в фольгу, 180гр</t>
   </si>
   <si>
-    <t>Сыр ПАПА МОЖЕТ "Тильзитер" ж. 45% газ.среда, 400 гр (8 шт)</t>
-  </si>
-  <si>
-    <t>Сыр ПАПА МОЖЕТ "Папин завтрак" ж. 45% газ.среда, 400 гр (8 шт)</t>
-  </si>
-  <si>
-    <t>Сыр ПАПА МОЖЕТ "Министерский" ж. 45% газ.среда, 400 гр (8 шт)</t>
-  </si>
-  <si>
     <t>\</t>
   </si>
   <si>
     <t>Сыр полутвердый "Гауда", с массовой долей жира в пересчете на сухое вещество 45%, брус из блока 1/5, пленка желтая, короб складной ТМ Папа может</t>
   </si>
   <si>
-    <t>Сыр полутвердый "Российский" 3,2 кг, 50%, "Папа Может" ЮГ</t>
-  </si>
-  <si>
     <t>Сыр Перлини 40% 100гр (8шт)</t>
   </si>
   <si>
@@ -198,12 +186,6 @@
     <t>Сыр полутвердый "Тильзитер" с массовой долей жира в пересчете на сухое вещество 45%, брус из блока 1/5, пленка желтая, короб складной, весовой</t>
   </si>
   <si>
-    <t>Сыр Голландский 45%. Нарезка 125г ТМ Папа Может</t>
-  </si>
-  <si>
-    <t>Сыр Российский Особый 45%. Нарезка 125г  ТМ Папа Может</t>
-  </si>
-  <si>
     <t>783К798</t>
   </si>
   <si>
@@ -270,9 +252,6 @@
     <t>Продукт белково-жировой Сметанковый 50% вес ТМ Коровино</t>
   </si>
   <si>
-    <t>не доступно к заказу</t>
-  </si>
-  <si>
     <t>Сыр полутвердый Российский, цилиндр, 1/4, пленка, массовая доля жира в сухом веществе 50%</t>
   </si>
   <si>
@@ -282,14 +261,20 @@
     <t>Сыр полутвердый "Купеческий" с ароматом топленого молока, с массовой долей жира в пересчете на сухое вещество 50%, брус из блока 1/5, пленка желтая, короб складной ТМ "Папа может"</t>
   </si>
   <si>
-    <t>Средний вес короба 16,4( вес 1 брус 3,2кг)</t>
+    <t>БЖП, произведенный по технологии сыра копченый "Балык" резаный 4 вкуса</t>
+  </si>
+  <si>
+    <t>БЖП, произведенный по технологии сыра копченый "Косичка" мини Ассорти</t>
+  </si>
+  <si>
+    <t>Сыр копченый "Косичка" мини ПАПА МОЖЕТ 55г лоток</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18">
+  <fonts count="17">
     <font>
       <sz val="10"/>
       <color indexed="8"/>
@@ -383,12 +368,6 @@
     <font>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
-      <name val="Arial Cyr"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
       <name val="Liberation Sans1"/>
       <charset val="204"/>
     </font>
@@ -463,7 +442,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -502,25 +481,15 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -528,20 +497,21 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -914,7 +884,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="10" style="4" customWidth="1"/>
@@ -942,7 +912,7 @@
     </row>
     <row r="2" spans="1:9" ht="38.25">
       <c r="A2" s="7" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>12</v>
@@ -960,25 +930,25 @@
       <c r="I2" s="7"/>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="37" t="s">
+      <c r="A3" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="37" t="s">
+      <c r="C3" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="38" t="s">
+      <c r="D3" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="38" t="s">
+      <c r="E3" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="37" t="s">
+      <c r="F3" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="39" t="s">
+      <c r="G3" s="32" t="s">
         <v>10</v>
       </c>
       <c r="H3" s="11" t="s">
@@ -1013,207 +983,203 @@
       </c>
       <c r="I4" s="11"/>
     </row>
-    <row r="5" spans="1:9" s="13" customFormat="1">
-      <c r="A5" s="1">
-        <v>8785204</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="C5" s="10">
+    <row r="5" spans="1:9" s="13" customFormat="1" ht="25.5">
+      <c r="A5" s="33">
+        <v>8783323</v>
+      </c>
+      <c r="B5" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" s="28">
+        <v>4</v>
+      </c>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="11">
+        <f>E5/5</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="22">
+        <v>1.8</v>
+      </c>
+      <c r="H5" s="21">
+        <f>E5</f>
+        <v>0</v>
+      </c>
+      <c r="I5" s="21"/>
+    </row>
+    <row r="6" spans="1:9" s="23" customFormat="1" ht="25.5">
+      <c r="A6" s="1">
+        <v>5038459</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="10">
+        <v>10</v>
+      </c>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="11">
+        <f>D6/C6</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="12">
+        <v>0.18</v>
+      </c>
+      <c r="H6" s="11">
+        <f>G6*D6</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="11"/>
+    </row>
+    <row r="7" spans="1:9" s="13" customFormat="1" ht="25.5">
+      <c r="A7" s="33">
+        <v>8785235</v>
+      </c>
+      <c r="B7" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7" s="10">
         <v>5</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="E5" s="17"/>
-      <c r="F5" s="11">
-        <f>E5/16.5</f>
-        <v>0</v>
-      </c>
-      <c r="G5" s="12">
-        <v>3.2</v>
-      </c>
-      <c r="H5" s="11">
-        <f>E5</f>
-        <v>0</v>
-      </c>
-      <c r="I5" s="11"/>
-    </row>
-    <row r="6" spans="1:9" s="26" customFormat="1" ht="25.5">
-      <c r="A6" s="20">
-        <v>8783323</v>
-      </c>
-      <c r="B6" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="C6" s="22">
-        <v>4</v>
-      </c>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="11">
-        <f>E6/5</f>
-        <v>0</v>
-      </c>
-      <c r="G6" s="25">
-        <v>1.8</v>
-      </c>
-      <c r="H6" s="24">
-        <f>E6</f>
-        <v>0</v>
-      </c>
-      <c r="I6" s="24"/>
-    </row>
-    <row r="7" spans="1:9" s="13" customFormat="1" ht="25.5">
-      <c r="A7" s="1">
-        <v>5038459</v>
-      </c>
-      <c r="B7" s="19" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" s="10">
-        <v>10</v>
       </c>
       <c r="D7" s="17"/>
       <c r="E7" s="17"/>
       <c r="F7" s="11">
-        <f>D7/C7</f>
-        <v>0</v>
-      </c>
-      <c r="G7" s="12">
-        <v>0.18</v>
+        <f>E7/16.5</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="11">
+        <v>3.5</v>
       </c>
       <c r="H7" s="11">
-        <f>G7*D7</f>
-        <v>0</v>
-      </c>
-      <c r="I7" s="11"/>
+        <f>E7</f>
+        <v>0</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="8" spans="1:9" s="13" customFormat="1" ht="25.5">
-      <c r="A8" s="20">
-        <v>8785235</v>
-      </c>
-      <c r="B8" s="21" t="s">
-        <v>79</v>
+      <c r="A8" s="1">
+        <v>5038411</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>34</v>
       </c>
       <c r="C8" s="10">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D8" s="17"/>
       <c r="E8" s="17"/>
       <c r="F8" s="11">
-        <f>E8/16.5</f>
-        <v>0</v>
-      </c>
-      <c r="G8" s="11">
-        <v>3.5</v>
+        <f>D8/C8</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="12">
+        <v>0.18</v>
       </c>
       <c r="H8" s="11">
-        <f>E8</f>
-        <v>0</v>
-      </c>
-      <c r="I8" s="11" t="s">
-        <v>15</v>
-      </c>
+        <f>G8*D8</f>
+        <v>0</v>
+      </c>
+      <c r="I8" s="11"/>
     </row>
     <row r="9" spans="1:9" s="13" customFormat="1" ht="25.5">
-      <c r="A9" s="1">
-        <v>5038411</v>
+      <c r="A9" s="2">
+        <v>8785242</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="C9" s="10">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D9" s="17"/>
       <c r="E9" s="17"/>
       <c r="F9" s="11">
-        <f>D9/C9</f>
-        <v>0</v>
-      </c>
-      <c r="G9" s="12">
-        <v>0.18</v>
+        <f>E9/16.5</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="11">
+        <v>3.5</v>
       </c>
       <c r="H9" s="11">
-        <f>G9*D9</f>
-        <v>0</v>
-      </c>
-      <c r="I9" s="11"/>
+        <f>E9</f>
+        <v>0</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="10" spans="1:9" s="13" customFormat="1" ht="25.5">
-      <c r="A10" s="2">
-        <v>8785242</v>
+      <c r="A10" s="1">
+        <v>5038398</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C10" s="10">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D10" s="17"/>
       <c r="E10" s="17"/>
       <c r="F10" s="11">
-        <f>E10/16.5</f>
-        <v>0</v>
-      </c>
-      <c r="G10" s="11">
-        <v>3.5</v>
+        <f>D10/C10</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="12">
+        <v>0.18</v>
       </c>
       <c r="H10" s="11">
-        <f>E10</f>
-        <v>0</v>
-      </c>
-      <c r="I10" s="11" t="s">
-        <v>15</v>
-      </c>
+        <f>G10*D10</f>
+        <v>0</v>
+      </c>
+      <c r="I10" s="11"/>
     </row>
     <row r="11" spans="1:9" s="13" customFormat="1" ht="25.5">
-      <c r="A11" s="1">
-        <v>5038398</v>
+      <c r="A11" s="2">
+        <v>8785259</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="C11" s="10">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D11" s="17"/>
       <c r="E11" s="17"/>
       <c r="F11" s="11">
-        <f>D11/C11</f>
-        <v>0</v>
-      </c>
-      <c r="G11" s="12">
-        <v>0.18</v>
+        <f>E11/16.5</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="11">
+        <v>3.5</v>
       </c>
       <c r="H11" s="11">
-        <f>G11*D11</f>
+        <f>E11</f>
         <v>0</v>
       </c>
       <c r="I11" s="11"/>
     </row>
-    <row r="12" spans="1:9" s="13" customFormat="1">
-      <c r="A12" s="1">
-        <v>5039609</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>43</v>
+    <row r="12" spans="1:9" s="13" customFormat="1" ht="25.5">
+      <c r="A12" s="2">
+        <v>5038855</v>
+      </c>
+      <c r="B12" s="24" t="s">
+        <v>41</v>
       </c>
       <c r="C12" s="10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D12" s="17"/>
-      <c r="E12" s="17" t="s">
-        <v>77</v>
-      </c>
+      <c r="E12" s="17"/>
       <c r="F12" s="11">
         <f>D12/C12</f>
         <v>0</v>
       </c>
       <c r="G12" s="12">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="H12" s="11">
         <f>G12*D12</f>
@@ -1223,471 +1189,469 @@
     </row>
     <row r="13" spans="1:9" s="13" customFormat="1" ht="25.5">
       <c r="A13" s="2">
-        <v>8785259</v>
+        <v>5038831</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="C13" s="10">
-        <v>5</v>
+        <v>39</v>
+      </c>
+      <c r="C13" s="25">
+        <v>10</v>
       </c>
       <c r="D13" s="17"/>
       <c r="E13" s="17"/>
       <c r="F13" s="11">
-        <f>E13/16.5</f>
-        <v>0</v>
-      </c>
-      <c r="G13" s="11">
-        <v>3.5</v>
+        <f>D13/C13</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="12">
+        <v>0.18</v>
       </c>
       <c r="H13" s="11">
-        <f>E13</f>
+        <f>G13*D13</f>
         <v>0</v>
       </c>
       <c r="I13" s="11"/>
     </row>
-    <row r="14" spans="1:9" s="13" customFormat="1" ht="25.5">
-      <c r="A14" s="2">
-        <v>5038855</v>
-      </c>
-      <c r="B14" s="27" t="s">
-        <v>41</v>
-      </c>
-      <c r="C14" s="10">
-        <v>10</v>
+    <row r="14" spans="1:9" s="13" customFormat="1" ht="38.25">
+      <c r="A14" s="26">
+        <v>8784931</v>
+      </c>
+      <c r="B14" s="34" t="s">
+        <v>73</v>
+      </c>
+      <c r="C14" s="25">
+        <v>5</v>
       </c>
       <c r="D14" s="17"/>
       <c r="E14" s="17"/>
       <c r="F14" s="11">
-        <f t="shared" ref="F14:F27" si="0">D14/C14</f>
+        <f>E14/16.5</f>
         <v>0</v>
       </c>
       <c r="G14" s="12">
-        <v>0.2</v>
+        <v>3.5</v>
       </c>
       <c r="H14" s="11">
-        <f>G14*D14</f>
-        <v>0</v>
-      </c>
-      <c r="I14" s="11"/>
+        <f>E14</f>
+        <v>0</v>
+      </c>
+      <c r="I14" s="11" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="15" spans="1:9" s="13" customFormat="1">
       <c r="A15" s="2">
-        <v>5039647</v>
-      </c>
-      <c r="B15" s="28" t="s">
-        <v>44</v>
+        <v>1018950</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>40</v>
       </c>
       <c r="C15" s="10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D15" s="17"/>
       <c r="E15" s="17"/>
       <c r="F15" s="11">
-        <f t="shared" si="0"/>
+        <f>D15/C15</f>
         <v>0</v>
       </c>
       <c r="G15" s="12">
-        <v>0.4</v>
+        <v>0.18</v>
       </c>
       <c r="H15" s="11">
-        <f>G15*D15</f>
+        <f t="shared" ref="H15:H23" si="0">G15*D15</f>
         <v>0</v>
       </c>
       <c r="I15" s="11"/>
     </row>
-    <row r="16" spans="1:9" s="13" customFormat="1" ht="25.5">
+    <row r="16" spans="1:9" s="13" customFormat="1">
       <c r="A16" s="2">
-        <v>5038831</v>
-      </c>
-      <c r="B16" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="C16" s="29">
+        <v>1018967</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" s="10">
         <v>10</v>
       </c>
       <c r="D16" s="17"/>
       <c r="E16" s="17"/>
       <c r="F16" s="11">
-        <f t="shared" si="0"/>
+        <f>D16/C16</f>
         <v>0</v>
       </c>
       <c r="G16" s="12">
         <v>0.18</v>
       </c>
       <c r="H16" s="11">
-        <f>G16*D16</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I16" s="11"/>
     </row>
     <row r="17" spans="1:9" s="13" customFormat="1">
       <c r="A17" s="2">
-        <v>5039623</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="C17" s="29">
-        <v>8</v>
+        <v>8444194</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="10">
+        <v>6</v>
       </c>
       <c r="D17" s="17"/>
-      <c r="E17" s="17" t="s">
-        <v>77</v>
-      </c>
+      <c r="E17" s="17"/>
       <c r="F17" s="11">
+        <f t="shared" ref="F17:F23" si="1">D17/C17</f>
+        <v>0</v>
+      </c>
+      <c r="G17" s="12">
+        <v>0.1</v>
+      </c>
+      <c r="H17" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G17" s="12">
-        <v>0.4</v>
-      </c>
-      <c r="H17" s="11">
-        <f>G17*D17</f>
-        <v>0</v>
-      </c>
       <c r="I17" s="11"/>
     </row>
-    <row r="18" spans="1:9" s="13" customFormat="1" ht="38.25">
-      <c r="A18" s="15">
-        <v>8784931</v>
-      </c>
-      <c r="B18" s="21" t="s">
-        <v>80</v>
-      </c>
-      <c r="C18" s="29">
-        <v>5</v>
+    <row r="18" spans="1:9" s="13" customFormat="1">
+      <c r="A18" s="2">
+        <v>8444187</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" s="10">
+        <v>6</v>
       </c>
       <c r="D18" s="17"/>
       <c r="E18" s="17"/>
       <c r="F18" s="11">
-        <f>E18/16.4</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G18" s="12">
-        <v>3.5</v>
+        <v>0.1</v>
       </c>
       <c r="H18" s="11">
-        <f>E18</f>
-        <v>0</v>
-      </c>
-      <c r="I18" s="11" t="s">
-        <v>81</v>
-      </c>
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I18" s="11"/>
     </row>
     <row r="19" spans="1:9" s="13" customFormat="1">
       <c r="A19" s="2">
-        <v>1018950</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>40</v>
+        <v>8444163</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>22</v>
       </c>
       <c r="C19" s="10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D19" s="17"/>
       <c r="E19" s="17"/>
       <c r="F19" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G19" s="12">
+        <v>0.1</v>
+      </c>
+      <c r="H19" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G19" s="12">
-        <v>0.18</v>
-      </c>
-      <c r="H19" s="11">
-        <f t="shared" ref="H19:H27" si="1">G19*D19</f>
         <v>0</v>
       </c>
       <c r="I19" s="11"/>
     </row>
     <row r="20" spans="1:9" s="13" customFormat="1">
       <c r="A20" s="2">
-        <v>1018967</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>42</v>
+        <v>8444170</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>56</v>
       </c>
       <c r="C20" s="10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D20" s="17"/>
       <c r="E20" s="17"/>
       <c r="F20" s="11">
+        <f>D20/C20</f>
+        <v>0</v>
+      </c>
+      <c r="G20" s="12">
+        <v>0.1</v>
+      </c>
+      <c r="H20" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G20" s="12">
-        <v>0.18</v>
-      </c>
-      <c r="H20" s="11">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I20" s="11"/>
     </row>
     <row r="21" spans="1:9" s="13" customFormat="1">
       <c r="A21" s="2">
-        <v>8444194</v>
+        <v>9988377</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C21" s="10">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D21" s="17"/>
       <c r="E21" s="17"/>
       <c r="F21" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G21" s="12">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="H21" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G21" s="12">
-        <v>0.1</v>
-      </c>
-      <c r="H21" s="11">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I21" s="11"/>
     </row>
     <row r="22" spans="1:9" s="13" customFormat="1">
       <c r="A22" s="2">
-        <v>8444187</v>
+        <v>9988391</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C22" s="10">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D22" s="17"/>
       <c r="E22" s="17"/>
       <c r="F22" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G22" s="12">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="H22" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G22" s="12">
-        <v>0.1</v>
-      </c>
-      <c r="H22" s="11">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I22" s="11"/>
     </row>
     <row r="23" spans="1:9" s="13" customFormat="1">
       <c r="A23" s="2">
-        <v>8444163</v>
+        <v>5034819</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C23" s="10">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D23" s="17"/>
       <c r="E23" s="17"/>
       <c r="F23" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G23" s="12">
+        <v>0.18</v>
+      </c>
+      <c r="H23" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G23" s="12">
-        <v>0.1</v>
-      </c>
-      <c r="H23" s="11">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I23" s="11"/>
     </row>
     <row r="24" spans="1:9" s="13" customFormat="1">
       <c r="A24" s="2">
-        <v>8444170</v>
+        <v>2981244</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="C24" s="10">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D24" s="17"/>
       <c r="E24" s="17"/>
       <c r="F24" s="11">
-        <f>D24/C24</f>
+        <f>E24/7.8</f>
         <v>0</v>
       </c>
       <c r="G24" s="12">
-        <v>0.1</v>
+        <v>1.3</v>
       </c>
       <c r="H24" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I24" s="11"/>
+        <f>E24</f>
+        <v>0</v>
+      </c>
+      <c r="I24" s="11" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="25" spans="1:9" s="13" customFormat="1">
       <c r="A25" s="2">
-        <v>9988377</v>
+        <v>8785198</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C25" s="10">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D25" s="17"/>
       <c r="E25" s="17"/>
       <c r="F25" s="11">
-        <f t="shared" si="0"/>
+        <f>E25/16.5</f>
         <v>0</v>
       </c>
       <c r="G25" s="12">
-        <v>0.14000000000000001</v>
+        <v>3.2</v>
       </c>
       <c r="H25" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I25" s="11"/>
+        <f>E25</f>
+        <v>0</v>
+      </c>
+      <c r="I25" s="11" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="26" spans="1:9" s="13" customFormat="1">
       <c r="A26" s="2">
-        <v>9988391</v>
+        <v>9988452</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C26" s="10">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D26" s="17"/>
       <c r="E26" s="17"/>
       <c r="F26" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="F26:F37" si="2">D26/C26</f>
         <v>0</v>
       </c>
       <c r="G26" s="12">
-        <v>0.14000000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="H26" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="H26:H31" si="3">G26*D26</f>
         <v>0</v>
       </c>
       <c r="I26" s="11"/>
     </row>
     <row r="27" spans="1:9" s="13" customFormat="1">
       <c r="A27" s="2">
-        <v>5034819</v>
+        <v>9988476</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C27" s="10">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="D27" s="17"/>
       <c r="E27" s="17"/>
       <c r="F27" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G27" s="12">
-        <v>0.18</v>
+        <v>0.4</v>
       </c>
       <c r="H27" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I27" s="11"/>
     </row>
     <row r="28" spans="1:9" s="13" customFormat="1">
       <c r="A28" s="2">
-        <v>2981244</v>
+        <v>9988681</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="C28" s="10">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D28" s="17"/>
       <c r="E28" s="17"/>
       <c r="F28" s="11">
-        <f>E28/7.8</f>
+        <f>D28/C28</f>
         <v>0</v>
       </c>
       <c r="G28" s="12">
-        <v>1.3</v>
+        <v>0.18</v>
       </c>
       <c r="H28" s="11">
-        <f>E28</f>
-        <v>0</v>
-      </c>
-      <c r="I28" s="11" t="s">
-        <v>19</v>
-      </c>
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I28" s="11"/>
     </row>
     <row r="29" spans="1:9" s="13" customFormat="1">
       <c r="A29" s="2">
-        <v>8785198</v>
+        <v>9988438</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C29" s="10">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D29" s="17"/>
       <c r="E29" s="17"/>
       <c r="F29" s="11">
-        <f>E29/16.5</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G29" s="12">
-        <v>3.2</v>
+        <v>0.18</v>
       </c>
       <c r="H29" s="11">
-        <f>E29</f>
-        <v>0</v>
-      </c>
-      <c r="I29" s="11" t="s">
-        <v>15</v>
-      </c>
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I29" s="11"/>
     </row>
     <row r="30" spans="1:9" s="13" customFormat="1">
       <c r="A30" s="2">
-        <v>9988452</v>
+        <v>9988445</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C30" s="10">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D30" s="17"/>
       <c r="E30" s="17"/>
       <c r="F30" s="11">
-        <f t="shared" ref="F30:F43" si="2">D30/C30</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G30" s="12">
-        <v>0.4</v>
+        <v>0.18</v>
       </c>
       <c r="H30" s="11">
-        <f t="shared" ref="H30:H35" si="3">G30*D30</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I30" s="11"/>
     </row>
     <row r="31" spans="1:9" s="13" customFormat="1">
       <c r="A31" s="2">
-        <v>9988476</v>
+        <v>9988421</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C31" s="10">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="D31" s="17"/>
       <c r="E31" s="17"/>
@@ -1696,7 +1660,7 @@
         <v>0</v>
       </c>
       <c r="G31" s="12">
-        <v>0.4</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="H31" s="11">
         <f t="shared" si="3"/>
@@ -1706,10 +1670,10 @@
     </row>
     <row r="32" spans="1:9" s="13" customFormat="1">
       <c r="A32" s="2">
-        <v>9988681</v>
+        <v>9988674</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C32" s="10">
         <v>16</v>
@@ -1717,27 +1681,27 @@
       <c r="D32" s="17"/>
       <c r="E32" s="17"/>
       <c r="F32" s="11">
-        <f>D32/C32</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G32" s="12">
         <v>0.18</v>
       </c>
       <c r="H32" s="11">
-        <f t="shared" si="3"/>
+        <f>D32*G32</f>
         <v>0</v>
       </c>
       <c r="I32" s="11"/>
     </row>
     <row r="33" spans="1:9" s="13" customFormat="1">
-      <c r="A33" s="2">
-        <v>9988438</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>30</v>
+      <c r="A33" s="26">
+        <v>8444903</v>
+      </c>
+      <c r="B33" s="27" t="s">
+        <v>45</v>
       </c>
       <c r="C33" s="10">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D33" s="17"/>
       <c r="E33" s="17"/>
@@ -1746,23 +1710,23 @@
         <v>0</v>
       </c>
       <c r="G33" s="12">
-        <v>0.18</v>
+        <v>0.1</v>
       </c>
       <c r="H33" s="11">
-        <f t="shared" si="3"/>
+        <f>D33*G33</f>
         <v>0</v>
       </c>
       <c r="I33" s="11"/>
     </row>
     <row r="34" spans="1:9" s="13" customFormat="1">
-      <c r="A34" s="2">
-        <v>9988445</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>31</v>
+      <c r="A34" s="26">
+        <v>8444910</v>
+      </c>
+      <c r="B34" s="27" t="s">
+        <v>46</v>
       </c>
       <c r="C34" s="10">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D34" s="17"/>
       <c r="E34" s="17"/>
@@ -1771,23 +1735,23 @@
         <v>0</v>
       </c>
       <c r="G34" s="12">
-        <v>0.18</v>
+        <v>0.1</v>
       </c>
       <c r="H34" s="11">
-        <f t="shared" si="3"/>
+        <f>D34*G34</f>
         <v>0</v>
       </c>
       <c r="I34" s="11"/>
     </row>
     <row r="35" spans="1:9" s="13" customFormat="1">
-      <c r="A35" s="2">
-        <v>9988421</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>32</v>
+      <c r="A35" s="26">
+        <v>8444927</v>
+      </c>
+      <c r="B35" s="27" t="s">
+        <v>47</v>
       </c>
       <c r="C35" s="10">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D35" s="17"/>
       <c r="E35" s="17"/>
@@ -1796,23 +1760,23 @@
         <v>0</v>
       </c>
       <c r="G35" s="12">
-        <v>0.14000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="H35" s="11">
-        <f t="shared" si="3"/>
+        <f>D35*G35</f>
         <v>0</v>
       </c>
       <c r="I35" s="11"/>
     </row>
     <row r="36" spans="1:9" s="13" customFormat="1">
       <c r="A36" s="2">
-        <v>9988674</v>
+        <v>8445160</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="C36" s="10">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D36" s="17"/>
       <c r="E36" s="17"/>
@@ -1821,20 +1785,20 @@
         <v>0</v>
       </c>
       <c r="G36" s="12">
-        <v>0.18</v>
+        <v>0.1</v>
       </c>
       <c r="H36" s="11">
-        <f t="shared" ref="H36:H43" si="4">D36*G36</f>
+        <f>G36*D36</f>
         <v>0</v>
       </c>
       <c r="I36" s="11"/>
     </row>
     <row r="37" spans="1:9" s="13" customFormat="1">
-      <c r="A37" s="30">
-        <v>8444903</v>
-      </c>
-      <c r="B37" s="31" t="s">
-        <v>49</v>
+      <c r="A37" s="2">
+        <v>8445177</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>65</v>
       </c>
       <c r="C37" s="10">
         <v>8</v>
@@ -1849,79 +1813,81 @@
         <v>0.1</v>
       </c>
       <c r="H37" s="11">
-        <f t="shared" si="4"/>
+        <f>G37*D37</f>
         <v>0</v>
       </c>
       <c r="I37" s="11"/>
     </row>
     <row r="38" spans="1:9" s="13" customFormat="1">
-      <c r="A38" s="30">
-        <v>8444910</v>
-      </c>
-      <c r="B38" s="31" t="s">
-        <v>50</v>
+      <c r="A38" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>13</v>
       </c>
       <c r="C38" s="10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D38" s="17"/>
       <c r="E38" s="17"/>
       <c r="F38" s="11">
-        <f t="shared" si="2"/>
+        <f>D38/C38</f>
         <v>0</v>
       </c>
       <c r="G38" s="12">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H38" s="11">
-        <f t="shared" si="4"/>
+        <f>G38*D38</f>
         <v>0</v>
       </c>
       <c r="I38" s="11"/>
     </row>
     <row r="39" spans="1:9" s="13" customFormat="1">
-      <c r="A39" s="30">
-        <v>8444927</v>
-      </c>
-      <c r="B39" s="31" t="s">
-        <v>51</v>
+      <c r="A39" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>16</v>
       </c>
       <c r="C39" s="10">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D39" s="17"/>
       <c r="E39" s="17"/>
       <c r="F39" s="11">
-        <f t="shared" si="2"/>
+        <f>E39/15</f>
         <v>0</v>
       </c>
       <c r="G39" s="12">
-        <v>0.1</v>
+        <v>3.5</v>
       </c>
       <c r="H39" s="11">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I39" s="11"/>
-    </row>
-    <row r="40" spans="1:9" s="36" customFormat="1">
-      <c r="A40" s="15">
-        <v>8445160</v>
-      </c>
-      <c r="B40" s="16" t="s">
-        <v>70</v>
+        <f>E39</f>
+        <v>0</v>
+      </c>
+      <c r="I39" s="11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" s="29" customFormat="1">
+      <c r="A40" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B40" s="12" t="s">
+        <v>14</v>
       </c>
       <c r="C40" s="10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D40" s="17"/>
       <c r="E40" s="17"/>
       <c r="F40" s="11">
-        <f t="shared" si="2"/>
+        <f>D40/C40</f>
         <v>0</v>
       </c>
       <c r="G40" s="12">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H40" s="11">
         <f>G40*D40</f>
@@ -1929,94 +1895,94 @@
       </c>
       <c r="I40" s="11"/>
     </row>
-    <row r="41" spans="1:9" s="36" customFormat="1" ht="11.25" customHeight="1">
-      <c r="A41" s="15">
-        <v>8445177</v>
-      </c>
-      <c r="B41" s="16" t="s">
-        <v>71</v>
+    <row r="41" spans="1:9" s="29" customFormat="1" ht="11.25" customHeight="1">
+      <c r="A41" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B41" s="12" t="s">
+        <v>17</v>
       </c>
       <c r="C41" s="10">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D41" s="17"/>
       <c r="E41" s="17"/>
       <c r="F41" s="11">
-        <f t="shared" si="2"/>
+        <f>E41/15</f>
         <v>0</v>
       </c>
       <c r="G41" s="12">
-        <v>0.1</v>
+        <v>3.5</v>
       </c>
       <c r="H41" s="11">
-        <f>G41*D41</f>
-        <v>0</v>
-      </c>
-      <c r="I41" s="11"/>
+        <f>E41</f>
+        <v>0</v>
+      </c>
+      <c r="I41" s="11" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="42" spans="1:9" s="13" customFormat="1">
-      <c r="A42" s="30">
-        <v>6600454</v>
-      </c>
-      <c r="B42" s="31" t="s">
-        <v>54</v>
-      </c>
-      <c r="C42" s="32">
+      <c r="A42" s="2">
+        <v>7100108</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C42" s="10">
         <v>12</v>
       </c>
-      <c r="D42" s="33"/>
-      <c r="E42" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="F42" s="34">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G42" s="35">
-        <v>0.125</v>
-      </c>
-      <c r="H42" s="34">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I42" s="34"/>
+      <c r="D42" s="17"/>
+      <c r="E42" s="17"/>
+      <c r="F42" s="11">
+        <f>D42/C42</f>
+        <v>0</v>
+      </c>
+      <c r="G42" s="12">
+        <v>0.2</v>
+      </c>
+      <c r="H42" s="11">
+        <f>D42*G42</f>
+        <v>0</v>
+      </c>
+      <c r="I42" s="11"/>
     </row>
     <row r="43" spans="1:9" s="13" customFormat="1">
-      <c r="A43" s="30">
-        <v>6600447</v>
-      </c>
-      <c r="B43" s="31" t="s">
-        <v>53</v>
-      </c>
-      <c r="C43" s="32">
+      <c r="A43" s="2">
+        <v>7100139</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C43" s="10">
+        <v>8</v>
+      </c>
+      <c r="D43" s="17"/>
+      <c r="E43" s="17"/>
+      <c r="F43" s="11">
+        <f>E43/20</f>
+        <v>0</v>
+      </c>
+      <c r="G43" s="12">
+        <v>2.5</v>
+      </c>
+      <c r="H43" s="11">
+        <f>E43</f>
+        <v>0</v>
+      </c>
+      <c r="I43" s="11" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" s="13" customFormat="1">
+      <c r="A44" s="2">
+        <v>7100740</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C44" s="10">
         <v>12</v>
-      </c>
-      <c r="D43" s="33"/>
-      <c r="E43" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="F43" s="34">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G43" s="35">
-        <v>0.125</v>
-      </c>
-      <c r="H43" s="34">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I43" s="34"/>
-    </row>
-    <row r="44" spans="1:9" s="13" customFormat="1">
-      <c r="A44" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B44" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="C44" s="10">
-        <v>10</v>
       </c>
       <c r="D44" s="17"/>
       <c r="E44" s="17"/>
@@ -2028,47 +1994,47 @@
         <v>0.2</v>
       </c>
       <c r="H44" s="11">
-        <f>G44*D44</f>
+        <f>D44*G44</f>
         <v>0</v>
       </c>
       <c r="I44" s="11"/>
     </row>
     <row r="45" spans="1:9" s="13" customFormat="1">
-      <c r="A45" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B45" s="12" t="s">
-        <v>16</v>
+      <c r="A45" s="2">
+        <v>7100726</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>70</v>
       </c>
       <c r="C45" s="10">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D45" s="17"/>
       <c r="E45" s="17"/>
       <c r="F45" s="11">
-        <f>E45/15</f>
+        <f>E45/20</f>
         <v>0</v>
       </c>
       <c r="G45" s="12">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="H45" s="11">
         <f>E45</f>
         <v>0</v>
       </c>
       <c r="I45" s="11" t="s">
-        <v>18</v>
+        <v>68</v>
       </c>
     </row>
     <row r="46" spans="1:9" s="13" customFormat="1">
-      <c r="A46" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B46" s="12" t="s">
-        <v>14</v>
+      <c r="A46" s="2">
+        <v>4421584</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>54</v>
       </c>
       <c r="C46" s="10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D46" s="17"/>
       <c r="E46" s="17"/>
@@ -2077,7 +2043,7 @@
         <v>0</v>
       </c>
       <c r="G46" s="12">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="H46" s="11">
         <f>G46*D46</f>
@@ -2086,41 +2052,39 @@
       <c r="I46" s="11"/>
     </row>
     <row r="47" spans="1:9" s="13" customFormat="1">
-      <c r="A47" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B47" s="12" t="s">
-        <v>17</v>
+      <c r="A47" s="2">
+        <v>4421577</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>53</v>
       </c>
       <c r="C47" s="10">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D47" s="17"/>
       <c r="E47" s="17"/>
       <c r="F47" s="11">
-        <f>E47/15</f>
+        <f>D47/C47</f>
         <v>0</v>
       </c>
       <c r="G47" s="12">
-        <v>3.5</v>
+        <v>0.18</v>
       </c>
       <c r="H47" s="11">
-        <f>E47</f>
-        <v>0</v>
-      </c>
-      <c r="I47" s="11" t="s">
-        <v>18</v>
-      </c>
+        <f>G47*D47</f>
+        <v>0</v>
+      </c>
+      <c r="I47" s="11"/>
     </row>
     <row r="48" spans="1:9" s="13" customFormat="1">
       <c r="A48" s="2">
-        <v>7100108</v>
+        <v>9985949</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="C48" s="10">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D48" s="17"/>
       <c r="E48" s="17"/>
@@ -2128,48 +2092,48 @@
         <f>D48/C48</f>
         <v>0</v>
       </c>
-      <c r="G48" s="12">
-        <v>0.2</v>
+      <c r="G48" s="18">
+        <v>1</v>
       </c>
       <c r="H48" s="11">
-        <f>D48*G48</f>
+        <f>G48*D48</f>
         <v>0</v>
       </c>
       <c r="I48" s="11"/>
     </row>
     <row r="49" spans="1:9" s="13" customFormat="1">
       <c r="A49" s="2">
-        <v>7100139</v>
+        <v>8786928</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="C49" s="10">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D49" s="17"/>
       <c r="E49" s="17"/>
       <c r="F49" s="11">
-        <f>E49/20</f>
+        <f>E49/6</f>
         <v>0</v>
       </c>
       <c r="G49" s="12">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="H49" s="11">
         <f>E49</f>
         <v>0</v>
       </c>
       <c r="I49" s="11" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
     </row>
     <row r="50" spans="1:9" s="13" customFormat="1">
       <c r="A50" s="2">
-        <v>7100740</v>
+        <v>6948270</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="C50" s="10">
         <v>12</v>
@@ -2177,51 +2141,49 @@
       <c r="D50" s="17"/>
       <c r="E50" s="17"/>
       <c r="F50" s="11">
-        <f>D50/C50</f>
+        <f t="shared" ref="F50:F57" si="4">D50/C50</f>
         <v>0</v>
       </c>
       <c r="G50" s="12">
-        <v>0.2</v>
+        <v>0.372</v>
       </c>
       <c r="H50" s="11">
-        <f>D50*G50</f>
+        <f t="shared" ref="H50:H57" si="5">G50*D50</f>
         <v>0</v>
       </c>
       <c r="I50" s="11"/>
     </row>
     <row r="51" spans="1:9" s="13" customFormat="1">
       <c r="A51" s="2">
-        <v>7100726</v>
+        <v>6948287</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="C51" s="10">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D51" s="17"/>
       <c r="E51" s="17"/>
       <c r="F51" s="11">
-        <f>E51/20</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G51" s="12">
-        <v>2.5</v>
+        <v>0.74399999999999999</v>
       </c>
       <c r="H51" s="11">
-        <f>E51</f>
-        <v>0</v>
-      </c>
-      <c r="I51" s="11" t="s">
-        <v>74</v>
-      </c>
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I51" s="11"/>
     </row>
     <row r="52" spans="1:9" s="13" customFormat="1">
       <c r="A52" s="2">
-        <v>4421584</v>
+        <v>6948256</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C52" s="10">
         <v>12</v>
@@ -2229,24 +2191,24 @@
       <c r="D52" s="17"/>
       <c r="E52" s="17"/>
       <c r="F52" s="11">
-        <f>D52/C52</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G52" s="12">
-        <v>0.18</v>
+        <v>0.372</v>
       </c>
       <c r="H52" s="11">
-        <f>G52*D52</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="I52" s="11"/>
     </row>
     <row r="53" spans="1:9" s="13" customFormat="1">
       <c r="A53" s="2">
-        <v>4421577</v>
+        <v>6948263</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C53" s="10">
         <v>12</v>
@@ -2254,210 +2216,133 @@
       <c r="D53" s="17"/>
       <c r="E53" s="17"/>
       <c r="F53" s="11">
-        <f>D53/C53</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G53" s="12">
-        <v>0.18</v>
+        <v>0.74399999999999999</v>
       </c>
       <c r="H53" s="11">
-        <f>G53*D53</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="I53" s="11"/>
     </row>
     <row r="54" spans="1:9" s="13" customFormat="1">
       <c r="A54" s="2">
-        <v>9985949</v>
+        <v>6948249</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C54" s="10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D54" s="17"/>
       <c r="E54" s="17"/>
       <c r="F54" s="11">
-        <f>D54/C54</f>
-        <v>0</v>
-      </c>
-      <c r="G54" s="18">
-        <v>1</v>
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G54" s="12">
+        <v>0.82499999999999996</v>
       </c>
       <c r="H54" s="11">
-        <f>G54*D54</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="I54" s="11"/>
     </row>
     <row r="55" spans="1:9" s="13" customFormat="1">
-      <c r="A55" s="2">
-        <v>8786928</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>63</v>
+      <c r="A55" s="15">
+        <v>2105201</v>
+      </c>
+      <c r="B55" s="16" t="s">
+        <v>74</v>
       </c>
       <c r="C55" s="10">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="D55" s="17"/>
       <c r="E55" s="17"/>
       <c r="F55" s="11">
-        <f>E55/6</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G55" s="12">
-        <v>1.5</v>
+        <v>0.1</v>
       </c>
       <c r="H55" s="11">
-        <f>E55</f>
-        <v>0</v>
-      </c>
-      <c r="I55" s="11" t="s">
-        <v>64</v>
-      </c>
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I55" s="11"/>
     </row>
     <row r="56" spans="1:9" s="13" customFormat="1">
-      <c r="A56" s="2">
-        <v>6948270</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>65</v>
+      <c r="A56" s="15">
+        <v>2103201</v>
+      </c>
+      <c r="B56" s="16" t="s">
+        <v>75</v>
       </c>
       <c r="C56" s="10">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D56" s="17"/>
       <c r="E56" s="17"/>
       <c r="F56" s="11">
-        <f>D56/C56</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G56" s="12">
-        <v>0.372</v>
+        <v>0.1</v>
       </c>
       <c r="H56" s="11">
-        <f>G56*D56</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="I56" s="11"/>
     </row>
     <row r="57" spans="1:9" s="13" customFormat="1">
-      <c r="A57" s="2">
-        <v>6948287</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>66</v>
+      <c r="A57" s="15">
+        <v>1103201</v>
+      </c>
+      <c r="B57" s="16" t="s">
+        <v>76</v>
       </c>
       <c r="C57" s="10">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="D57" s="17"/>
       <c r="E57" s="17"/>
       <c r="F57" s="11">
-        <f>D57/C57</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G57" s="12">
-        <v>0.74399999999999999</v>
+        <v>5.5E-2</v>
       </c>
       <c r="H57" s="11">
-        <f>G57*D57</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="I57" s="11"/>
     </row>
     <row r="58" spans="1:9" s="13" customFormat="1">
-      <c r="A58" s="2">
-        <v>6948256</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C58" s="10">
-        <v>12</v>
-      </c>
+      <c r="A58" s="11"/>
+      <c r="B58" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C58" s="11"/>
       <c r="D58" s="17"/>
       <c r="E58" s="17"/>
-      <c r="F58" s="11">
-        <f>D58/C58</f>
-        <v>0</v>
-      </c>
-      <c r="G58" s="12">
-        <v>0.372</v>
-      </c>
-      <c r="H58" s="11">
-        <f>G58*D58</f>
+      <c r="F58" s="11"/>
+      <c r="G58" s="11"/>
+      <c r="H58" s="3">
+        <f>SUM(H4:H57)</f>
         <v>0</v>
       </c>
       <c r="I58" s="11"/>
-    </row>
-    <row r="59" spans="1:9" s="13" customFormat="1">
-      <c r="A59" s="2">
-        <v>6948263</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C59" s="10">
-        <v>12</v>
-      </c>
-      <c r="D59" s="17"/>
-      <c r="E59" s="17"/>
-      <c r="F59" s="11">
-        <f>D59/C59</f>
-        <v>0</v>
-      </c>
-      <c r="G59" s="12">
-        <v>0.74399999999999999</v>
-      </c>
-      <c r="H59" s="11">
-        <f>G59*D59</f>
-        <v>0</v>
-      </c>
-      <c r="I59" s="11"/>
-    </row>
-    <row r="60" spans="1:9">
-      <c r="A60" s="2">
-        <v>6948249</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C60" s="10">
-        <v>12</v>
-      </c>
-      <c r="D60" s="17"/>
-      <c r="E60" s="17"/>
-      <c r="F60" s="11">
-        <f>D60/C60</f>
-        <v>0</v>
-      </c>
-      <c r="G60" s="12">
-        <v>0.82499999999999996</v>
-      </c>
-      <c r="H60" s="11">
-        <f>G60*D60</f>
-        <v>0</v>
-      </c>
-      <c r="I60" s="11"/>
-    </row>
-    <row r="61" spans="1:9">
-      <c r="A61" s="11"/>
-      <c r="B61" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C61" s="11"/>
-      <c r="D61" s="17"/>
-      <c r="E61" s="17"/>
-      <c r="F61" s="11"/>
-      <c r="G61" s="11"/>
-      <c r="H61" s="3">
-        <f>SUM(H4:H60)</f>
-        <v>0</v>
-      </c>
-      <c r="I61" s="11"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
@@ -2473,7 +2358,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="10" style="4" customWidth="1"/>
@@ -2501,7 +2386,7 @@
     </row>
     <row r="2" spans="1:9" ht="38.25">
       <c r="A2" s="7" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>12</v>
@@ -2519,25 +2404,25 @@
       <c r="I2" s="7"/>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="37" t="s">
+      <c r="A3" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="37" t="s">
+      <c r="C3" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="38" t="s">
+      <c r="D3" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="38" t="s">
+      <c r="E3" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="37" t="s">
+      <c r="F3" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="39" t="s">
+      <c r="G3" s="32" t="s">
         <v>10</v>
       </c>
       <c r="H3" s="11" t="s">
@@ -2572,207 +2457,203 @@
       </c>
       <c r="I4" s="11"/>
     </row>
-    <row r="5" spans="1:9" s="13" customFormat="1">
-      <c r="A5" s="1">
-        <v>8785204</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="C5" s="10">
+    <row r="5" spans="1:9" s="13" customFormat="1" ht="25.5">
+      <c r="A5" s="33">
+        <v>8783323</v>
+      </c>
+      <c r="B5" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" s="28">
+        <v>4</v>
+      </c>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="11">
+        <f>E5/5</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="22">
+        <v>1.8</v>
+      </c>
+      <c r="H5" s="21">
+        <f>E5</f>
+        <v>0</v>
+      </c>
+      <c r="I5" s="21"/>
+    </row>
+    <row r="6" spans="1:9" s="23" customFormat="1" ht="25.5">
+      <c r="A6" s="1">
+        <v>5038459</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="10">
+        <v>10</v>
+      </c>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="11">
+        <f>D6/C6</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="12">
+        <v>0.18</v>
+      </c>
+      <c r="H6" s="11">
+        <f>G6*D6</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="11"/>
+    </row>
+    <row r="7" spans="1:9" s="13" customFormat="1" ht="25.5">
+      <c r="A7" s="33">
+        <v>8785235</v>
+      </c>
+      <c r="B7" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7" s="10">
         <v>5</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="E5" s="17"/>
-      <c r="F5" s="11">
-        <f>E5/16.5</f>
-        <v>0</v>
-      </c>
-      <c r="G5" s="12">
-        <v>3.2</v>
-      </c>
-      <c r="H5" s="11">
-        <f>E5</f>
-        <v>0</v>
-      </c>
-      <c r="I5" s="11"/>
-    </row>
-    <row r="6" spans="1:9" s="26" customFormat="1" ht="25.5">
-      <c r="A6" s="20">
-        <v>8783323</v>
-      </c>
-      <c r="B6" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="C6" s="22">
-        <v>4</v>
-      </c>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="11">
-        <f>E6/5</f>
-        <v>0</v>
-      </c>
-      <c r="G6" s="25">
-        <v>1.8</v>
-      </c>
-      <c r="H6" s="24">
-        <f>E6</f>
-        <v>0</v>
-      </c>
-      <c r="I6" s="24"/>
-    </row>
-    <row r="7" spans="1:9" s="13" customFormat="1" ht="25.5">
-      <c r="A7" s="1">
-        <v>5038459</v>
-      </c>
-      <c r="B7" s="19" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" s="10">
-        <v>10</v>
       </c>
       <c r="D7" s="17"/>
       <c r="E7" s="17"/>
       <c r="F7" s="11">
-        <f>D7/C7</f>
-        <v>0</v>
-      </c>
-      <c r="G7" s="12">
-        <v>0.18</v>
+        <f>E7/16.5</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="11">
+        <v>3.5</v>
       </c>
       <c r="H7" s="11">
-        <f>G7*D7</f>
-        <v>0</v>
-      </c>
-      <c r="I7" s="11"/>
+        <f>E7</f>
+        <v>0</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="8" spans="1:9" s="13" customFormat="1" ht="25.5">
-      <c r="A8" s="20">
-        <v>8785235</v>
-      </c>
-      <c r="B8" s="21" t="s">
-        <v>79</v>
+      <c r="A8" s="1">
+        <v>5038411</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>34</v>
       </c>
       <c r="C8" s="10">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D8" s="17"/>
       <c r="E8" s="17"/>
       <c r="F8" s="11">
-        <f>E8/16.5</f>
-        <v>0</v>
-      </c>
-      <c r="G8" s="11">
-        <v>3.5</v>
+        <f>D8/C8</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="12">
+        <v>0.18</v>
       </c>
       <c r="H8" s="11">
-        <f>E8</f>
-        <v>0</v>
-      </c>
-      <c r="I8" s="11" t="s">
-        <v>15</v>
-      </c>
+        <f>G8*D8</f>
+        <v>0</v>
+      </c>
+      <c r="I8" s="11"/>
     </row>
     <row r="9" spans="1:9" s="13" customFormat="1" ht="25.5">
-      <c r="A9" s="1">
-        <v>5038411</v>
+      <c r="A9" s="2">
+        <v>8785242</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="C9" s="10">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D9" s="17"/>
       <c r="E9" s="17"/>
       <c r="F9" s="11">
-        <f>D9/C9</f>
-        <v>0</v>
-      </c>
-      <c r="G9" s="12">
-        <v>0.18</v>
+        <f>E9/16.5</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="11">
+        <v>3.5</v>
       </c>
       <c r="H9" s="11">
-        <f>G9*D9</f>
-        <v>0</v>
-      </c>
-      <c r="I9" s="11"/>
+        <f>E9</f>
+        <v>0</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="10" spans="1:9" s="13" customFormat="1" ht="25.5">
-      <c r="A10" s="2">
-        <v>8785242</v>
+      <c r="A10" s="1">
+        <v>5038398</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C10" s="10">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D10" s="17"/>
       <c r="E10" s="17"/>
       <c r="F10" s="11">
-        <f>E10/16.5</f>
-        <v>0</v>
-      </c>
-      <c r="G10" s="11">
-        <v>3.5</v>
+        <f>D10/C10</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="12">
+        <v>0.18</v>
       </c>
       <c r="H10" s="11">
-        <f>E10</f>
-        <v>0</v>
-      </c>
-      <c r="I10" s="11" t="s">
-        <v>15</v>
-      </c>
+        <f>G10*D10</f>
+        <v>0</v>
+      </c>
+      <c r="I10" s="11"/>
     </row>
     <row r="11" spans="1:9" s="13" customFormat="1" ht="25.5">
-      <c r="A11" s="1">
-        <v>5038398</v>
+      <c r="A11" s="2">
+        <v>8785259</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="C11" s="10">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D11" s="17"/>
       <c r="E11" s="17"/>
       <c r="F11" s="11">
-        <f>D11/C11</f>
-        <v>0</v>
-      </c>
-      <c r="G11" s="12">
-        <v>0.18</v>
+        <f>E11/16.5</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="11">
+        <v>3.5</v>
       </c>
       <c r="H11" s="11">
-        <f>G11*D11</f>
+        <f>E11</f>
         <v>0</v>
       </c>
       <c r="I11" s="11"/>
     </row>
-    <row r="12" spans="1:9" s="13" customFormat="1">
-      <c r="A12" s="1">
-        <v>5039609</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>43</v>
+    <row r="12" spans="1:9" s="13" customFormat="1" ht="25.5">
+      <c r="A12" s="2">
+        <v>5038855</v>
+      </c>
+      <c r="B12" s="24" t="s">
+        <v>41</v>
       </c>
       <c r="C12" s="10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D12" s="17"/>
-      <c r="E12" s="17" t="s">
-        <v>77</v>
-      </c>
+      <c r="E12" s="17"/>
       <c r="F12" s="11">
         <f>D12/C12</f>
         <v>0</v>
       </c>
       <c r="G12" s="12">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="H12" s="11">
         <f>G12*D12</f>
@@ -2782,471 +2663,469 @@
     </row>
     <row r="13" spans="1:9" s="13" customFormat="1" ht="25.5">
       <c r="A13" s="2">
-        <v>8785259</v>
+        <v>5038831</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="C13" s="10">
-        <v>5</v>
+        <v>39</v>
+      </c>
+      <c r="C13" s="25">
+        <v>10</v>
       </c>
       <c r="D13" s="17"/>
       <c r="E13" s="17"/>
       <c r="F13" s="11">
-        <f>E13/16.5</f>
-        <v>0</v>
-      </c>
-      <c r="G13" s="11">
-        <v>3.5</v>
+        <f>D13/C13</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="12">
+        <v>0.18</v>
       </c>
       <c r="H13" s="11">
-        <f>E13</f>
+        <f>G13*D13</f>
         <v>0</v>
       </c>
       <c r="I13" s="11"/>
     </row>
-    <row r="14" spans="1:9" s="13" customFormat="1" ht="25.5">
-      <c r="A14" s="2">
-        <v>5038855</v>
-      </c>
-      <c r="B14" s="27" t="s">
-        <v>41</v>
-      </c>
-      <c r="C14" s="10">
-        <v>10</v>
+    <row r="14" spans="1:9" s="13" customFormat="1" ht="38.25">
+      <c r="A14" s="26">
+        <v>8784931</v>
+      </c>
+      <c r="B14" s="34" t="s">
+        <v>73</v>
+      </c>
+      <c r="C14" s="25">
+        <v>5</v>
       </c>
       <c r="D14" s="17"/>
       <c r="E14" s="17"/>
       <c r="F14" s="11">
-        <f t="shared" ref="F14:F27" si="0">D14/C14</f>
+        <f>E14/16.5</f>
         <v>0</v>
       </c>
       <c r="G14" s="12">
-        <v>0.2</v>
+        <v>3.5</v>
       </c>
       <c r="H14" s="11">
-        <f>G14*D14</f>
-        <v>0</v>
-      </c>
-      <c r="I14" s="11"/>
+        <f>E14</f>
+        <v>0</v>
+      </c>
+      <c r="I14" s="11" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="15" spans="1:9" s="13" customFormat="1">
       <c r="A15" s="2">
-        <v>5039647</v>
-      </c>
-      <c r="B15" s="28" t="s">
-        <v>44</v>
+        <v>1018950</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>40</v>
       </c>
       <c r="C15" s="10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D15" s="17"/>
       <c r="E15" s="17"/>
       <c r="F15" s="11">
-        <f t="shared" si="0"/>
+        <f>D15/C15</f>
         <v>0</v>
       </c>
       <c r="G15" s="12">
-        <v>0.4</v>
+        <v>0.18</v>
       </c>
       <c r="H15" s="11">
-        <f>G15*D15</f>
+        <f t="shared" ref="H15:H23" si="0">G15*D15</f>
         <v>0</v>
       </c>
       <c r="I15" s="11"/>
     </row>
-    <row r="16" spans="1:9" s="13" customFormat="1" ht="25.5">
+    <row r="16" spans="1:9" s="13" customFormat="1">
       <c r="A16" s="2">
-        <v>5038831</v>
-      </c>
-      <c r="B16" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="C16" s="29">
+        <v>1018967</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" s="10">
         <v>10</v>
       </c>
       <c r="D16" s="17"/>
       <c r="E16" s="17"/>
       <c r="F16" s="11">
-        <f t="shared" si="0"/>
+        <f>D16/C16</f>
         <v>0</v>
       </c>
       <c r="G16" s="12">
         <v>0.18</v>
       </c>
       <c r="H16" s="11">
-        <f>G16*D16</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I16" s="11"/>
     </row>
     <row r="17" spans="1:9" s="13" customFormat="1">
       <c r="A17" s="2">
-        <v>5039623</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="C17" s="29">
-        <v>8</v>
+        <v>8444194</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="10">
+        <v>6</v>
       </c>
       <c r="D17" s="17"/>
-      <c r="E17" s="17" t="s">
-        <v>77</v>
-      </c>
+      <c r="E17" s="17"/>
       <c r="F17" s="11">
+        <f t="shared" ref="F17:F23" si="1">D17/C17</f>
+        <v>0</v>
+      </c>
+      <c r="G17" s="12">
+        <v>0.1</v>
+      </c>
+      <c r="H17" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G17" s="12">
-        <v>0.4</v>
-      </c>
-      <c r="H17" s="11">
-        <f>G17*D17</f>
-        <v>0</v>
-      </c>
       <c r="I17" s="11"/>
     </row>
-    <row r="18" spans="1:9" s="13" customFormat="1" ht="38.25">
-      <c r="A18" s="15">
-        <v>8784931</v>
-      </c>
-      <c r="B18" s="21" t="s">
-        <v>80</v>
-      </c>
-      <c r="C18" s="29">
-        <v>5</v>
+    <row r="18" spans="1:9" s="13" customFormat="1">
+      <c r="A18" s="2">
+        <v>8444187</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" s="10">
+        <v>6</v>
       </c>
       <c r="D18" s="17"/>
       <c r="E18" s="17"/>
       <c r="F18" s="11">
-        <f>E18/16.4</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G18" s="12">
-        <v>3.5</v>
+        <v>0.1</v>
       </c>
       <c r="H18" s="11">
-        <f>E18</f>
-        <v>0</v>
-      </c>
-      <c r="I18" s="11" t="s">
-        <v>81</v>
-      </c>
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I18" s="11"/>
     </row>
     <row r="19" spans="1:9" s="13" customFormat="1">
       <c r="A19" s="2">
-        <v>1018950</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>40</v>
+        <v>8444163</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>22</v>
       </c>
       <c r="C19" s="10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D19" s="17"/>
       <c r="E19" s="17"/>
       <c r="F19" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G19" s="12">
+        <v>0.1</v>
+      </c>
+      <c r="H19" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G19" s="12">
-        <v>0.18</v>
-      </c>
-      <c r="H19" s="11">
-        <f t="shared" ref="H19:H27" si="1">G19*D19</f>
         <v>0</v>
       </c>
       <c r="I19" s="11"/>
     </row>
     <row r="20" spans="1:9" s="13" customFormat="1">
       <c r="A20" s="2">
-        <v>1018967</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>42</v>
+        <v>8444170</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>56</v>
       </c>
       <c r="C20" s="10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D20" s="17"/>
       <c r="E20" s="17"/>
       <c r="F20" s="11">
+        <f>D20/C20</f>
+        <v>0</v>
+      </c>
+      <c r="G20" s="12">
+        <v>0.1</v>
+      </c>
+      <c r="H20" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G20" s="12">
-        <v>0.18</v>
-      </c>
-      <c r="H20" s="11">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I20" s="11"/>
     </row>
     <row r="21" spans="1:9" s="13" customFormat="1">
       <c r="A21" s="2">
-        <v>8444194</v>
+        <v>9988377</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C21" s="10">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D21" s="17"/>
       <c r="E21" s="17"/>
       <c r="F21" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G21" s="12">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="H21" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G21" s="12">
-        <v>0.1</v>
-      </c>
-      <c r="H21" s="11">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I21" s="11"/>
     </row>
     <row r="22" spans="1:9" s="13" customFormat="1">
       <c r="A22" s="2">
-        <v>8444187</v>
+        <v>9988391</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C22" s="10">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D22" s="17"/>
       <c r="E22" s="17"/>
       <c r="F22" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G22" s="12">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="H22" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G22" s="12">
-        <v>0.1</v>
-      </c>
-      <c r="H22" s="11">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I22" s="11"/>
     </row>
     <row r="23" spans="1:9" s="13" customFormat="1">
       <c r="A23" s="2">
-        <v>8444163</v>
+        <v>5034819</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C23" s="10">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D23" s="17"/>
       <c r="E23" s="17"/>
       <c r="F23" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G23" s="12">
+        <v>0.18</v>
+      </c>
+      <c r="H23" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G23" s="12">
-        <v>0.1</v>
-      </c>
-      <c r="H23" s="11">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I23" s="11"/>
     </row>
     <row r="24" spans="1:9" s="13" customFormat="1">
       <c r="A24" s="2">
-        <v>8444170</v>
+        <v>2981244</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="C24" s="10">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D24" s="17"/>
       <c r="E24" s="17"/>
       <c r="F24" s="11">
-        <f>D24/C24</f>
+        <f>E24/7.8</f>
         <v>0</v>
       </c>
       <c r="G24" s="12">
-        <v>0.1</v>
+        <v>1.3</v>
       </c>
       <c r="H24" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I24" s="11"/>
+        <f>E24</f>
+        <v>0</v>
+      </c>
+      <c r="I24" s="11" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="25" spans="1:9" s="13" customFormat="1">
       <c r="A25" s="2">
-        <v>9988377</v>
+        <v>8785198</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C25" s="10">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D25" s="17"/>
       <c r="E25" s="17"/>
       <c r="F25" s="11">
-        <f t="shared" si="0"/>
+        <f>E25/16.5</f>
         <v>0</v>
       </c>
       <c r="G25" s="12">
-        <v>0.14000000000000001</v>
+        <v>3.2</v>
       </c>
       <c r="H25" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I25" s="11"/>
+        <f>E25</f>
+        <v>0</v>
+      </c>
+      <c r="I25" s="11" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="26" spans="1:9" s="13" customFormat="1">
       <c r="A26" s="2">
-        <v>9988391</v>
+        <v>9988452</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C26" s="10">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D26" s="17"/>
       <c r="E26" s="17"/>
       <c r="F26" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="F26:F37" si="2">D26/C26</f>
         <v>0</v>
       </c>
       <c r="G26" s="12">
-        <v>0.14000000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="H26" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="H26:H31" si="3">G26*D26</f>
         <v>0</v>
       </c>
       <c r="I26" s="11"/>
     </row>
     <row r="27" spans="1:9" s="13" customFormat="1">
       <c r="A27" s="2">
-        <v>5034819</v>
+        <v>9988476</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C27" s="10">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="D27" s="17"/>
       <c r="E27" s="17"/>
       <c r="F27" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G27" s="12">
-        <v>0.18</v>
+        <v>0.4</v>
       </c>
       <c r="H27" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I27" s="11"/>
     </row>
     <row r="28" spans="1:9" s="13" customFormat="1">
       <c r="A28" s="2">
-        <v>2981244</v>
+        <v>9988681</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="C28" s="10">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D28" s="17"/>
       <c r="E28" s="17"/>
       <c r="F28" s="11">
-        <f>E28/7.8</f>
+        <f>D28/C28</f>
         <v>0</v>
       </c>
       <c r="G28" s="12">
-        <v>1.3</v>
+        <v>0.18</v>
       </c>
       <c r="H28" s="11">
-        <f>E28</f>
-        <v>0</v>
-      </c>
-      <c r="I28" s="11" t="s">
-        <v>19</v>
-      </c>
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I28" s="11"/>
     </row>
     <row r="29" spans="1:9" s="13" customFormat="1">
       <c r="A29" s="2">
-        <v>8785198</v>
+        <v>9988438</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C29" s="10">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D29" s="17"/>
       <c r="E29" s="17"/>
       <c r="F29" s="11">
-        <f>E29/16.5</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G29" s="12">
-        <v>3.2</v>
+        <v>0.18</v>
       </c>
       <c r="H29" s="11">
-        <f>E29</f>
-        <v>0</v>
-      </c>
-      <c r="I29" s="11" t="s">
-        <v>15</v>
-      </c>
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I29" s="11"/>
     </row>
     <row r="30" spans="1:9" s="13" customFormat="1">
       <c r="A30" s="2">
-        <v>9988452</v>
+        <v>9988445</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C30" s="10">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D30" s="17"/>
       <c r="E30" s="17"/>
       <c r="F30" s="11">
-        <f t="shared" ref="F30:F43" si="2">D30/C30</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G30" s="12">
-        <v>0.4</v>
+        <v>0.18</v>
       </c>
       <c r="H30" s="11">
-        <f t="shared" ref="H30:H35" si="3">G30*D30</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I30" s="11"/>
     </row>
     <row r="31" spans="1:9" s="13" customFormat="1">
       <c r="A31" s="2">
-        <v>9988476</v>
+        <v>9988421</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C31" s="10">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="D31" s="17"/>
       <c r="E31" s="17"/>
@@ -3255,7 +3134,7 @@
         <v>0</v>
       </c>
       <c r="G31" s="12">
-        <v>0.4</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="H31" s="11">
         <f t="shared" si="3"/>
@@ -3265,10 +3144,10 @@
     </row>
     <row r="32" spans="1:9" s="13" customFormat="1">
       <c r="A32" s="2">
-        <v>9988681</v>
+        <v>9988674</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C32" s="10">
         <v>16</v>
@@ -3276,27 +3155,27 @@
       <c r="D32" s="17"/>
       <c r="E32" s="17"/>
       <c r="F32" s="11">
-        <f>D32/C32</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G32" s="12">
         <v>0.18</v>
       </c>
       <c r="H32" s="11">
-        <f t="shared" si="3"/>
+        <f>D32*G32</f>
         <v>0</v>
       </c>
       <c r="I32" s="11"/>
     </row>
     <row r="33" spans="1:9" s="13" customFormat="1">
-      <c r="A33" s="2">
-        <v>9988438</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>30</v>
+      <c r="A33" s="26">
+        <v>8444903</v>
+      </c>
+      <c r="B33" s="27" t="s">
+        <v>45</v>
       </c>
       <c r="C33" s="10">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D33" s="17"/>
       <c r="E33" s="17"/>
@@ -3305,23 +3184,23 @@
         <v>0</v>
       </c>
       <c r="G33" s="12">
-        <v>0.18</v>
+        <v>0.1</v>
       </c>
       <c r="H33" s="11">
-        <f t="shared" si="3"/>
+        <f>D33*G33</f>
         <v>0</v>
       </c>
       <c r="I33" s="11"/>
     </row>
     <row r="34" spans="1:9" s="13" customFormat="1">
-      <c r="A34" s="2">
-        <v>9988445</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>31</v>
+      <c r="A34" s="26">
+        <v>8444910</v>
+      </c>
+      <c r="B34" s="27" t="s">
+        <v>46</v>
       </c>
       <c r="C34" s="10">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D34" s="17"/>
       <c r="E34" s="17"/>
@@ -3330,23 +3209,23 @@
         <v>0</v>
       </c>
       <c r="G34" s="12">
-        <v>0.18</v>
+        <v>0.1</v>
       </c>
       <c r="H34" s="11">
-        <f t="shared" si="3"/>
+        <f>D34*G34</f>
         <v>0</v>
       </c>
       <c r="I34" s="11"/>
     </row>
     <row r="35" spans="1:9" s="13" customFormat="1">
-      <c r="A35" s="2">
-        <v>9988421</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>32</v>
+      <c r="A35" s="26">
+        <v>8444927</v>
+      </c>
+      <c r="B35" s="27" t="s">
+        <v>47</v>
       </c>
       <c r="C35" s="10">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D35" s="17"/>
       <c r="E35" s="17"/>
@@ -3355,23 +3234,23 @@
         <v>0</v>
       </c>
       <c r="G35" s="12">
-        <v>0.14000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="H35" s="11">
-        <f t="shared" si="3"/>
+        <f>D35*G35</f>
         <v>0</v>
       </c>
       <c r="I35" s="11"/>
     </row>
     <row r="36" spans="1:9" s="13" customFormat="1">
       <c r="A36" s="2">
-        <v>9988674</v>
+        <v>8445160</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="C36" s="10">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D36" s="17"/>
       <c r="E36" s="17"/>
@@ -3380,20 +3259,20 @@
         <v>0</v>
       </c>
       <c r="G36" s="12">
-        <v>0.18</v>
+        <v>0.1</v>
       </c>
       <c r="H36" s="11">
-        <f t="shared" ref="H36:H43" si="4">D36*G36</f>
+        <f>G36*D36</f>
         <v>0</v>
       </c>
       <c r="I36" s="11"/>
     </row>
     <row r="37" spans="1:9" s="13" customFormat="1">
-      <c r="A37" s="30">
-        <v>8444903</v>
-      </c>
-      <c r="B37" s="31" t="s">
-        <v>49</v>
+      <c r="A37" s="2">
+        <v>8445177</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>65</v>
       </c>
       <c r="C37" s="10">
         <v>8</v>
@@ -3408,79 +3287,81 @@
         <v>0.1</v>
       </c>
       <c r="H37" s="11">
-        <f t="shared" si="4"/>
+        <f>G37*D37</f>
         <v>0</v>
       </c>
       <c r="I37" s="11"/>
     </row>
     <row r="38" spans="1:9" s="13" customFormat="1">
-      <c r="A38" s="30">
-        <v>8444910</v>
-      </c>
-      <c r="B38" s="31" t="s">
-        <v>50</v>
+      <c r="A38" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>13</v>
       </c>
       <c r="C38" s="10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D38" s="17"/>
       <c r="E38" s="17"/>
       <c r="F38" s="11">
-        <f t="shared" si="2"/>
+        <f>D38/C38</f>
         <v>0</v>
       </c>
       <c r="G38" s="12">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H38" s="11">
-        <f t="shared" si="4"/>
+        <f>G38*D38</f>
         <v>0</v>
       </c>
       <c r="I38" s="11"/>
     </row>
     <row r="39" spans="1:9" s="13" customFormat="1">
-      <c r="A39" s="30">
-        <v>8444927</v>
-      </c>
-      <c r="B39" s="31" t="s">
-        <v>51</v>
+      <c r="A39" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>16</v>
       </c>
       <c r="C39" s="10">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D39" s="17"/>
       <c r="E39" s="17"/>
       <c r="F39" s="11">
-        <f t="shared" si="2"/>
+        <f>E39/15</f>
         <v>0</v>
       </c>
       <c r="G39" s="12">
-        <v>0.1</v>
+        <v>3.5</v>
       </c>
       <c r="H39" s="11">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I39" s="11"/>
-    </row>
-    <row r="40" spans="1:9" s="36" customFormat="1">
-      <c r="A40" s="15">
-        <v>8445160</v>
-      </c>
-      <c r="B40" s="16" t="s">
-        <v>70</v>
+        <f>E39</f>
+        <v>0</v>
+      </c>
+      <c r="I39" s="11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" s="29" customFormat="1">
+      <c r="A40" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B40" s="12" t="s">
+        <v>14</v>
       </c>
       <c r="C40" s="10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D40" s="17"/>
       <c r="E40" s="17"/>
       <c r="F40" s="11">
-        <f t="shared" si="2"/>
+        <f>D40/C40</f>
         <v>0</v>
       </c>
       <c r="G40" s="12">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H40" s="11">
         <f>G40*D40</f>
@@ -3488,94 +3369,94 @@
       </c>
       <c r="I40" s="11"/>
     </row>
-    <row r="41" spans="1:9" s="36" customFormat="1" ht="11.25" customHeight="1">
-      <c r="A41" s="15">
-        <v>8445177</v>
-      </c>
-      <c r="B41" s="16" t="s">
-        <v>71</v>
+    <row r="41" spans="1:9" s="29" customFormat="1" ht="11.25" customHeight="1">
+      <c r="A41" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B41" s="12" t="s">
+        <v>17</v>
       </c>
       <c r="C41" s="10">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D41" s="17"/>
       <c r="E41" s="17"/>
       <c r="F41" s="11">
-        <f t="shared" si="2"/>
+        <f>E41/15</f>
         <v>0</v>
       </c>
       <c r="G41" s="12">
-        <v>0.1</v>
+        <v>3.5</v>
       </c>
       <c r="H41" s="11">
-        <f>G41*D41</f>
-        <v>0</v>
-      </c>
-      <c r="I41" s="11"/>
+        <f>E41</f>
+        <v>0</v>
+      </c>
+      <c r="I41" s="11" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="42" spans="1:9" s="13" customFormat="1">
-      <c r="A42" s="30">
-        <v>6600454</v>
-      </c>
-      <c r="B42" s="31" t="s">
-        <v>54</v>
-      </c>
-      <c r="C42" s="32">
+      <c r="A42" s="2">
+        <v>7100108</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C42" s="10">
         <v>12</v>
       </c>
-      <c r="D42" s="33"/>
-      <c r="E42" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="F42" s="34">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G42" s="35">
-        <v>0.125</v>
-      </c>
-      <c r="H42" s="34">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I42" s="34"/>
+      <c r="D42" s="17"/>
+      <c r="E42" s="17"/>
+      <c r="F42" s="11">
+        <f>D42/C42</f>
+        <v>0</v>
+      </c>
+      <c r="G42" s="12">
+        <v>0.2</v>
+      </c>
+      <c r="H42" s="11">
+        <f>D42*G42</f>
+        <v>0</v>
+      </c>
+      <c r="I42" s="11"/>
     </row>
     <row r="43" spans="1:9" s="13" customFormat="1">
-      <c r="A43" s="30">
-        <v>6600447</v>
-      </c>
-      <c r="B43" s="31" t="s">
-        <v>53</v>
-      </c>
-      <c r="C43" s="32">
+      <c r="A43" s="2">
+        <v>7100139</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C43" s="10">
+        <v>8</v>
+      </c>
+      <c r="D43" s="17"/>
+      <c r="E43" s="17"/>
+      <c r="F43" s="11">
+        <f>E43/20</f>
+        <v>0</v>
+      </c>
+      <c r="G43" s="12">
+        <v>2.5</v>
+      </c>
+      <c r="H43" s="11">
+        <f>E43</f>
+        <v>0</v>
+      </c>
+      <c r="I43" s="11" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" s="13" customFormat="1">
+      <c r="A44" s="2">
+        <v>7100740</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C44" s="10">
         <v>12</v>
-      </c>
-      <c r="D43" s="33"/>
-      <c r="E43" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="F43" s="34">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G43" s="35">
-        <v>0.125</v>
-      </c>
-      <c r="H43" s="34">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I43" s="34"/>
-    </row>
-    <row r="44" spans="1:9" s="13" customFormat="1">
-      <c r="A44" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B44" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="C44" s="10">
-        <v>10</v>
       </c>
       <c r="D44" s="17"/>
       <c r="E44" s="17"/>
@@ -3587,47 +3468,47 @@
         <v>0.2</v>
       </c>
       <c r="H44" s="11">
-        <f>G44*D44</f>
+        <f>D44*G44</f>
         <v>0</v>
       </c>
       <c r="I44" s="11"/>
     </row>
     <row r="45" spans="1:9" s="13" customFormat="1">
-      <c r="A45" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B45" s="12" t="s">
-        <v>16</v>
+      <c r="A45" s="2">
+        <v>7100726</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>70</v>
       </c>
       <c r="C45" s="10">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D45" s="17"/>
       <c r="E45" s="17"/>
       <c r="F45" s="11">
-        <f>E45/15</f>
+        <f>E45/20</f>
         <v>0</v>
       </c>
       <c r="G45" s="12">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="H45" s="11">
         <f>E45</f>
         <v>0</v>
       </c>
       <c r="I45" s="11" t="s">
-        <v>18</v>
+        <v>68</v>
       </c>
     </row>
     <row r="46" spans="1:9" s="13" customFormat="1">
-      <c r="A46" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B46" s="12" t="s">
-        <v>14</v>
+      <c r="A46" s="2">
+        <v>4421584</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>54</v>
       </c>
       <c r="C46" s="10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D46" s="17"/>
       <c r="E46" s="17"/>
@@ -3636,7 +3517,7 @@
         <v>0</v>
       </c>
       <c r="G46" s="12">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="H46" s="11">
         <f>G46*D46</f>
@@ -3645,41 +3526,39 @@
       <c r="I46" s="11"/>
     </row>
     <row r="47" spans="1:9" s="13" customFormat="1">
-      <c r="A47" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B47" s="12" t="s">
-        <v>17</v>
+      <c r="A47" s="2">
+        <v>4421577</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>53</v>
       </c>
       <c r="C47" s="10">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D47" s="17"/>
       <c r="E47" s="17"/>
       <c r="F47" s="11">
-        <f>E47/15</f>
+        <f>D47/C47</f>
         <v>0</v>
       </c>
       <c r="G47" s="12">
-        <v>3.5</v>
+        <v>0.18</v>
       </c>
       <c r="H47" s="11">
-        <f>E47</f>
-        <v>0</v>
-      </c>
-      <c r="I47" s="11" t="s">
-        <v>18</v>
-      </c>
+        <f>G47*D47</f>
+        <v>0</v>
+      </c>
+      <c r="I47" s="11"/>
     </row>
     <row r="48" spans="1:9" s="13" customFormat="1">
       <c r="A48" s="2">
-        <v>7100108</v>
+        <v>9985949</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="C48" s="10">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D48" s="17"/>
       <c r="E48" s="17"/>
@@ -3687,48 +3566,48 @@
         <f>D48/C48</f>
         <v>0</v>
       </c>
-      <c r="G48" s="12">
-        <v>0.2</v>
+      <c r="G48" s="18">
+        <v>1</v>
       </c>
       <c r="H48" s="11">
-        <f>D48*G48</f>
+        <f>G48*D48</f>
         <v>0</v>
       </c>
       <c r="I48" s="11"/>
     </row>
     <row r="49" spans="1:9" s="13" customFormat="1">
       <c r="A49" s="2">
-        <v>7100139</v>
+        <v>8786928</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="C49" s="10">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D49" s="17"/>
       <c r="E49" s="17"/>
       <c r="F49" s="11">
-        <f>E49/20</f>
+        <f>E49/6</f>
         <v>0</v>
       </c>
       <c r="G49" s="12">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="H49" s="11">
         <f>E49</f>
         <v>0</v>
       </c>
       <c r="I49" s="11" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
     </row>
     <row r="50" spans="1:9" s="13" customFormat="1">
       <c r="A50" s="2">
-        <v>7100740</v>
+        <v>6948270</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="C50" s="10">
         <v>12</v>
@@ -3736,51 +3615,49 @@
       <c r="D50" s="17"/>
       <c r="E50" s="17"/>
       <c r="F50" s="11">
-        <f>D50/C50</f>
+        <f t="shared" ref="F50:F57" si="4">D50/C50</f>
         <v>0</v>
       </c>
       <c r="G50" s="12">
-        <v>0.2</v>
+        <v>0.372</v>
       </c>
       <c r="H50" s="11">
-        <f>D50*G50</f>
+        <f t="shared" ref="H50:H57" si="5">G50*D50</f>
         <v>0</v>
       </c>
       <c r="I50" s="11"/>
     </row>
     <row r="51" spans="1:9" s="13" customFormat="1">
       <c r="A51" s="2">
-        <v>7100726</v>
+        <v>6948287</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="C51" s="10">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D51" s="17"/>
       <c r="E51" s="17"/>
       <c r="F51" s="11">
-        <f>E51/20</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G51" s="12">
-        <v>2.5</v>
+        <v>0.74399999999999999</v>
       </c>
       <c r="H51" s="11">
-        <f>E51</f>
-        <v>0</v>
-      </c>
-      <c r="I51" s="11" t="s">
-        <v>74</v>
-      </c>
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I51" s="11"/>
     </row>
     <row r="52" spans="1:9" s="13" customFormat="1">
       <c r="A52" s="2">
-        <v>4421584</v>
+        <v>6948256</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C52" s="10">
         <v>12</v>
@@ -3788,24 +3665,24 @@
       <c r="D52" s="17"/>
       <c r="E52" s="17"/>
       <c r="F52" s="11">
-        <f>D52/C52</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G52" s="12">
-        <v>0.18</v>
+        <v>0.372</v>
       </c>
       <c r="H52" s="11">
-        <f>G52*D52</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="I52" s="11"/>
     </row>
     <row r="53" spans="1:9" s="13" customFormat="1">
       <c r="A53" s="2">
-        <v>4421577</v>
+        <v>6948263</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C53" s="10">
         <v>12</v>
@@ -3813,210 +3690,133 @@
       <c r="D53" s="17"/>
       <c r="E53" s="17"/>
       <c r="F53" s="11">
-        <f>D53/C53</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G53" s="12">
-        <v>0.18</v>
+        <v>0.74399999999999999</v>
       </c>
       <c r="H53" s="11">
-        <f>G53*D53</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="I53" s="11"/>
     </row>
     <row r="54" spans="1:9" s="13" customFormat="1">
       <c r="A54" s="2">
-        <v>9985949</v>
+        <v>6948249</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C54" s="10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D54" s="17"/>
       <c r="E54" s="17"/>
       <c r="F54" s="11">
-        <f>D54/C54</f>
-        <v>0</v>
-      </c>
-      <c r="G54" s="18">
-        <v>1</v>
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G54" s="12">
+        <v>0.82499999999999996</v>
       </c>
       <c r="H54" s="11">
-        <f>G54*D54</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="I54" s="11"/>
     </row>
     <row r="55" spans="1:9" s="13" customFormat="1">
-      <c r="A55" s="2">
-        <v>8786928</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>63</v>
+      <c r="A55" s="15">
+        <v>2105201</v>
+      </c>
+      <c r="B55" s="16" t="s">
+        <v>74</v>
       </c>
       <c r="C55" s="10">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="D55" s="17"/>
       <c r="E55" s="17"/>
       <c r="F55" s="11">
-        <f>E55/6</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G55" s="12">
-        <v>1.5</v>
+        <v>0.1</v>
       </c>
       <c r="H55" s="11">
-        <f>E55</f>
-        <v>0</v>
-      </c>
-      <c r="I55" s="11" t="s">
-        <v>64</v>
-      </c>
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I55" s="11"/>
     </row>
     <row r="56" spans="1:9" s="13" customFormat="1">
-      <c r="A56" s="2">
-        <v>6948270</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>65</v>
+      <c r="A56" s="15">
+        <v>2103201</v>
+      </c>
+      <c r="B56" s="16" t="s">
+        <v>75</v>
       </c>
       <c r="C56" s="10">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D56" s="17"/>
       <c r="E56" s="17"/>
       <c r="F56" s="11">
-        <f>D56/C56</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G56" s="12">
-        <v>0.372</v>
+        <v>0.1</v>
       </c>
       <c r="H56" s="11">
-        <f>G56*D56</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="I56" s="11"/>
     </row>
     <row r="57" spans="1:9" s="13" customFormat="1">
-      <c r="A57" s="2">
-        <v>6948287</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>66</v>
+      <c r="A57" s="15">
+        <v>1103201</v>
+      </c>
+      <c r="B57" s="16" t="s">
+        <v>76</v>
       </c>
       <c r="C57" s="10">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="D57" s="17"/>
       <c r="E57" s="17"/>
       <c r="F57" s="11">
-        <f>D57/C57</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G57" s="12">
-        <v>0.74399999999999999</v>
+        <v>5.5E-2</v>
       </c>
       <c r="H57" s="11">
-        <f>G57*D57</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="I57" s="11"/>
     </row>
     <row r="58" spans="1:9" s="13" customFormat="1">
-      <c r="A58" s="2">
-        <v>6948256</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C58" s="10">
-        <v>12</v>
-      </c>
+      <c r="A58" s="11"/>
+      <c r="B58" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C58" s="11"/>
       <c r="D58" s="17"/>
       <c r="E58" s="17"/>
-      <c r="F58" s="11">
-        <f>D58/C58</f>
-        <v>0</v>
-      </c>
-      <c r="G58" s="12">
-        <v>0.372</v>
-      </c>
-      <c r="H58" s="11">
-        <f>G58*D58</f>
+      <c r="F58" s="11"/>
+      <c r="G58" s="11"/>
+      <c r="H58" s="3">
+        <f>SUM(H4:H57)</f>
         <v>0</v>
       </c>
       <c r="I58" s="11"/>
-    </row>
-    <row r="59" spans="1:9" s="13" customFormat="1">
-      <c r="A59" s="2">
-        <v>6948263</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C59" s="10">
-        <v>12</v>
-      </c>
-      <c r="D59" s="17"/>
-      <c r="E59" s="17"/>
-      <c r="F59" s="11">
-        <f>D59/C59</f>
-        <v>0</v>
-      </c>
-      <c r="G59" s="12">
-        <v>0.74399999999999999</v>
-      </c>
-      <c r="H59" s="11">
-        <f>G59*D59</f>
-        <v>0</v>
-      </c>
-      <c r="I59" s="11"/>
-    </row>
-    <row r="60" spans="1:9">
-      <c r="A60" s="2">
-        <v>6948249</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C60" s="10">
-        <v>12</v>
-      </c>
-      <c r="D60" s="17"/>
-      <c r="E60" s="17"/>
-      <c r="F60" s="11">
-        <f>D60/C60</f>
-        <v>0</v>
-      </c>
-      <c r="G60" s="12">
-        <v>0.82499999999999996</v>
-      </c>
-      <c r="H60" s="11">
-        <f>G60*D60</f>
-        <v>0</v>
-      </c>
-      <c r="I60" s="11"/>
-    </row>
-    <row r="61" spans="1:9">
-      <c r="A61" s="11"/>
-      <c r="B61" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C61" s="11"/>
-      <c r="D61" s="17"/>
-      <c r="E61" s="17"/>
-      <c r="F61" s="11"/>
-      <c r="G61" s="11"/>
-      <c r="H61" s="3">
-        <f>SUM(H4:H60)</f>
-        <v>0</v>
-      </c>
-      <c r="I61" s="11"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:I52" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
@@ -4026,7 +3826,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="10" style="4" customWidth="1"/>
@@ -4054,7 +3854,7 @@
     </row>
     <row r="2" spans="1:9" ht="38.25">
       <c r="A2" s="7" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>12</v>
@@ -4072,25 +3872,25 @@
       <c r="I2" s="7"/>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="37" t="s">
+      <c r="A3" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="37" t="s">
+      <c r="C3" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="38" t="s">
+      <c r="D3" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="38" t="s">
+      <c r="E3" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="37" t="s">
+      <c r="F3" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="39" t="s">
+      <c r="G3" s="32" t="s">
         <v>10</v>
       </c>
       <c r="H3" s="11" t="s">
@@ -4125,207 +3925,203 @@
       </c>
       <c r="I4" s="11"/>
     </row>
-    <row r="5" spans="1:9" s="13" customFormat="1">
-      <c r="A5" s="1">
-        <v>8785204</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="C5" s="10">
+    <row r="5" spans="1:9" s="13" customFormat="1" ht="25.5">
+      <c r="A5" s="33">
+        <v>8783323</v>
+      </c>
+      <c r="B5" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" s="28">
+        <v>4</v>
+      </c>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="11">
+        <f>E5/5</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="22">
+        <v>1.8</v>
+      </c>
+      <c r="H5" s="21">
+        <f>E5</f>
+        <v>0</v>
+      </c>
+      <c r="I5" s="21"/>
+    </row>
+    <row r="6" spans="1:9" s="23" customFormat="1" ht="25.5">
+      <c r="A6" s="1">
+        <v>5038459</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="10">
+        <v>10</v>
+      </c>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="11">
+        <f>D6/C6</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="12">
+        <v>0.18</v>
+      </c>
+      <c r="H6" s="11">
+        <f>G6*D6</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="11"/>
+    </row>
+    <row r="7" spans="1:9" s="13" customFormat="1" ht="25.5">
+      <c r="A7" s="33">
+        <v>8785235</v>
+      </c>
+      <c r="B7" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7" s="10">
         <v>5</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="E5" s="17"/>
-      <c r="F5" s="11">
-        <f>E5/16.5</f>
-        <v>0</v>
-      </c>
-      <c r="G5" s="12">
-        <v>3.2</v>
-      </c>
-      <c r="H5" s="11">
-        <f>E5</f>
-        <v>0</v>
-      </c>
-      <c r="I5" s="11"/>
-    </row>
-    <row r="6" spans="1:9" s="26" customFormat="1" ht="25.5">
-      <c r="A6" s="20">
-        <v>8783323</v>
-      </c>
-      <c r="B6" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="C6" s="22">
-        <v>4</v>
-      </c>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="11">
-        <f>E6/5</f>
-        <v>0</v>
-      </c>
-      <c r="G6" s="25">
-        <v>1.8</v>
-      </c>
-      <c r="H6" s="24">
-        <f>E6</f>
-        <v>0</v>
-      </c>
-      <c r="I6" s="24"/>
-    </row>
-    <row r="7" spans="1:9" s="13" customFormat="1" ht="25.5">
-      <c r="A7" s="1">
-        <v>5038459</v>
-      </c>
-      <c r="B7" s="19" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" s="10">
-        <v>10</v>
       </c>
       <c r="D7" s="17"/>
       <c r="E7" s="17"/>
       <c r="F7" s="11">
-        <f>D7/C7</f>
-        <v>0</v>
-      </c>
-      <c r="G7" s="12">
-        <v>0.18</v>
+        <f>E7/16.5</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="11">
+        <v>3.5</v>
       </c>
       <c r="H7" s="11">
-        <f>G7*D7</f>
-        <v>0</v>
-      </c>
-      <c r="I7" s="11"/>
+        <f>E7</f>
+        <v>0</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="8" spans="1:9" s="13" customFormat="1" ht="25.5">
-      <c r="A8" s="20">
-        <v>8785235</v>
-      </c>
-      <c r="B8" s="21" t="s">
-        <v>79</v>
+      <c r="A8" s="1">
+        <v>5038411</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>34</v>
       </c>
       <c r="C8" s="10">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D8" s="17"/>
       <c r="E8" s="17"/>
       <c r="F8" s="11">
-        <f>E8/16.5</f>
-        <v>0</v>
-      </c>
-      <c r="G8" s="11">
-        <v>3.5</v>
+        <f>D8/C8</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="12">
+        <v>0.18</v>
       </c>
       <c r="H8" s="11">
-        <f>E8</f>
-        <v>0</v>
-      </c>
-      <c r="I8" s="11" t="s">
-        <v>15</v>
-      </c>
+        <f>G8*D8</f>
+        <v>0</v>
+      </c>
+      <c r="I8" s="11"/>
     </row>
     <row r="9" spans="1:9" s="13" customFormat="1" ht="25.5">
-      <c r="A9" s="1">
-        <v>5038411</v>
+      <c r="A9" s="2">
+        <v>8785242</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="C9" s="10">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D9" s="17"/>
       <c r="E9" s="17"/>
       <c r="F9" s="11">
-        <f>D9/C9</f>
-        <v>0</v>
-      </c>
-      <c r="G9" s="12">
-        <v>0.18</v>
+        <f>E9/16.5</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="11">
+        <v>3.5</v>
       </c>
       <c r="H9" s="11">
-        <f>G9*D9</f>
-        <v>0</v>
-      </c>
-      <c r="I9" s="11"/>
+        <f>E9</f>
+        <v>0</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="10" spans="1:9" s="13" customFormat="1" ht="25.5">
-      <c r="A10" s="2">
-        <v>8785242</v>
+      <c r="A10" s="1">
+        <v>5038398</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C10" s="10">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D10" s="17"/>
       <c r="E10" s="17"/>
       <c r="F10" s="11">
-        <f>E10/16.5</f>
-        <v>0</v>
-      </c>
-      <c r="G10" s="11">
-        <v>3.5</v>
+        <f>D10/C10</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="12">
+        <v>0.18</v>
       </c>
       <c r="H10" s="11">
-        <f>E10</f>
-        <v>0</v>
-      </c>
-      <c r="I10" s="11" t="s">
-        <v>15</v>
-      </c>
+        <f>G10*D10</f>
+        <v>0</v>
+      </c>
+      <c r="I10" s="11"/>
     </row>
     <row r="11" spans="1:9" s="13" customFormat="1" ht="25.5">
-      <c r="A11" s="1">
-        <v>5038398</v>
+      <c r="A11" s="2">
+        <v>8785259</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="C11" s="10">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D11" s="17"/>
       <c r="E11" s="17"/>
       <c r="F11" s="11">
-        <f>D11/C11</f>
-        <v>0</v>
-      </c>
-      <c r="G11" s="12">
-        <v>0.18</v>
+        <f>E11/16.5</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="11">
+        <v>3.5</v>
       </c>
       <c r="H11" s="11">
-        <f>G11*D11</f>
+        <f>E11</f>
         <v>0</v>
       </c>
       <c r="I11" s="11"/>
     </row>
-    <row r="12" spans="1:9" s="13" customFormat="1">
-      <c r="A12" s="1">
-        <v>5039609</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>43</v>
+    <row r="12" spans="1:9" s="13" customFormat="1" ht="25.5">
+      <c r="A12" s="2">
+        <v>5038855</v>
+      </c>
+      <c r="B12" s="24" t="s">
+        <v>41</v>
       </c>
       <c r="C12" s="10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D12" s="17"/>
-      <c r="E12" s="17" t="s">
-        <v>77</v>
-      </c>
+      <c r="E12" s="17"/>
       <c r="F12" s="11">
         <f>D12/C12</f>
         <v>0</v>
       </c>
       <c r="G12" s="12">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="H12" s="11">
         <f>G12*D12</f>
@@ -4335,471 +4131,469 @@
     </row>
     <row r="13" spans="1:9" s="13" customFormat="1" ht="25.5">
       <c r="A13" s="2">
-        <v>8785259</v>
+        <v>5038831</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="C13" s="10">
-        <v>5</v>
+        <v>39</v>
+      </c>
+      <c r="C13" s="25">
+        <v>10</v>
       </c>
       <c r="D13" s="17"/>
       <c r="E13" s="17"/>
       <c r="F13" s="11">
-        <f>E13/16.5</f>
-        <v>0</v>
-      </c>
-      <c r="G13" s="11">
-        <v>3.5</v>
+        <f>D13/C13</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="12">
+        <v>0.18</v>
       </c>
       <c r="H13" s="11">
-        <f>E13</f>
+        <f>G13*D13</f>
         <v>0</v>
       </c>
       <c r="I13" s="11"/>
     </row>
-    <row r="14" spans="1:9" s="13" customFormat="1" ht="25.5">
-      <c r="A14" s="2">
-        <v>5038855</v>
-      </c>
-      <c r="B14" s="27" t="s">
-        <v>41</v>
-      </c>
-      <c r="C14" s="10">
-        <v>10</v>
+    <row r="14" spans="1:9" s="13" customFormat="1" ht="38.25">
+      <c r="A14" s="26">
+        <v>8784931</v>
+      </c>
+      <c r="B14" s="34" t="s">
+        <v>73</v>
+      </c>
+      <c r="C14" s="25">
+        <v>5</v>
       </c>
       <c r="D14" s="17"/>
       <c r="E14" s="17"/>
       <c r="F14" s="11">
-        <f t="shared" ref="F14:F27" si="0">D14/C14</f>
+        <f>E14/16.5</f>
         <v>0</v>
       </c>
       <c r="G14" s="12">
-        <v>0.2</v>
+        <v>3.5</v>
       </c>
       <c r="H14" s="11">
-        <f>G14*D14</f>
-        <v>0</v>
-      </c>
-      <c r="I14" s="11"/>
+        <f>E14</f>
+        <v>0</v>
+      </c>
+      <c r="I14" s="11" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="15" spans="1:9" s="13" customFormat="1">
       <c r="A15" s="2">
-        <v>5039647</v>
-      </c>
-      <c r="B15" s="28" t="s">
-        <v>44</v>
+        <v>1018950</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>40</v>
       </c>
       <c r="C15" s="10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D15" s="17"/>
       <c r="E15" s="17"/>
       <c r="F15" s="11">
-        <f t="shared" si="0"/>
+        <f>D15/C15</f>
         <v>0</v>
       </c>
       <c r="G15" s="12">
-        <v>0.4</v>
+        <v>0.18</v>
       </c>
       <c r="H15" s="11">
-        <f>G15*D15</f>
+        <f t="shared" ref="H15:H23" si="0">G15*D15</f>
         <v>0</v>
       </c>
       <c r="I15" s="11"/>
     </row>
-    <row r="16" spans="1:9" s="13" customFormat="1" ht="25.5">
+    <row r="16" spans="1:9" s="13" customFormat="1">
       <c r="A16" s="2">
-        <v>5038831</v>
-      </c>
-      <c r="B16" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="C16" s="29">
+        <v>1018967</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" s="10">
         <v>10</v>
       </c>
       <c r="D16" s="17"/>
       <c r="E16" s="17"/>
       <c r="F16" s="11">
-        <f t="shared" si="0"/>
+        <f>D16/C16</f>
         <v>0</v>
       </c>
       <c r="G16" s="12">
         <v>0.18</v>
       </c>
       <c r="H16" s="11">
-        <f>G16*D16</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I16" s="11"/>
     </row>
     <row r="17" spans="1:9" s="13" customFormat="1">
       <c r="A17" s="2">
-        <v>5039623</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="C17" s="29">
-        <v>8</v>
+        <v>8444194</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="10">
+        <v>6</v>
       </c>
       <c r="D17" s="17"/>
-      <c r="E17" s="17" t="s">
-        <v>77</v>
-      </c>
+      <c r="E17" s="17"/>
       <c r="F17" s="11">
+        <f t="shared" ref="F17:F23" si="1">D17/C17</f>
+        <v>0</v>
+      </c>
+      <c r="G17" s="12">
+        <v>0.1</v>
+      </c>
+      <c r="H17" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G17" s="12">
-        <v>0.4</v>
-      </c>
-      <c r="H17" s="11">
-        <f>G17*D17</f>
-        <v>0</v>
-      </c>
       <c r="I17" s="11"/>
     </row>
-    <row r="18" spans="1:9" s="13" customFormat="1" ht="38.25">
-      <c r="A18" s="15">
-        <v>8784931</v>
-      </c>
-      <c r="B18" s="21" t="s">
-        <v>80</v>
-      </c>
-      <c r="C18" s="29">
-        <v>5</v>
+    <row r="18" spans="1:9" s="13" customFormat="1">
+      <c r="A18" s="2">
+        <v>8444187</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" s="10">
+        <v>6</v>
       </c>
       <c r="D18" s="17"/>
       <c r="E18" s="17"/>
       <c r="F18" s="11">
-        <f>E18/16.4</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G18" s="12">
-        <v>3.5</v>
+        <v>0.1</v>
       </c>
       <c r="H18" s="11">
-        <f>E18</f>
-        <v>0</v>
-      </c>
-      <c r="I18" s="11" t="s">
-        <v>81</v>
-      </c>
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I18" s="11"/>
     </row>
     <row r="19" spans="1:9" s="13" customFormat="1">
       <c r="A19" s="2">
-        <v>1018950</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>40</v>
+        <v>8444163</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>22</v>
       </c>
       <c r="C19" s="10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D19" s="17"/>
       <c r="E19" s="17"/>
       <c r="F19" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G19" s="12">
+        <v>0.1</v>
+      </c>
+      <c r="H19" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G19" s="12">
-        <v>0.18</v>
-      </c>
-      <c r="H19" s="11">
-        <f t="shared" ref="H19:H27" si="1">G19*D19</f>
         <v>0</v>
       </c>
       <c r="I19" s="11"/>
     </row>
     <row r="20" spans="1:9" s="13" customFormat="1">
       <c r="A20" s="2">
-        <v>1018967</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>42</v>
+        <v>8444170</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>56</v>
       </c>
       <c r="C20" s="10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D20" s="17"/>
       <c r="E20" s="17"/>
       <c r="F20" s="11">
+        <f>D20/C20</f>
+        <v>0</v>
+      </c>
+      <c r="G20" s="12">
+        <v>0.1</v>
+      </c>
+      <c r="H20" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G20" s="12">
-        <v>0.18</v>
-      </c>
-      <c r="H20" s="11">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I20" s="11"/>
     </row>
     <row r="21" spans="1:9" s="13" customFormat="1">
       <c r="A21" s="2">
-        <v>8444194</v>
+        <v>9988377</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C21" s="10">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D21" s="17"/>
       <c r="E21" s="17"/>
       <c r="F21" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G21" s="12">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="H21" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G21" s="12">
-        <v>0.1</v>
-      </c>
-      <c r="H21" s="11">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I21" s="11"/>
     </row>
     <row r="22" spans="1:9" s="13" customFormat="1">
       <c r="A22" s="2">
-        <v>8444187</v>
+        <v>9988391</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C22" s="10">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D22" s="17"/>
       <c r="E22" s="17"/>
       <c r="F22" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G22" s="12">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="H22" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G22" s="12">
-        <v>0.1</v>
-      </c>
-      <c r="H22" s="11">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I22" s="11"/>
     </row>
     <row r="23" spans="1:9" s="13" customFormat="1">
       <c r="A23" s="2">
-        <v>8444163</v>
+        <v>5034819</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C23" s="10">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D23" s="17"/>
       <c r="E23" s="17"/>
       <c r="F23" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G23" s="12">
+        <v>0.18</v>
+      </c>
+      <c r="H23" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G23" s="12">
-        <v>0.1</v>
-      </c>
-      <c r="H23" s="11">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I23" s="11"/>
     </row>
     <row r="24" spans="1:9" s="13" customFormat="1">
       <c r="A24" s="2">
-        <v>8444170</v>
+        <v>2981244</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="C24" s="10">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D24" s="17"/>
       <c r="E24" s="17"/>
       <c r="F24" s="11">
-        <f>D24/C24</f>
+        <f>E24/7.8</f>
         <v>0</v>
       </c>
       <c r="G24" s="12">
-        <v>0.1</v>
+        <v>1.3</v>
       </c>
       <c r="H24" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I24" s="11"/>
+        <f>E24</f>
+        <v>0</v>
+      </c>
+      <c r="I24" s="11" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="25" spans="1:9" s="13" customFormat="1">
       <c r="A25" s="2">
-        <v>9988377</v>
+        <v>8785198</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C25" s="10">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D25" s="17"/>
       <c r="E25" s="17"/>
       <c r="F25" s="11">
-        <f t="shared" si="0"/>
+        <f>E25/16.5</f>
         <v>0</v>
       </c>
       <c r="G25" s="12">
-        <v>0.14000000000000001</v>
+        <v>3.2</v>
       </c>
       <c r="H25" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I25" s="11"/>
+        <f>E25</f>
+        <v>0</v>
+      </c>
+      <c r="I25" s="11" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="26" spans="1:9" s="13" customFormat="1">
       <c r="A26" s="2">
-        <v>9988391</v>
+        <v>9988452</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C26" s="10">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D26" s="17"/>
       <c r="E26" s="17"/>
       <c r="F26" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="F26:F37" si="2">D26/C26</f>
         <v>0</v>
       </c>
       <c r="G26" s="12">
-        <v>0.14000000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="H26" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="H26:H31" si="3">G26*D26</f>
         <v>0</v>
       </c>
       <c r="I26" s="11"/>
     </row>
     <row r="27" spans="1:9" s="13" customFormat="1">
       <c r="A27" s="2">
-        <v>5034819</v>
+        <v>9988476</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C27" s="10">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="D27" s="17"/>
       <c r="E27" s="17"/>
       <c r="F27" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G27" s="12">
-        <v>0.18</v>
+        <v>0.4</v>
       </c>
       <c r="H27" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I27" s="11"/>
     </row>
     <row r="28" spans="1:9" s="13" customFormat="1">
       <c r="A28" s="2">
-        <v>2981244</v>
+        <v>9988681</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="C28" s="10">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D28" s="17"/>
       <c r="E28" s="17"/>
       <c r="F28" s="11">
-        <f>E28/7.8</f>
+        <f>D28/C28</f>
         <v>0</v>
       </c>
       <c r="G28" s="12">
-        <v>1.3</v>
+        <v>0.18</v>
       </c>
       <c r="H28" s="11">
-        <f>E28</f>
-        <v>0</v>
-      </c>
-      <c r="I28" s="11" t="s">
-        <v>19</v>
-      </c>
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I28" s="11"/>
     </row>
     <row r="29" spans="1:9" s="13" customFormat="1">
       <c r="A29" s="2">
-        <v>8785198</v>
+        <v>9988438</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C29" s="10">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D29" s="17"/>
       <c r="E29" s="17"/>
       <c r="F29" s="11">
-        <f>E29/16.5</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G29" s="12">
-        <v>3.2</v>
+        <v>0.18</v>
       </c>
       <c r="H29" s="11">
-        <f>E29</f>
-        <v>0</v>
-      </c>
-      <c r="I29" s="11" t="s">
-        <v>15</v>
-      </c>
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I29" s="11"/>
     </row>
     <row r="30" spans="1:9" s="13" customFormat="1">
       <c r="A30" s="2">
-        <v>9988452</v>
+        <v>9988445</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C30" s="10">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D30" s="17"/>
       <c r="E30" s="17"/>
       <c r="F30" s="11">
-        <f t="shared" ref="F30:F43" si="2">D30/C30</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G30" s="12">
-        <v>0.4</v>
+        <v>0.18</v>
       </c>
       <c r="H30" s="11">
-        <f t="shared" ref="H30:H35" si="3">G30*D30</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I30" s="11"/>
     </row>
     <row r="31" spans="1:9" s="13" customFormat="1">
       <c r="A31" s="2">
-        <v>9988476</v>
+        <v>9988421</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C31" s="10">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="D31" s="17"/>
       <c r="E31" s="17"/>
@@ -4808,7 +4602,7 @@
         <v>0</v>
       </c>
       <c r="G31" s="12">
-        <v>0.4</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="H31" s="11">
         <f t="shared" si="3"/>
@@ -4818,10 +4612,10 @@
     </row>
     <row r="32" spans="1:9" s="13" customFormat="1">
       <c r="A32" s="2">
-        <v>9988681</v>
+        <v>9988674</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C32" s="10">
         <v>16</v>
@@ -4829,27 +4623,27 @@
       <c r="D32" s="17"/>
       <c r="E32" s="17"/>
       <c r="F32" s="11">
-        <f>D32/C32</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G32" s="12">
         <v>0.18</v>
       </c>
       <c r="H32" s="11">
-        <f t="shared" si="3"/>
+        <f>D32*G32</f>
         <v>0</v>
       </c>
       <c r="I32" s="11"/>
     </row>
     <row r="33" spans="1:9" s="13" customFormat="1">
-      <c r="A33" s="2">
-        <v>9988438</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>30</v>
+      <c r="A33" s="26">
+        <v>8444903</v>
+      </c>
+      <c r="B33" s="27" t="s">
+        <v>45</v>
       </c>
       <c r="C33" s="10">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D33" s="17"/>
       <c r="E33" s="17"/>
@@ -4858,23 +4652,23 @@
         <v>0</v>
       </c>
       <c r="G33" s="12">
-        <v>0.18</v>
+        <v>0.1</v>
       </c>
       <c r="H33" s="11">
-        <f t="shared" si="3"/>
+        <f>D33*G33</f>
         <v>0</v>
       </c>
       <c r="I33" s="11"/>
     </row>
     <row r="34" spans="1:9" s="13" customFormat="1">
-      <c r="A34" s="2">
-        <v>9988445</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>31</v>
+      <c r="A34" s="26">
+        <v>8444910</v>
+      </c>
+      <c r="B34" s="27" t="s">
+        <v>46</v>
       </c>
       <c r="C34" s="10">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D34" s="17"/>
       <c r="E34" s="17"/>
@@ -4883,23 +4677,23 @@
         <v>0</v>
       </c>
       <c r="G34" s="12">
-        <v>0.18</v>
+        <v>0.1</v>
       </c>
       <c r="H34" s="11">
-        <f t="shared" si="3"/>
+        <f>D34*G34</f>
         <v>0</v>
       </c>
       <c r="I34" s="11"/>
     </row>
     <row r="35" spans="1:9" s="13" customFormat="1">
-      <c r="A35" s="2">
-        <v>9988421</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>32</v>
+      <c r="A35" s="26">
+        <v>8444927</v>
+      </c>
+      <c r="B35" s="27" t="s">
+        <v>47</v>
       </c>
       <c r="C35" s="10">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D35" s="17"/>
       <c r="E35" s="17"/>
@@ -4908,23 +4702,23 @@
         <v>0</v>
       </c>
       <c r="G35" s="12">
-        <v>0.14000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="H35" s="11">
-        <f t="shared" si="3"/>
+        <f>D35*G35</f>
         <v>0</v>
       </c>
       <c r="I35" s="11"/>
     </row>
     <row r="36" spans="1:9" s="13" customFormat="1">
       <c r="A36" s="2">
-        <v>9988674</v>
+        <v>8445160</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="C36" s="10">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D36" s="17"/>
       <c r="E36" s="17"/>
@@ -4933,20 +4727,20 @@
         <v>0</v>
       </c>
       <c r="G36" s="12">
-        <v>0.18</v>
+        <v>0.1</v>
       </c>
       <c r="H36" s="11">
-        <f t="shared" ref="H36:H43" si="4">D36*G36</f>
+        <f>G36*D36</f>
         <v>0</v>
       </c>
       <c r="I36" s="11"/>
     </row>
     <row r="37" spans="1:9" s="13" customFormat="1">
-      <c r="A37" s="30">
-        <v>8444903</v>
-      </c>
-      <c r="B37" s="31" t="s">
-        <v>49</v>
+      <c r="A37" s="2">
+        <v>8445177</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>65</v>
       </c>
       <c r="C37" s="10">
         <v>8</v>
@@ -4961,79 +4755,81 @@
         <v>0.1</v>
       </c>
       <c r="H37" s="11">
-        <f t="shared" si="4"/>
+        <f>G37*D37</f>
         <v>0</v>
       </c>
       <c r="I37" s="11"/>
     </row>
     <row r="38" spans="1:9" s="13" customFormat="1">
-      <c r="A38" s="30">
-        <v>8444910</v>
-      </c>
-      <c r="B38" s="31" t="s">
-        <v>50</v>
+      <c r="A38" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>13</v>
       </c>
       <c r="C38" s="10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D38" s="17"/>
       <c r="E38" s="17"/>
       <c r="F38" s="11">
-        <f t="shared" si="2"/>
+        <f>D38/C38</f>
         <v>0</v>
       </c>
       <c r="G38" s="12">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H38" s="11">
-        <f t="shared" si="4"/>
+        <f>G38*D38</f>
         <v>0</v>
       </c>
       <c r="I38" s="11"/>
     </row>
     <row r="39" spans="1:9" s="13" customFormat="1">
-      <c r="A39" s="30">
-        <v>8444927</v>
-      </c>
-      <c r="B39" s="31" t="s">
-        <v>51</v>
+      <c r="A39" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>16</v>
       </c>
       <c r="C39" s="10">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D39" s="17"/>
       <c r="E39" s="17"/>
       <c r="F39" s="11">
-        <f t="shared" si="2"/>
+        <f>E39/15</f>
         <v>0</v>
       </c>
       <c r="G39" s="12">
-        <v>0.1</v>
+        <v>3.5</v>
       </c>
       <c r="H39" s="11">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I39" s="11"/>
-    </row>
-    <row r="40" spans="1:9" s="36" customFormat="1">
-      <c r="A40" s="15">
-        <v>8445160</v>
-      </c>
-      <c r="B40" s="16" t="s">
-        <v>70</v>
+        <f>E39</f>
+        <v>0</v>
+      </c>
+      <c r="I39" s="11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" s="29" customFormat="1">
+      <c r="A40" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B40" s="12" t="s">
+        <v>14</v>
       </c>
       <c r="C40" s="10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D40" s="17"/>
       <c r="E40" s="17"/>
       <c r="F40" s="11">
-        <f t="shared" si="2"/>
+        <f>D40/C40</f>
         <v>0</v>
       </c>
       <c r="G40" s="12">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H40" s="11">
         <f>G40*D40</f>
@@ -5041,94 +4837,94 @@
       </c>
       <c r="I40" s="11"/>
     </row>
-    <row r="41" spans="1:9" s="36" customFormat="1" ht="11.25" customHeight="1">
-      <c r="A41" s="15">
-        <v>8445177</v>
-      </c>
-      <c r="B41" s="16" t="s">
-        <v>71</v>
+    <row r="41" spans="1:9" s="29" customFormat="1" ht="11.25" customHeight="1">
+      <c r="A41" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B41" s="12" t="s">
+        <v>17</v>
       </c>
       <c r="C41" s="10">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D41" s="17"/>
       <c r="E41" s="17"/>
       <c r="F41" s="11">
-        <f t="shared" si="2"/>
+        <f>E41/15</f>
         <v>0</v>
       </c>
       <c r="G41" s="12">
-        <v>0.1</v>
+        <v>3.5</v>
       </c>
       <c r="H41" s="11">
-        <f>G41*D41</f>
-        <v>0</v>
-      </c>
-      <c r="I41" s="11"/>
+        <f>E41</f>
+        <v>0</v>
+      </c>
+      <c r="I41" s="11" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="42" spans="1:9" s="13" customFormat="1">
-      <c r="A42" s="30">
-        <v>6600454</v>
-      </c>
-      <c r="B42" s="31" t="s">
-        <v>54</v>
-      </c>
-      <c r="C42" s="32">
+      <c r="A42" s="2">
+        <v>7100108</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C42" s="10">
         <v>12</v>
       </c>
-      <c r="D42" s="33"/>
-      <c r="E42" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="F42" s="34">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G42" s="35">
-        <v>0.125</v>
-      </c>
-      <c r="H42" s="34">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I42" s="34"/>
+      <c r="D42" s="17"/>
+      <c r="E42" s="17"/>
+      <c r="F42" s="11">
+        <f>D42/C42</f>
+        <v>0</v>
+      </c>
+      <c r="G42" s="12">
+        <v>0.2</v>
+      </c>
+      <c r="H42" s="11">
+        <f>D42*G42</f>
+        <v>0</v>
+      </c>
+      <c r="I42" s="11"/>
     </row>
     <row r="43" spans="1:9" s="13" customFormat="1">
-      <c r="A43" s="30">
-        <v>6600447</v>
-      </c>
-      <c r="B43" s="31" t="s">
-        <v>53</v>
-      </c>
-      <c r="C43" s="32">
+      <c r="A43" s="2">
+        <v>7100139</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C43" s="10">
+        <v>8</v>
+      </c>
+      <c r="D43" s="17"/>
+      <c r="E43" s="17"/>
+      <c r="F43" s="11">
+        <f>E43/20</f>
+        <v>0</v>
+      </c>
+      <c r="G43" s="12">
+        <v>2.5</v>
+      </c>
+      <c r="H43" s="11">
+        <f>E43</f>
+        <v>0</v>
+      </c>
+      <c r="I43" s="11" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" s="13" customFormat="1">
+      <c r="A44" s="2">
+        <v>7100740</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C44" s="10">
         <v>12</v>
-      </c>
-      <c r="D43" s="33"/>
-      <c r="E43" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="F43" s="34">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G43" s="35">
-        <v>0.125</v>
-      </c>
-      <c r="H43" s="34">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I43" s="34"/>
-    </row>
-    <row r="44" spans="1:9" s="13" customFormat="1">
-      <c r="A44" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B44" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="C44" s="10">
-        <v>10</v>
       </c>
       <c r="D44" s="17"/>
       <c r="E44" s="17"/>
@@ -5140,47 +4936,47 @@
         <v>0.2</v>
       </c>
       <c r="H44" s="11">
-        <f>G44*D44</f>
+        <f>D44*G44</f>
         <v>0</v>
       </c>
       <c r="I44" s="11"/>
     </row>
     <row r="45" spans="1:9" s="13" customFormat="1">
-      <c r="A45" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B45" s="12" t="s">
-        <v>16</v>
+      <c r="A45" s="2">
+        <v>7100726</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>70</v>
       </c>
       <c r="C45" s="10">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D45" s="17"/>
       <c r="E45" s="17"/>
       <c r="F45" s="11">
-        <f>E45/15</f>
+        <f>E45/20</f>
         <v>0</v>
       </c>
       <c r="G45" s="12">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="H45" s="11">
         <f>E45</f>
         <v>0</v>
       </c>
       <c r="I45" s="11" t="s">
-        <v>18</v>
+        <v>68</v>
       </c>
     </row>
     <row r="46" spans="1:9" s="13" customFormat="1">
-      <c r="A46" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B46" s="12" t="s">
-        <v>14</v>
+      <c r="A46" s="2">
+        <v>4421584</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>54</v>
       </c>
       <c r="C46" s="10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D46" s="17"/>
       <c r="E46" s="17"/>
@@ -5189,7 +4985,7 @@
         <v>0</v>
       </c>
       <c r="G46" s="12">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="H46" s="11">
         <f>G46*D46</f>
@@ -5198,41 +4994,39 @@
       <c r="I46" s="11"/>
     </row>
     <row r="47" spans="1:9" s="13" customFormat="1">
-      <c r="A47" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B47" s="12" t="s">
-        <v>17</v>
+      <c r="A47" s="2">
+        <v>4421577</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>53</v>
       </c>
       <c r="C47" s="10">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D47" s="17"/>
       <c r="E47" s="17"/>
       <c r="F47" s="11">
-        <f>E47/15</f>
+        <f>D47/C47</f>
         <v>0</v>
       </c>
       <c r="G47" s="12">
-        <v>3.5</v>
+        <v>0.18</v>
       </c>
       <c r="H47" s="11">
-        <f>E47</f>
-        <v>0</v>
-      </c>
-      <c r="I47" s="11" t="s">
-        <v>18</v>
-      </c>
+        <f>G47*D47</f>
+        <v>0</v>
+      </c>
+      <c r="I47" s="11"/>
     </row>
     <row r="48" spans="1:9" s="13" customFormat="1">
       <c r="A48" s="2">
-        <v>7100108</v>
+        <v>9985949</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="C48" s="10">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D48" s="17"/>
       <c r="E48" s="17"/>
@@ -5240,48 +5034,48 @@
         <f>D48/C48</f>
         <v>0</v>
       </c>
-      <c r="G48" s="12">
-        <v>0.2</v>
+      <c r="G48" s="18">
+        <v>1</v>
       </c>
       <c r="H48" s="11">
-        <f>D48*G48</f>
+        <f>G48*D48</f>
         <v>0</v>
       </c>
       <c r="I48" s="11"/>
     </row>
     <row r="49" spans="1:9" s="13" customFormat="1">
       <c r="A49" s="2">
-        <v>7100139</v>
+        <v>8786928</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="C49" s="10">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D49" s="17"/>
       <c r="E49" s="17"/>
       <c r="F49" s="11">
-        <f>E49/20</f>
+        <f>E49/6</f>
         <v>0</v>
       </c>
       <c r="G49" s="12">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="H49" s="11">
         <f>E49</f>
         <v>0</v>
       </c>
       <c r="I49" s="11" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
     </row>
     <row r="50" spans="1:9" s="13" customFormat="1">
       <c r="A50" s="2">
-        <v>7100740</v>
+        <v>6948270</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="C50" s="10">
         <v>12</v>
@@ -5289,51 +5083,49 @@
       <c r="D50" s="17"/>
       <c r="E50" s="17"/>
       <c r="F50" s="11">
-        <f>D50/C50</f>
+        <f t="shared" ref="F50:F57" si="4">D50/C50</f>
         <v>0</v>
       </c>
       <c r="G50" s="12">
-        <v>0.2</v>
+        <v>0.372</v>
       </c>
       <c r="H50" s="11">
-        <f>D50*G50</f>
+        <f t="shared" ref="H50:H57" si="5">G50*D50</f>
         <v>0</v>
       </c>
       <c r="I50" s="11"/>
     </row>
     <row r="51" spans="1:9" s="13" customFormat="1">
       <c r="A51" s="2">
-        <v>7100726</v>
+        <v>6948287</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="C51" s="10">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D51" s="17"/>
       <c r="E51" s="17"/>
       <c r="F51" s="11">
-        <f>E51/20</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G51" s="12">
-        <v>2.5</v>
+        <v>0.74399999999999999</v>
       </c>
       <c r="H51" s="11">
-        <f>E51</f>
-        <v>0</v>
-      </c>
-      <c r="I51" s="11" t="s">
-        <v>74</v>
-      </c>
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I51" s="11"/>
     </row>
     <row r="52" spans="1:9" s="13" customFormat="1">
       <c r="A52" s="2">
-        <v>4421584</v>
+        <v>6948256</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C52" s="10">
         <v>12</v>
@@ -5341,24 +5133,24 @@
       <c r="D52" s="17"/>
       <c r="E52" s="17"/>
       <c r="F52" s="11">
-        <f>D52/C52</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G52" s="12">
-        <v>0.18</v>
+        <v>0.372</v>
       </c>
       <c r="H52" s="11">
-        <f>G52*D52</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="I52" s="11"/>
     </row>
     <row r="53" spans="1:9" s="13" customFormat="1">
       <c r="A53" s="2">
-        <v>4421577</v>
+        <v>6948263</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C53" s="10">
         <v>12</v>
@@ -5366,210 +5158,133 @@
       <c r="D53" s="17"/>
       <c r="E53" s="17"/>
       <c r="F53" s="11">
-        <f>D53/C53</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G53" s="12">
-        <v>0.18</v>
+        <v>0.74399999999999999</v>
       </c>
       <c r="H53" s="11">
-        <f>G53*D53</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="I53" s="11"/>
     </row>
     <row r="54" spans="1:9" s="13" customFormat="1">
       <c r="A54" s="2">
-        <v>9985949</v>
+        <v>6948249</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C54" s="10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D54" s="17"/>
       <c r="E54" s="17"/>
       <c r="F54" s="11">
-        <f>D54/C54</f>
-        <v>0</v>
-      </c>
-      <c r="G54" s="18">
-        <v>1</v>
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G54" s="12">
+        <v>0.82499999999999996</v>
       </c>
       <c r="H54" s="11">
-        <f>G54*D54</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="I54" s="11"/>
     </row>
     <row r="55" spans="1:9" s="13" customFormat="1">
-      <c r="A55" s="2">
-        <v>8786928</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>63</v>
+      <c r="A55" s="15">
+        <v>2105201</v>
+      </c>
+      <c r="B55" s="16" t="s">
+        <v>74</v>
       </c>
       <c r="C55" s="10">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="D55" s="17"/>
       <c r="E55" s="17"/>
       <c r="F55" s="11">
-        <f>E55/6</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G55" s="12">
-        <v>1.5</v>
+        <v>0.1</v>
       </c>
       <c r="H55" s="11">
-        <f>E55</f>
-        <v>0</v>
-      </c>
-      <c r="I55" s="11" t="s">
-        <v>64</v>
-      </c>
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I55" s="11"/>
     </row>
     <row r="56" spans="1:9" s="13" customFormat="1">
-      <c r="A56" s="2">
-        <v>6948270</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>65</v>
+      <c r="A56" s="15">
+        <v>2103201</v>
+      </c>
+      <c r="B56" s="16" t="s">
+        <v>75</v>
       </c>
       <c r="C56" s="10">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D56" s="17"/>
       <c r="E56" s="17"/>
       <c r="F56" s="11">
-        <f>D56/C56</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G56" s="12">
-        <v>0.372</v>
+        <v>0.1</v>
       </c>
       <c r="H56" s="11">
-        <f>G56*D56</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="I56" s="11"/>
     </row>
     <row r="57" spans="1:9" s="13" customFormat="1">
-      <c r="A57" s="2">
-        <v>6948287</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>66</v>
+      <c r="A57" s="15">
+        <v>1103201</v>
+      </c>
+      <c r="B57" s="16" t="s">
+        <v>76</v>
       </c>
       <c r="C57" s="10">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="D57" s="17"/>
       <c r="E57" s="17"/>
       <c r="F57" s="11">
-        <f>D57/C57</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G57" s="12">
-        <v>0.74399999999999999</v>
+        <v>5.5E-2</v>
       </c>
       <c r="H57" s="11">
-        <f>G57*D57</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="I57" s="11"/>
     </row>
     <row r="58" spans="1:9" s="13" customFormat="1">
-      <c r="A58" s="2">
-        <v>6948256</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C58" s="10">
-        <v>12</v>
-      </c>
+      <c r="A58" s="11"/>
+      <c r="B58" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C58" s="11"/>
       <c r="D58" s="17"/>
       <c r="E58" s="17"/>
-      <c r="F58" s="11">
-        <f>D58/C58</f>
-        <v>0</v>
-      </c>
-      <c r="G58" s="12">
-        <v>0.372</v>
-      </c>
-      <c r="H58" s="11">
-        <f>G58*D58</f>
+      <c r="F58" s="11"/>
+      <c r="G58" s="11"/>
+      <c r="H58" s="3">
+        <f>SUM(H4:H57)</f>
         <v>0</v>
       </c>
       <c r="I58" s="11"/>
-    </row>
-    <row r="59" spans="1:9" s="13" customFormat="1">
-      <c r="A59" s="2">
-        <v>6948263</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C59" s="10">
-        <v>12</v>
-      </c>
-      <c r="D59" s="17"/>
-      <c r="E59" s="17"/>
-      <c r="F59" s="11">
-        <f>D59/C59</f>
-        <v>0</v>
-      </c>
-      <c r="G59" s="12">
-        <v>0.74399999999999999</v>
-      </c>
-      <c r="H59" s="11">
-        <f>G59*D59</f>
-        <v>0</v>
-      </c>
-      <c r="I59" s="11"/>
-    </row>
-    <row r="60" spans="1:9">
-      <c r="A60" s="2">
-        <v>6948249</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C60" s="10">
-        <v>12</v>
-      </c>
-      <c r="D60" s="17"/>
-      <c r="E60" s="17"/>
-      <c r="F60" s="11">
-        <f>D60/C60</f>
-        <v>0</v>
-      </c>
-      <c r="G60" s="12">
-        <v>0.82499999999999996</v>
-      </c>
-      <c r="H60" s="11">
-        <f>G60*D60</f>
-        <v>0</v>
-      </c>
-      <c r="I60" s="11"/>
-    </row>
-    <row r="61" spans="1:9">
-      <c r="A61" s="11"/>
-      <c r="B61" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C61" s="11"/>
-      <c r="D61" s="17"/>
-      <c r="E61" s="17"/>
-      <c r="F61" s="11"/>
-      <c r="G61" s="11"/>
-      <c r="H61" s="3">
-        <f>SUM(H4:H60)</f>
-        <v>0</v>
-      </c>
-      <c r="I61" s="11"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:I52" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
@@ -5579,7 +5294,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="10" style="4" customWidth="1"/>
@@ -5607,7 +5322,7 @@
     </row>
     <row r="2" spans="1:9" ht="38.25">
       <c r="A2" s="7" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>12</v>
@@ -5625,25 +5340,25 @@
       <c r="I2" s="7"/>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="37" t="s">
+      <c r="A3" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="37" t="s">
+      <c r="C3" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="38" t="s">
+      <c r="D3" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="38" t="s">
+      <c r="E3" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="37" t="s">
+      <c r="F3" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="39" t="s">
+      <c r="G3" s="32" t="s">
         <v>10</v>
       </c>
       <c r="H3" s="11" t="s">
@@ -5678,207 +5393,203 @@
       </c>
       <c r="I4" s="11"/>
     </row>
-    <row r="5" spans="1:9" s="13" customFormat="1">
-      <c r="A5" s="1">
-        <v>8785204</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="C5" s="10">
+    <row r="5" spans="1:9" s="13" customFormat="1" ht="25.5">
+      <c r="A5" s="33">
+        <v>8783323</v>
+      </c>
+      <c r="B5" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" s="28">
+        <v>4</v>
+      </c>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="11">
+        <f>E5/5</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="22">
+        <v>1.8</v>
+      </c>
+      <c r="H5" s="21">
+        <f>E5</f>
+        <v>0</v>
+      </c>
+      <c r="I5" s="21"/>
+    </row>
+    <row r="6" spans="1:9" s="23" customFormat="1" ht="25.5">
+      <c r="A6" s="1">
+        <v>5038459</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="10">
+        <v>10</v>
+      </c>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="11">
+        <f>D6/C6</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="12">
+        <v>0.18</v>
+      </c>
+      <c r="H6" s="11">
+        <f>G6*D6</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="11"/>
+    </row>
+    <row r="7" spans="1:9" s="13" customFormat="1" ht="25.5">
+      <c r="A7" s="33">
+        <v>8785235</v>
+      </c>
+      <c r="B7" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7" s="10">
         <v>5</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="E5" s="17"/>
-      <c r="F5" s="11">
-        <f>E5/16.5</f>
-        <v>0</v>
-      </c>
-      <c r="G5" s="12">
-        <v>3.2</v>
-      </c>
-      <c r="H5" s="11">
-        <f>E5</f>
-        <v>0</v>
-      </c>
-      <c r="I5" s="11"/>
-    </row>
-    <row r="6" spans="1:9" s="26" customFormat="1" ht="25.5">
-      <c r="A6" s="20">
-        <v>8783323</v>
-      </c>
-      <c r="B6" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="C6" s="22">
-        <v>4</v>
-      </c>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="11">
-        <f>E6/5</f>
-        <v>0</v>
-      </c>
-      <c r="G6" s="25">
-        <v>1.8</v>
-      </c>
-      <c r="H6" s="24">
-        <f>E6</f>
-        <v>0</v>
-      </c>
-      <c r="I6" s="24"/>
-    </row>
-    <row r="7" spans="1:9" s="13" customFormat="1" ht="25.5">
-      <c r="A7" s="1">
-        <v>5038459</v>
-      </c>
-      <c r="B7" s="19" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" s="10">
-        <v>10</v>
       </c>
       <c r="D7" s="17"/>
       <c r="E7" s="17"/>
       <c r="F7" s="11">
-        <f>D7/C7</f>
-        <v>0</v>
-      </c>
-      <c r="G7" s="12">
-        <v>0.18</v>
+        <f>E7/16.5</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="11">
+        <v>3.5</v>
       </c>
       <c r="H7" s="11">
-        <f>G7*D7</f>
-        <v>0</v>
-      </c>
-      <c r="I7" s="11"/>
+        <f>E7</f>
+        <v>0</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="8" spans="1:9" s="13" customFormat="1" ht="25.5">
-      <c r="A8" s="20">
-        <v>8785235</v>
-      </c>
-      <c r="B8" s="21" t="s">
-        <v>79</v>
+      <c r="A8" s="1">
+        <v>5038411</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>34</v>
       </c>
       <c r="C8" s="10">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D8" s="17"/>
       <c r="E8" s="17"/>
       <c r="F8" s="11">
-        <f>E8/16.5</f>
-        <v>0</v>
-      </c>
-      <c r="G8" s="11">
-        <v>3.5</v>
+        <f>D8/C8</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="12">
+        <v>0.18</v>
       </c>
       <c r="H8" s="11">
-        <f>E8</f>
-        <v>0</v>
-      </c>
-      <c r="I8" s="11" t="s">
-        <v>15</v>
-      </c>
+        <f>G8*D8</f>
+        <v>0</v>
+      </c>
+      <c r="I8" s="11"/>
     </row>
     <row r="9" spans="1:9" s="13" customFormat="1" ht="25.5">
-      <c r="A9" s="1">
-        <v>5038411</v>
+      <c r="A9" s="2">
+        <v>8785242</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="C9" s="10">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D9" s="17"/>
       <c r="E9" s="17"/>
       <c r="F9" s="11">
-        <f>D9/C9</f>
-        <v>0</v>
-      </c>
-      <c r="G9" s="12">
-        <v>0.18</v>
+        <f>E9/16.5</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="11">
+        <v>3.5</v>
       </c>
       <c r="H9" s="11">
-        <f>G9*D9</f>
-        <v>0</v>
-      </c>
-      <c r="I9" s="11"/>
+        <f>E9</f>
+        <v>0</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="10" spans="1:9" s="13" customFormat="1" ht="25.5">
-      <c r="A10" s="2">
-        <v>8785242</v>
+      <c r="A10" s="1">
+        <v>5038398</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C10" s="10">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D10" s="17"/>
       <c r="E10" s="17"/>
       <c r="F10" s="11">
-        <f>E10/16.5</f>
-        <v>0</v>
-      </c>
-      <c r="G10" s="11">
-        <v>3.5</v>
+        <f>D10/C10</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="12">
+        <v>0.18</v>
       </c>
       <c r="H10" s="11">
-        <f>E10</f>
-        <v>0</v>
-      </c>
-      <c r="I10" s="11" t="s">
-        <v>15</v>
-      </c>
+        <f>G10*D10</f>
+        <v>0</v>
+      </c>
+      <c r="I10" s="11"/>
     </row>
     <row r="11" spans="1:9" s="13" customFormat="1" ht="25.5">
-      <c r="A11" s="1">
-        <v>5038398</v>
+      <c r="A11" s="2">
+        <v>8785259</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="C11" s="10">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D11" s="17"/>
       <c r="E11" s="17"/>
       <c r="F11" s="11">
-        <f>D11/C11</f>
-        <v>0</v>
-      </c>
-      <c r="G11" s="12">
-        <v>0.18</v>
+        <f>E11/16.5</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="11">
+        <v>3.5</v>
       </c>
       <c r="H11" s="11">
-        <f>G11*D11</f>
+        <f>E11</f>
         <v>0</v>
       </c>
       <c r="I11" s="11"/>
     </row>
-    <row r="12" spans="1:9" s="13" customFormat="1">
-      <c r="A12" s="1">
-        <v>5039609</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>43</v>
+    <row r="12" spans="1:9" s="13" customFormat="1" ht="25.5">
+      <c r="A12" s="2">
+        <v>5038855</v>
+      </c>
+      <c r="B12" s="24" t="s">
+        <v>41</v>
       </c>
       <c r="C12" s="10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D12" s="17"/>
-      <c r="E12" s="17" t="s">
-        <v>77</v>
-      </c>
+      <c r="E12" s="17"/>
       <c r="F12" s="11">
         <f>D12/C12</f>
         <v>0</v>
       </c>
       <c r="G12" s="12">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="H12" s="11">
         <f>G12*D12</f>
@@ -5888,471 +5599,469 @@
     </row>
     <row r="13" spans="1:9" s="13" customFormat="1" ht="25.5">
       <c r="A13" s="2">
-        <v>8785259</v>
+        <v>5038831</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="C13" s="10">
-        <v>5</v>
+        <v>39</v>
+      </c>
+      <c r="C13" s="25">
+        <v>10</v>
       </c>
       <c r="D13" s="17"/>
       <c r="E13" s="17"/>
       <c r="F13" s="11">
-        <f>E13/16.5</f>
-        <v>0</v>
-      </c>
-      <c r="G13" s="11">
-        <v>3.5</v>
+        <f>D13/C13</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="12">
+        <v>0.18</v>
       </c>
       <c r="H13" s="11">
-        <f>E13</f>
+        <f>G13*D13</f>
         <v>0</v>
       </c>
       <c r="I13" s="11"/>
     </row>
-    <row r="14" spans="1:9" s="13" customFormat="1" ht="25.5">
-      <c r="A14" s="2">
-        <v>5038855</v>
-      </c>
-      <c r="B14" s="27" t="s">
-        <v>41</v>
-      </c>
-      <c r="C14" s="10">
-        <v>10</v>
+    <row r="14" spans="1:9" s="13" customFormat="1" ht="38.25">
+      <c r="A14" s="26">
+        <v>8784931</v>
+      </c>
+      <c r="B14" s="34" t="s">
+        <v>73</v>
+      </c>
+      <c r="C14" s="25">
+        <v>5</v>
       </c>
       <c r="D14" s="17"/>
       <c r="E14" s="17"/>
       <c r="F14" s="11">
-        <f t="shared" ref="F14:F27" si="0">D14/C14</f>
+        <f>E14/16.5</f>
         <v>0</v>
       </c>
       <c r="G14" s="12">
-        <v>0.2</v>
+        <v>3.5</v>
       </c>
       <c r="H14" s="11">
-        <f>G14*D14</f>
-        <v>0</v>
-      </c>
-      <c r="I14" s="11"/>
+        <f>E14</f>
+        <v>0</v>
+      </c>
+      <c r="I14" s="11" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="15" spans="1:9" s="13" customFormat="1">
       <c r="A15" s="2">
-        <v>5039647</v>
-      </c>
-      <c r="B15" s="28" t="s">
-        <v>44</v>
+        <v>1018950</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>40</v>
       </c>
       <c r="C15" s="10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D15" s="17"/>
       <c r="E15" s="17"/>
       <c r="F15" s="11">
-        <f t="shared" si="0"/>
+        <f>D15/C15</f>
         <v>0</v>
       </c>
       <c r="G15" s="12">
-        <v>0.4</v>
+        <v>0.18</v>
       </c>
       <c r="H15" s="11">
-        <f>G15*D15</f>
+        <f t="shared" ref="H15:H23" si="0">G15*D15</f>
         <v>0</v>
       </c>
       <c r="I15" s="11"/>
     </row>
-    <row r="16" spans="1:9" s="13" customFormat="1" ht="25.5">
+    <row r="16" spans="1:9" s="13" customFormat="1">
       <c r="A16" s="2">
-        <v>5038831</v>
-      </c>
-      <c r="B16" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="C16" s="29">
+        <v>1018967</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" s="10">
         <v>10</v>
       </c>
       <c r="D16" s="17"/>
       <c r="E16" s="17"/>
       <c r="F16" s="11">
-        <f t="shared" si="0"/>
+        <f>D16/C16</f>
         <v>0</v>
       </c>
       <c r="G16" s="12">
         <v>0.18</v>
       </c>
       <c r="H16" s="11">
-        <f>G16*D16</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I16" s="11"/>
     </row>
     <row r="17" spans="1:9" s="13" customFormat="1">
       <c r="A17" s="2">
-        <v>5039623</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="C17" s="29">
-        <v>8</v>
+        <v>8444194</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="10">
+        <v>6</v>
       </c>
       <c r="D17" s="17"/>
-      <c r="E17" s="17" t="s">
-        <v>77</v>
-      </c>
+      <c r="E17" s="17"/>
       <c r="F17" s="11">
+        <f t="shared" ref="F17:F23" si="1">D17/C17</f>
+        <v>0</v>
+      </c>
+      <c r="G17" s="12">
+        <v>0.1</v>
+      </c>
+      <c r="H17" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G17" s="12">
-        <v>0.4</v>
-      </c>
-      <c r="H17" s="11">
-        <f>G17*D17</f>
-        <v>0</v>
-      </c>
       <c r="I17" s="11"/>
     </row>
-    <row r="18" spans="1:9" s="13" customFormat="1" ht="38.25">
-      <c r="A18" s="15">
-        <v>8784931</v>
-      </c>
-      <c r="B18" s="21" t="s">
-        <v>80</v>
-      </c>
-      <c r="C18" s="29">
-        <v>5</v>
+    <row r="18" spans="1:9" s="13" customFormat="1">
+      <c r="A18" s="2">
+        <v>8444187</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" s="10">
+        <v>6</v>
       </c>
       <c r="D18" s="17"/>
       <c r="E18" s="17"/>
       <c r="F18" s="11">
-        <f>E18/16.4</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G18" s="12">
-        <v>3.5</v>
+        <v>0.1</v>
       </c>
       <c r="H18" s="11">
-        <f>E18</f>
-        <v>0</v>
-      </c>
-      <c r="I18" s="11" t="s">
-        <v>81</v>
-      </c>
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I18" s="11"/>
     </row>
     <row r="19" spans="1:9" s="13" customFormat="1">
       <c r="A19" s="2">
-        <v>1018950</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>40</v>
+        <v>8444163</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>22</v>
       </c>
       <c r="C19" s="10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D19" s="17"/>
       <c r="E19" s="17"/>
       <c r="F19" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G19" s="12">
+        <v>0.1</v>
+      </c>
+      <c r="H19" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G19" s="12">
-        <v>0.18</v>
-      </c>
-      <c r="H19" s="11">
-        <f t="shared" ref="H19:H27" si="1">G19*D19</f>
         <v>0</v>
       </c>
       <c r="I19" s="11"/>
     </row>
     <row r="20" spans="1:9" s="13" customFormat="1">
       <c r="A20" s="2">
-        <v>1018967</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>42</v>
+        <v>8444170</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>56</v>
       </c>
       <c r="C20" s="10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D20" s="17"/>
       <c r="E20" s="17"/>
       <c r="F20" s="11">
+        <f>D20/C20</f>
+        <v>0</v>
+      </c>
+      <c r="G20" s="12">
+        <v>0.1</v>
+      </c>
+      <c r="H20" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G20" s="12">
-        <v>0.18</v>
-      </c>
-      <c r="H20" s="11">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I20" s="11"/>
     </row>
     <row r="21" spans="1:9" s="13" customFormat="1">
       <c r="A21" s="2">
-        <v>8444194</v>
+        <v>9988377</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C21" s="10">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D21" s="17"/>
       <c r="E21" s="17"/>
       <c r="F21" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G21" s="12">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="H21" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G21" s="12">
-        <v>0.1</v>
-      </c>
-      <c r="H21" s="11">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I21" s="11"/>
     </row>
     <row r="22" spans="1:9" s="13" customFormat="1">
       <c r="A22" s="2">
-        <v>8444187</v>
+        <v>9988391</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C22" s="10">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D22" s="17"/>
       <c r="E22" s="17"/>
       <c r="F22" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G22" s="12">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="H22" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G22" s="12">
-        <v>0.1</v>
-      </c>
-      <c r="H22" s="11">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I22" s="11"/>
     </row>
     <row r="23" spans="1:9" s="13" customFormat="1">
       <c r="A23" s="2">
-        <v>8444163</v>
+        <v>5034819</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C23" s="10">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D23" s="17"/>
       <c r="E23" s="17"/>
       <c r="F23" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G23" s="12">
+        <v>0.18</v>
+      </c>
+      <c r="H23" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G23" s="12">
-        <v>0.1</v>
-      </c>
-      <c r="H23" s="11">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I23" s="11"/>
     </row>
     <row r="24" spans="1:9" s="13" customFormat="1">
       <c r="A24" s="2">
-        <v>8444170</v>
+        <v>2981244</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="C24" s="10">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D24" s="17"/>
       <c r="E24" s="17"/>
       <c r="F24" s="11">
-        <f>D24/C24</f>
+        <f>E24/7.8</f>
         <v>0</v>
       </c>
       <c r="G24" s="12">
-        <v>0.1</v>
+        <v>1.3</v>
       </c>
       <c r="H24" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I24" s="11"/>
+        <f>E24</f>
+        <v>0</v>
+      </c>
+      <c r="I24" s="11" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="25" spans="1:9" s="13" customFormat="1">
       <c r="A25" s="2">
-        <v>9988377</v>
+        <v>8785198</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C25" s="10">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D25" s="17"/>
       <c r="E25" s="17"/>
       <c r="F25" s="11">
-        <f t="shared" si="0"/>
+        <f>E25/16.5</f>
         <v>0</v>
       </c>
       <c r="G25" s="12">
-        <v>0.14000000000000001</v>
+        <v>3.2</v>
       </c>
       <c r="H25" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I25" s="11"/>
+        <f>E25</f>
+        <v>0</v>
+      </c>
+      <c r="I25" s="11" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="26" spans="1:9" s="13" customFormat="1">
       <c r="A26" s="2">
-        <v>9988391</v>
+        <v>9988452</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C26" s="10">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D26" s="17"/>
       <c r="E26" s="17"/>
       <c r="F26" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="F26:F37" si="2">D26/C26</f>
         <v>0</v>
       </c>
       <c r="G26" s="12">
-        <v>0.14000000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="H26" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="H26:H31" si="3">G26*D26</f>
         <v>0</v>
       </c>
       <c r="I26" s="11"/>
     </row>
     <row r="27" spans="1:9" s="13" customFormat="1">
       <c r="A27" s="2">
-        <v>5034819</v>
+        <v>9988476</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C27" s="10">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="D27" s="17"/>
       <c r="E27" s="17"/>
       <c r="F27" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G27" s="12">
-        <v>0.18</v>
+        <v>0.4</v>
       </c>
       <c r="H27" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I27" s="11"/>
     </row>
     <row r="28" spans="1:9" s="13" customFormat="1">
       <c r="A28" s="2">
-        <v>2981244</v>
+        <v>9988681</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="C28" s="10">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D28" s="17"/>
       <c r="E28" s="17"/>
       <c r="F28" s="11">
-        <f>E28/7.8</f>
+        <f>D28/C28</f>
         <v>0</v>
       </c>
       <c r="G28" s="12">
-        <v>1.3</v>
+        <v>0.18</v>
       </c>
       <c r="H28" s="11">
-        <f>E28</f>
-        <v>0</v>
-      </c>
-      <c r="I28" s="11" t="s">
-        <v>19</v>
-      </c>
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I28" s="11"/>
     </row>
     <row r="29" spans="1:9" s="13" customFormat="1">
       <c r="A29" s="2">
-        <v>8785198</v>
+        <v>9988438</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C29" s="10">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D29" s="17"/>
       <c r="E29" s="17"/>
       <c r="F29" s="11">
-        <f>E29/16.5</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G29" s="12">
-        <v>3.2</v>
+        <v>0.18</v>
       </c>
       <c r="H29" s="11">
-        <f>E29</f>
-        <v>0</v>
-      </c>
-      <c r="I29" s="11" t="s">
-        <v>15</v>
-      </c>
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I29" s="11"/>
     </row>
     <row r="30" spans="1:9" s="13" customFormat="1">
       <c r="A30" s="2">
-        <v>9988452</v>
+        <v>9988445</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C30" s="10">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D30" s="17"/>
       <c r="E30" s="17"/>
       <c r="F30" s="11">
-        <f t="shared" ref="F30:F43" si="2">D30/C30</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G30" s="12">
-        <v>0.4</v>
+        <v>0.18</v>
       </c>
       <c r="H30" s="11">
-        <f t="shared" ref="H30:H35" si="3">G30*D30</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I30" s="11"/>
     </row>
     <row r="31" spans="1:9" s="13" customFormat="1">
       <c r="A31" s="2">
-        <v>9988476</v>
+        <v>9988421</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C31" s="10">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="D31" s="17"/>
       <c r="E31" s="17"/>
@@ -6361,7 +6070,7 @@
         <v>0</v>
       </c>
       <c r="G31" s="12">
-        <v>0.4</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="H31" s="11">
         <f t="shared" si="3"/>
@@ -6371,10 +6080,10 @@
     </row>
     <row r="32" spans="1:9" s="13" customFormat="1">
       <c r="A32" s="2">
-        <v>9988681</v>
+        <v>9988674</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C32" s="10">
         <v>16</v>
@@ -6382,27 +6091,27 @@
       <c r="D32" s="17"/>
       <c r="E32" s="17"/>
       <c r="F32" s="11">
-        <f>D32/C32</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G32" s="12">
         <v>0.18</v>
       </c>
       <c r="H32" s="11">
-        <f t="shared" si="3"/>
+        <f>D32*G32</f>
         <v>0</v>
       </c>
       <c r="I32" s="11"/>
     </row>
     <row r="33" spans="1:9" s="13" customFormat="1">
-      <c r="A33" s="2">
-        <v>9988438</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>30</v>
+      <c r="A33" s="26">
+        <v>8444903</v>
+      </c>
+      <c r="B33" s="27" t="s">
+        <v>45</v>
       </c>
       <c r="C33" s="10">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D33" s="17"/>
       <c r="E33" s="17"/>
@@ -6411,23 +6120,23 @@
         <v>0</v>
       </c>
       <c r="G33" s="12">
-        <v>0.18</v>
+        <v>0.1</v>
       </c>
       <c r="H33" s="11">
-        <f t="shared" si="3"/>
+        <f>D33*G33</f>
         <v>0</v>
       </c>
       <c r="I33" s="11"/>
     </row>
     <row r="34" spans="1:9" s="13" customFormat="1">
-      <c r="A34" s="2">
-        <v>9988445</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>31</v>
+      <c r="A34" s="26">
+        <v>8444910</v>
+      </c>
+      <c r="B34" s="27" t="s">
+        <v>46</v>
       </c>
       <c r="C34" s="10">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D34" s="17"/>
       <c r="E34" s="17"/>
@@ -6436,23 +6145,23 @@
         <v>0</v>
       </c>
       <c r="G34" s="12">
-        <v>0.18</v>
+        <v>0.1</v>
       </c>
       <c r="H34" s="11">
-        <f t="shared" si="3"/>
+        <f>D34*G34</f>
         <v>0</v>
       </c>
       <c r="I34" s="11"/>
     </row>
     <row r="35" spans="1:9" s="13" customFormat="1">
-      <c r="A35" s="2">
-        <v>9988421</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>32</v>
+      <c r="A35" s="26">
+        <v>8444927</v>
+      </c>
+      <c r="B35" s="27" t="s">
+        <v>47</v>
       </c>
       <c r="C35" s="10">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D35" s="17"/>
       <c r="E35" s="17"/>
@@ -6461,23 +6170,23 @@
         <v>0</v>
       </c>
       <c r="G35" s="12">
-        <v>0.14000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="H35" s="11">
-        <f t="shared" si="3"/>
+        <f>D35*G35</f>
         <v>0</v>
       </c>
       <c r="I35" s="11"/>
     </row>
     <row r="36" spans="1:9" s="13" customFormat="1">
       <c r="A36" s="2">
-        <v>9988674</v>
+        <v>8445160</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="C36" s="10">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D36" s="17"/>
       <c r="E36" s="17"/>
@@ -6486,20 +6195,20 @@
         <v>0</v>
       </c>
       <c r="G36" s="12">
-        <v>0.18</v>
+        <v>0.1</v>
       </c>
       <c r="H36" s="11">
-        <f t="shared" ref="H36:H43" si="4">D36*G36</f>
+        <f>G36*D36</f>
         <v>0</v>
       </c>
       <c r="I36" s="11"/>
     </row>
     <row r="37" spans="1:9" s="13" customFormat="1">
-      <c r="A37" s="30">
-        <v>8444903</v>
-      </c>
-      <c r="B37" s="31" t="s">
-        <v>49</v>
+      <c r="A37" s="2">
+        <v>8445177</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>65</v>
       </c>
       <c r="C37" s="10">
         <v>8</v>
@@ -6514,79 +6223,81 @@
         <v>0.1</v>
       </c>
       <c r="H37" s="11">
-        <f t="shared" si="4"/>
+        <f>G37*D37</f>
         <v>0</v>
       </c>
       <c r="I37" s="11"/>
     </row>
     <row r="38" spans="1:9" s="13" customFormat="1">
-      <c r="A38" s="30">
-        <v>8444910</v>
-      </c>
-      <c r="B38" s="31" t="s">
-        <v>50</v>
+      <c r="A38" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>13</v>
       </c>
       <c r="C38" s="10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D38" s="17"/>
       <c r="E38" s="17"/>
       <c r="F38" s="11">
-        <f t="shared" si="2"/>
+        <f>D38/C38</f>
         <v>0</v>
       </c>
       <c r="G38" s="12">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H38" s="11">
-        <f t="shared" si="4"/>
+        <f>G38*D38</f>
         <v>0</v>
       </c>
       <c r="I38" s="11"/>
     </row>
     <row r="39" spans="1:9" s="13" customFormat="1">
-      <c r="A39" s="30">
-        <v>8444927</v>
-      </c>
-      <c r="B39" s="31" t="s">
-        <v>51</v>
+      <c r="A39" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>16</v>
       </c>
       <c r="C39" s="10">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D39" s="17"/>
       <c r="E39" s="17"/>
       <c r="F39" s="11">
-        <f t="shared" si="2"/>
+        <f>E39/15</f>
         <v>0</v>
       </c>
       <c r="G39" s="12">
-        <v>0.1</v>
+        <v>3.5</v>
       </c>
       <c r="H39" s="11">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I39" s="11"/>
-    </row>
-    <row r="40" spans="1:9" s="36" customFormat="1">
-      <c r="A40" s="15">
-        <v>8445160</v>
-      </c>
-      <c r="B40" s="16" t="s">
-        <v>70</v>
+        <f>E39</f>
+        <v>0</v>
+      </c>
+      <c r="I39" s="11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" s="29" customFormat="1">
+      <c r="A40" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B40" s="12" t="s">
+        <v>14</v>
       </c>
       <c r="C40" s="10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D40" s="17"/>
       <c r="E40" s="17"/>
       <c r="F40" s="11">
-        <f t="shared" si="2"/>
+        <f>D40/C40</f>
         <v>0</v>
       </c>
       <c r="G40" s="12">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H40" s="11">
         <f>G40*D40</f>
@@ -6594,94 +6305,94 @@
       </c>
       <c r="I40" s="11"/>
     </row>
-    <row r="41" spans="1:9" s="36" customFormat="1" ht="11.25" customHeight="1">
-      <c r="A41" s="15">
-        <v>8445177</v>
-      </c>
-      <c r="B41" s="16" t="s">
-        <v>71</v>
+    <row r="41" spans="1:9" s="29" customFormat="1" ht="11.25" customHeight="1">
+      <c r="A41" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B41" s="12" t="s">
+        <v>17</v>
       </c>
       <c r="C41" s="10">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D41" s="17"/>
       <c r="E41" s="17"/>
       <c r="F41" s="11">
-        <f t="shared" si="2"/>
+        <f>E41/15</f>
         <v>0</v>
       </c>
       <c r="G41" s="12">
-        <v>0.1</v>
+        <v>3.5</v>
       </c>
       <c r="H41" s="11">
-        <f>G41*D41</f>
-        <v>0</v>
-      </c>
-      <c r="I41" s="11"/>
+        <f>E41</f>
+        <v>0</v>
+      </c>
+      <c r="I41" s="11" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="42" spans="1:9" s="13" customFormat="1">
-      <c r="A42" s="30">
-        <v>6600454</v>
-      </c>
-      <c r="B42" s="31" t="s">
-        <v>54</v>
-      </c>
-      <c r="C42" s="32">
+      <c r="A42" s="2">
+        <v>7100108</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C42" s="10">
         <v>12</v>
       </c>
-      <c r="D42" s="33"/>
-      <c r="E42" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="F42" s="34">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G42" s="35">
-        <v>0.125</v>
-      </c>
-      <c r="H42" s="34">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I42" s="34"/>
+      <c r="D42" s="17"/>
+      <c r="E42" s="17"/>
+      <c r="F42" s="11">
+        <f>D42/C42</f>
+        <v>0</v>
+      </c>
+      <c r="G42" s="12">
+        <v>0.2</v>
+      </c>
+      <c r="H42" s="11">
+        <f>D42*G42</f>
+        <v>0</v>
+      </c>
+      <c r="I42" s="11"/>
     </row>
     <row r="43" spans="1:9" s="13" customFormat="1">
-      <c r="A43" s="30">
-        <v>6600447</v>
-      </c>
-      <c r="B43" s="31" t="s">
-        <v>53</v>
-      </c>
-      <c r="C43" s="32">
+      <c r="A43" s="2">
+        <v>7100139</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C43" s="10">
+        <v>8</v>
+      </c>
+      <c r="D43" s="17"/>
+      <c r="E43" s="17"/>
+      <c r="F43" s="11">
+        <f>E43/20</f>
+        <v>0</v>
+      </c>
+      <c r="G43" s="12">
+        <v>2.5</v>
+      </c>
+      <c r="H43" s="11">
+        <f>E43</f>
+        <v>0</v>
+      </c>
+      <c r="I43" s="11" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" s="13" customFormat="1">
+      <c r="A44" s="2">
+        <v>7100740</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C44" s="10">
         <v>12</v>
-      </c>
-      <c r="D43" s="33"/>
-      <c r="E43" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="F43" s="34">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G43" s="35">
-        <v>0.125</v>
-      </c>
-      <c r="H43" s="34">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I43" s="34"/>
-    </row>
-    <row r="44" spans="1:9" s="13" customFormat="1">
-      <c r="A44" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B44" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="C44" s="10">
-        <v>10</v>
       </c>
       <c r="D44" s="17"/>
       <c r="E44" s="17"/>
@@ -6693,47 +6404,47 @@
         <v>0.2</v>
       </c>
       <c r="H44" s="11">
-        <f>G44*D44</f>
+        <f>D44*G44</f>
         <v>0</v>
       </c>
       <c r="I44" s="11"/>
     </row>
     <row r="45" spans="1:9" s="13" customFormat="1">
-      <c r="A45" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B45" s="12" t="s">
-        <v>16</v>
+      <c r="A45" s="2">
+        <v>7100726</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>70</v>
       </c>
       <c r="C45" s="10">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D45" s="17"/>
       <c r="E45" s="17"/>
       <c r="F45" s="11">
-        <f>E45/15</f>
+        <f>E45/20</f>
         <v>0</v>
       </c>
       <c r="G45" s="12">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="H45" s="11">
         <f>E45</f>
         <v>0</v>
       </c>
       <c r="I45" s="11" t="s">
-        <v>18</v>
+        <v>68</v>
       </c>
     </row>
     <row r="46" spans="1:9" s="13" customFormat="1">
-      <c r="A46" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B46" s="12" t="s">
-        <v>14</v>
+      <c r="A46" s="2">
+        <v>4421584</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>54</v>
       </c>
       <c r="C46" s="10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D46" s="17"/>
       <c r="E46" s="17"/>
@@ -6742,7 +6453,7 @@
         <v>0</v>
       </c>
       <c r="G46" s="12">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="H46" s="11">
         <f>G46*D46</f>
@@ -6751,41 +6462,39 @@
       <c r="I46" s="11"/>
     </row>
     <row r="47" spans="1:9" s="13" customFormat="1">
-      <c r="A47" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B47" s="12" t="s">
-        <v>17</v>
+      <c r="A47" s="2">
+        <v>4421577</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>53</v>
       </c>
       <c r="C47" s="10">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D47" s="17"/>
       <c r="E47" s="17"/>
       <c r="F47" s="11">
-        <f>E47/15</f>
+        <f>D47/C47</f>
         <v>0</v>
       </c>
       <c r="G47" s="12">
-        <v>3.5</v>
+        <v>0.18</v>
       </c>
       <c r="H47" s="11">
-        <f>E47</f>
-        <v>0</v>
-      </c>
-      <c r="I47" s="11" t="s">
-        <v>18</v>
-      </c>
+        <f>G47*D47</f>
+        <v>0</v>
+      </c>
+      <c r="I47" s="11"/>
     </row>
     <row r="48" spans="1:9" s="13" customFormat="1">
       <c r="A48" s="2">
-        <v>7100108</v>
+        <v>9985949</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="C48" s="10">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D48" s="17"/>
       <c r="E48" s="17"/>
@@ -6793,48 +6502,48 @@
         <f>D48/C48</f>
         <v>0</v>
       </c>
-      <c r="G48" s="12">
-        <v>0.2</v>
+      <c r="G48" s="18">
+        <v>1</v>
       </c>
       <c r="H48" s="11">
-        <f>D48*G48</f>
+        <f>G48*D48</f>
         <v>0</v>
       </c>
       <c r="I48" s="11"/>
     </row>
     <row r="49" spans="1:9" s="13" customFormat="1">
       <c r="A49" s="2">
-        <v>7100139</v>
+        <v>8786928</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="C49" s="10">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D49" s="17"/>
       <c r="E49" s="17"/>
       <c r="F49" s="11">
-        <f>E49/20</f>
+        <f>E49/6</f>
         <v>0</v>
       </c>
       <c r="G49" s="12">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="H49" s="11">
         <f>E49</f>
         <v>0</v>
       </c>
       <c r="I49" s="11" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
     </row>
     <row r="50" spans="1:9" s="13" customFormat="1">
       <c r="A50" s="2">
-        <v>7100740</v>
+        <v>6948270</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="C50" s="10">
         <v>12</v>
@@ -6842,51 +6551,49 @@
       <c r="D50" s="17"/>
       <c r="E50" s="17"/>
       <c r="F50" s="11">
-        <f>D50/C50</f>
+        <f t="shared" ref="F50:F57" si="4">D50/C50</f>
         <v>0</v>
       </c>
       <c r="G50" s="12">
-        <v>0.2</v>
+        <v>0.372</v>
       </c>
       <c r="H50" s="11">
-        <f>D50*G50</f>
+        <f t="shared" ref="H50:H57" si="5">G50*D50</f>
         <v>0</v>
       </c>
       <c r="I50" s="11"/>
     </row>
     <row r="51" spans="1:9" s="13" customFormat="1">
       <c r="A51" s="2">
-        <v>7100726</v>
+        <v>6948287</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="C51" s="10">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D51" s="17"/>
       <c r="E51" s="17"/>
       <c r="F51" s="11">
-        <f>E51/20</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G51" s="12">
-        <v>2.5</v>
+        <v>0.74399999999999999</v>
       </c>
       <c r="H51" s="11">
-        <f>E51</f>
-        <v>0</v>
-      </c>
-      <c r="I51" s="11" t="s">
-        <v>74</v>
-      </c>
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I51" s="11"/>
     </row>
     <row r="52" spans="1:9" s="13" customFormat="1">
       <c r="A52" s="2">
-        <v>4421584</v>
+        <v>6948256</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C52" s="10">
         <v>12</v>
@@ -6894,24 +6601,24 @@
       <c r="D52" s="17"/>
       <c r="E52" s="17"/>
       <c r="F52" s="11">
-        <f>D52/C52</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G52" s="12">
-        <v>0.18</v>
+        <v>0.372</v>
       </c>
       <c r="H52" s="11">
-        <f>G52*D52</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="I52" s="11"/>
     </row>
     <row r="53" spans="1:9" s="13" customFormat="1">
       <c r="A53" s="2">
-        <v>4421577</v>
+        <v>6948263</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C53" s="10">
         <v>12</v>
@@ -6919,210 +6626,133 @@
       <c r="D53" s="17"/>
       <c r="E53" s="17"/>
       <c r="F53" s="11">
-        <f>D53/C53</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G53" s="12">
-        <v>0.18</v>
+        <v>0.74399999999999999</v>
       </c>
       <c r="H53" s="11">
-        <f>G53*D53</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="I53" s="11"/>
     </row>
     <row r="54" spans="1:9" s="13" customFormat="1">
       <c r="A54" s="2">
-        <v>9985949</v>
+        <v>6948249</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C54" s="10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D54" s="17"/>
       <c r="E54" s="17"/>
       <c r="F54" s="11">
-        <f>D54/C54</f>
-        <v>0</v>
-      </c>
-      <c r="G54" s="18">
-        <v>1</v>
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G54" s="12">
+        <v>0.82499999999999996</v>
       </c>
       <c r="H54" s="11">
-        <f>G54*D54</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="I54" s="11"/>
     </row>
     <row r="55" spans="1:9" s="13" customFormat="1">
-      <c r="A55" s="2">
-        <v>8786928</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>63</v>
+      <c r="A55" s="15">
+        <v>2105201</v>
+      </c>
+      <c r="B55" s="16" t="s">
+        <v>74</v>
       </c>
       <c r="C55" s="10">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="D55" s="17"/>
       <c r="E55" s="17"/>
       <c r="F55" s="11">
-        <f>E55/6</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G55" s="12">
-        <v>1.5</v>
+        <v>0.1</v>
       </c>
       <c r="H55" s="11">
-        <f>E55</f>
-        <v>0</v>
-      </c>
-      <c r="I55" s="11" t="s">
-        <v>64</v>
-      </c>
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I55" s="11"/>
     </row>
     <row r="56" spans="1:9" s="13" customFormat="1">
-      <c r="A56" s="2">
-        <v>6948270</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>65</v>
+      <c r="A56" s="15">
+        <v>2103201</v>
+      </c>
+      <c r="B56" s="16" t="s">
+        <v>75</v>
       </c>
       <c r="C56" s="10">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D56" s="17"/>
       <c r="E56" s="17"/>
       <c r="F56" s="11">
-        <f>D56/C56</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G56" s="12">
-        <v>0.372</v>
+        <v>0.1</v>
       </c>
       <c r="H56" s="11">
-        <f>G56*D56</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="I56" s="11"/>
     </row>
     <row r="57" spans="1:9" s="13" customFormat="1">
-      <c r="A57" s="2">
-        <v>6948287</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>66</v>
+      <c r="A57" s="15">
+        <v>1103201</v>
+      </c>
+      <c r="B57" s="16" t="s">
+        <v>76</v>
       </c>
       <c r="C57" s="10">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="D57" s="17"/>
       <c r="E57" s="17"/>
       <c r="F57" s="11">
-        <f>D57/C57</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G57" s="12">
-        <v>0.74399999999999999</v>
+        <v>5.5E-2</v>
       </c>
       <c r="H57" s="11">
-        <f>G57*D57</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="I57" s="11"/>
     </row>
     <row r="58" spans="1:9" s="13" customFormat="1">
-      <c r="A58" s="2">
-        <v>6948256</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C58" s="10">
-        <v>12</v>
-      </c>
+      <c r="A58" s="11"/>
+      <c r="B58" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C58" s="11"/>
       <c r="D58" s="17"/>
       <c r="E58" s="17"/>
-      <c r="F58" s="11">
-        <f>D58/C58</f>
-        <v>0</v>
-      </c>
-      <c r="G58" s="12">
-        <v>0.372</v>
-      </c>
-      <c r="H58" s="11">
-        <f>G58*D58</f>
+      <c r="F58" s="11"/>
+      <c r="G58" s="11"/>
+      <c r="H58" s="3">
+        <f>SUM(H4:H57)</f>
         <v>0</v>
       </c>
       <c r="I58" s="11"/>
-    </row>
-    <row r="59" spans="1:9" s="13" customFormat="1">
-      <c r="A59" s="2">
-        <v>6948263</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C59" s="10">
-        <v>12</v>
-      </c>
-      <c r="D59" s="17"/>
-      <c r="E59" s="17"/>
-      <c r="F59" s="11">
-        <f>D59/C59</f>
-        <v>0</v>
-      </c>
-      <c r="G59" s="12">
-        <v>0.74399999999999999</v>
-      </c>
-      <c r="H59" s="11">
-        <f>G59*D59</f>
-        <v>0</v>
-      </c>
-      <c r="I59" s="11"/>
-    </row>
-    <row r="60" spans="1:9">
-      <c r="A60" s="2">
-        <v>6948249</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C60" s="10">
-        <v>12</v>
-      </c>
-      <c r="D60" s="17"/>
-      <c r="E60" s="17"/>
-      <c r="F60" s="11">
-        <f>D60/C60</f>
-        <v>0</v>
-      </c>
-      <c r="G60" s="12">
-        <v>0.82499999999999996</v>
-      </c>
-      <c r="H60" s="11">
-        <f>G60*D60</f>
-        <v>0</v>
-      </c>
-      <c r="I60" s="11"/>
-    </row>
-    <row r="61" spans="1:9">
-      <c r="A61" s="11"/>
-      <c r="B61" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C61" s="11"/>
-      <c r="D61" s="17"/>
-      <c r="E61" s="17"/>
-      <c r="F61" s="11"/>
-      <c r="G61" s="11"/>
-      <c r="H61" s="3">
-        <f>SUM(H4:H60)</f>
-        <v>0</v>
-      </c>
-      <c r="I61" s="11"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:I52" xr:uid="{00000000-0009-0000-0000-000003000000}"/>

--- a/в бланки заводов/Останкино СЫР/OrderCheeseInForm/новый_бланк/Бланк заказов сыр  дистр.xlsx
+++ b/в бланки заводов/Останкино СЫР/OrderCheeseInForm/новый_бланк/Бланк заказов сыр  дистр.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино СЫР\OrderCheeseInForm\новый_бланк\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1822C4D7-091B-4FC2-A136-C10D4FA25580}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59F80CE1-D558-42EC-99D0-C3F1F4950C55}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Мелитополь" sheetId="1" r:id="rId1"/>
@@ -2311,7 +2311,7 @@
         <v>76</v>
       </c>
       <c r="C57" s="10">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="D57" s="17"/>
       <c r="E57" s="17"/>
@@ -3785,7 +3785,7 @@
         <v>76</v>
       </c>
       <c r="C57" s="10">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="D57" s="17"/>
       <c r="E57" s="17"/>
@@ -5253,7 +5253,7 @@
         <v>76</v>
       </c>
       <c r="C57" s="10">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="D57" s="17"/>
       <c r="E57" s="17"/>
@@ -6721,7 +6721,7 @@
         <v>76</v>
       </c>
       <c r="C57" s="10">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="D57" s="17"/>
       <c r="E57" s="17"/>
